--- a/files/BUS331_Investment_Committee_Decision_Record_Student.xlsx
+++ b/files/BUS331_Investment_Committee_Decision_Record_Student.xlsx
@@ -24,7 +24,7 @@
   <x:numFmts count="1">
     <x:numFmt numFmtId="200" formatCode="mmm d, yyyy"/>
   </x:numFmts>
-  <x:fonts count="15">
+  <x:fonts count="16">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -108,6 +108,11 @@
       <x:color rgb="FF8A3027"/>
       <x:name val="Carlito"/>
     </x:font>
+    <x:font>
+      <x:sz val="10"/>
+      <x:color rgb="FF102238"/>
+      <x:name val="Aptos"/>
+    </x:font>
   </x:fonts>
   <x:fills count="10">
     <x:fill>
@@ -157,7 +162,7 @@
       </x:patternFill>
     </x:fill>
   </x:fills>
-  <x:borders count="22">
+  <x:borders count="23">
     <x:border/>
     <x:border>
       <x:left style="thin">
@@ -265,6 +270,20 @@
       <x:left style="thin">
         <x:color rgb="FFD9B973"/>
       </x:left>
+      <x:right style="thin">
+        <x:color rgb="FFD9B973"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color rgb="FFD9B973"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FFD9B973"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FFD9B973"/>
+      </x:left>
       <x:top style="thin">
         <x:color rgb="FFD9B973"/>
       </x:top>
@@ -355,7 +374,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="117">
+  <x:cellXfs count="126">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -461,25 +480,31 @@
     <x:xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
     <x:xf numFmtId="0" fontId="9" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="9" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="12" fillId="4" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="1"/>
-    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="12" fillId="4" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center" wrapText="1"/>
+    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="12" fillId="4" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
     <x:xf numFmtId="0" fontId="12" fillId="4" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="12" fillId="4" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="12" fillId="4" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -487,9 +512,7 @@
     <x:xf numFmtId="0" fontId="12" fillId="4" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="12" fillId="4" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="12" fillId="4" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="1"/>
-    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="12" fillId="4" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
@@ -499,12 +522,12 @@
     <x:xf numFmtId="0" fontId="12" fillId="4" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
     <x:xf numFmtId="0" fontId="12" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="1"/>
-    </x:xf>
     <x:xf numFmtId="0" fontId="12" fillId="4" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
@@ -514,8 +537,8 @@
     <x:xf numFmtId="0" fontId="12" fillId="4" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center" wrapText="1"/>
+    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="12" fillId="4" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
@@ -526,12 +549,12 @@
     <x:xf numFmtId="0" fontId="12" fillId="4" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
     <x:xf numFmtId="0" fontId="12" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center" wrapText="1"/>
-    </x:xf>
     <x:xf numFmtId="0" fontId="12" fillId="4" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
@@ -541,13 +564,16 @@
     <x:xf numFmtId="0" fontId="12" fillId="4" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="200" fontId="12" fillId="4" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="12" fillId="4" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="200" fontId="12" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="200" fontId="12" fillId="4" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="200" fontId="12" fillId="4" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="9" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -561,7 +587,7 @@
     <x:xf numFmtId="0" fontId="9" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="14" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="9" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="9" fillId="7" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="9" fillId="7" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="9" fillId="7" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -572,34 +598,52 @@
     <x:xf numFmtId="0" fontId="9" fillId="8" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="200" fontId="12" fillId="4" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="200" fontId="12" fillId="4" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="200" fontId="12" fillId="4" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="200" fontId="12" fillId="4" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="5" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="5" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="200" fontId="12" fillId="4" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="12" fillId="6" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="200" fontId="12" fillId="4" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="12" fillId="6" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="6" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="15" fillId="6" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="15" fillId="6" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="15" fillId="6" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="12" fillId="4" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="12" fillId="4" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
   </x:cellStyles>
-  <x:dxfs count="49">
+  <x:dxfs count="56">
     <x:dxf>
       <x:font>
         <x:b/>
@@ -663,6 +707,83 @@
       <x:fill>
         <x:patternFill patternType="solid">
           <x:bgColor rgb="FFFFF1C7"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FF17623E"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFDDF4E8"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FF8A3027"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFFBE3DF"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FF7A5600"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFFFF1C7"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FF7A5600"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFFFF1C7"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FF8A3027"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFFBE3DF"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FF8A3027"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFFBE3DF"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FF8A3027"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFFBE3DF"/>
         </x:patternFill>
       </x:fill>
     </x:dxf>
@@ -1565,7 +1686,7 @@
     </x:row>
     <x:row r="25" ht="28" customHeight="1">
       <x:c r="A25" s="37" t="str">
-        <x:v>Canvas remains the authority for due dates, submission links, and course-grade weights.</x:v>
+        <x:v>Use the current phase page for work steps and approval readiness. Use the Canvas Submission Workflow for exact files and filenames; Canvas controls due dates, points, and the actual upload.</x:v>
       </x:c>
       <x:c r="B25" s="37"/>
       <x:c r="C25" s="37"/>
@@ -1641,7 +1762,7 @@
     </x:row>
     <x:row r="2" ht="24" customHeight="1">
       <x:c r="A2" s="6" t="str">
-        <x:v>Assign one student to each of five committee seats. Roles define distinct decision rights; all members share the final decision.</x:v>
+        <x:v>Assign all five roles to four or five members. A dual-role member casts one vote.</x:v>
       </x:c>
       <x:c r="B2" s="6"/>
       <x:c r="C2" s="6"/>
@@ -1830,6 +1951,85 @@
       <x:c r="D15" s="16" t="str"/>
       <x:c r="E15" s="16" t="str"/>
       <x:c r="F15" s="16" t="str"/>
+    </x:row>
+    <x:row r="17" ht="23" customHeight="1">
+      <x:c r="A17" s="11" t="str">
+        <x:v>VOTING MEMBERS — ENTER EACH PERSON ONCE</x:v>
+      </x:c>
+      <x:c r="B17" s="11"/>
+      <x:c r="C17" s="11"/>
+      <x:c r="D17" s="11"/>
+      <x:c r="E17" s="11"/>
+      <x:c r="F17" s="11"/>
+    </x:row>
+    <x:row r="18">
+      <x:c r="A18" t="str">
+        <x:v>Member 1</x:v>
+      </x:c>
+      <x:c r="B18" s="45"/>
+      <x:c r="D18" t="str">
+        <x:v>Team size (4 or 5)</x:v>
+      </x:c>
+      <x:c r="E18" s="59"/>
+    </x:row>
+    <x:row r="19">
+      <x:c r="A19" t="str">
+        <x:v>Member 2</x:v>
+      </x:c>
+      <x:c r="B19" s="46"/>
+      <x:c r="D19" t="str">
+        <x:v>Confirmed size</x:v>
+      </x:c>
+      <x:c r="E19" t="str">
+        <x:f>IF(E18="","",VALUE(E18))</x:f>
+      </x:c>
+    </x:row>
+    <x:row r="20">
+      <x:c r="A20" t="str">
+        <x:v>Member 3</x:v>
+      </x:c>
+      <x:c r="B20" s="46"/>
+      <x:c r="D20" s="9" t="str">
+        <x:v>Enter each person once at left. Assign the same person to two roles above when the team has four members. Vote names on gate sheets link to this list.</x:v>
+      </x:c>
+      <x:c r="E20" s="9"/>
+      <x:c r="F20" s="9"/>
+    </x:row>
+    <x:row r="21">
+      <x:c r="A21" t="str">
+        <x:v>Member 4</x:v>
+      </x:c>
+      <x:c r="B21" s="46"/>
+      <x:c r="D21" s="9"/>
+      <x:c r="E21" s="9"/>
+      <x:c r="F21" s="9"/>
+    </x:row>
+    <x:row r="22">
+      <x:c r="A22" t="str">
+        <x:v>Member 5 (optional)</x:v>
+      </x:c>
+      <x:c r="B22" s="47"/>
+      <x:c r="D22" s="9"/>
+      <x:c r="E22" s="9"/>
+      <x:c r="F22" s="9"/>
+    </x:row>
+    <x:row r="23">
+      <x:c r="A23" t="str">
+        <x:v>Roster status</x:v>
+      </x:c>
+      <x:c r="B23" t="str">
+        <x:f>IF(OR(E19="",AND(E19&lt;&gt;4,E19&lt;&gt;5),COUNTA(B18:B22)&lt;&gt;E19,COUNTA(B5:B9)&lt;&gt;5),"INCOMPLETE",IF(OR(AND(B18&lt;&gt;"",B18=B19),AND(B18&lt;&gt;"",B18=B20),AND(B18&lt;&gt;"",B18=B21),AND(B18&lt;&gt;"",B18=B22),AND(B19&lt;&gt;"",B19=B20),AND(B19&lt;&gt;"",B19=B21),AND(B19&lt;&gt;"",B19=B22),AND(B20&lt;&gt;"",B20=B21),AND(B20&lt;&gt;"",B20=B22),AND(B21&lt;&gt;"",B21=B22)),"DUPLICATE MEMBER",IF(B24="COVERED","READY","ROLE OWNER MISMATCH")))</x:f>
+        <x:v>INCOMPLETE</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24">
+      <x:c r="A24" t="str">
+        <x:v>Role coverage</x:v>
+      </x:c>
+      <x:c r="B24" t="str">
+        <x:f>IF(OR(E19="",COUNTA(B5:B9)&lt;&gt;5),"INCOMPLETE",IF(AND(COUNTIF(B18:B22,B5)&gt;0,COUNTIF(B18:B22,B6)&gt;0,COUNTIF(B18:B22,B7)&gt;0,COUNTIF(B18:B22,B8)&gt;0,COUNTIF(B18:B22,B9)&gt;0,COUNTIF(B5:B9,B18)&gt;0,COUNTIF(B5:B9,B19)&gt;0,COUNTIF(B5:B9,B20)&gt;0,COUNTIF(B5:B9,B21)&gt;0,IF(E19=5,COUNTIF(B5:B9,B22)&gt;0,TRUE)),"COVERED","ROLE OWNER MISMATCH"))</x:f>
+        <x:v>INCOMPLETE</x:v>
+      </x:c>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -1841,7 +2041,23 @@
     <x:mergeCell ref="B13:F13"/>
     <x:mergeCell ref="B14:F14"/>
     <x:mergeCell ref="B15:F15"/>
+    <x:mergeCell ref="A17:F17"/>
+    <x:mergeCell ref="D20:F22"/>
   </x:mergeCells>
+  <x:conditionalFormatting sqref="B23:B23">
+    <x:cfRule type="containsText" dxfId="13" priority="1" operator="containsText" text="EVIDENCE READY"/>
+    <x:cfRule type="containsText" dxfId="14" priority="2" operator="containsText" text="REVISE"/>
+    <x:cfRule type="containsText" dxfId="15" priority="3" operator="containsText" text="INCOMPLETE"/>
+    <x:cfRule type="containsText" dxfId="16" priority="4" operator="containsText" text="MINIMUM"/>
+    <x:cfRule type="containsText" dxfId="17" priority="5" operator="containsText" text="REVIEW"/>
+    <x:cfRule type="containsText" dxfId="18" priority="6" operator="containsText" text="MISSING"/>
+    <x:cfRule type="containsText" dxfId="19" priority="7" operator="containsText" text="ENTER"/>
+  </x:conditionalFormatting>
+  <x:dataValidations count="1">
+    <x:dataValidation type="list" sqref="E18">
+      <x:formula1>"4,5"</x:formula1>
+    </x:dataValidation>
+  </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
 </file>
@@ -1921,28 +2137,28 @@
       <x:c r="T2" s="6"/>
     </x:row>
     <x:row r="4" ht="30" customHeight="1">
-      <x:c r="A4" s="58" t="str">
+      <x:c r="A4" s="61" t="str">
         <x:v>Each of the five roles records at least one recommendation for each assigned client. Every material entry includes an alternative rejected and a key trade-off. Minimum Phase 1 evidence: 15 complete role-by-client entries across the team.</x:v>
       </x:c>
-      <x:c r="B4" s="58"/>
-      <x:c r="C4" s="58"/>
-      <x:c r="D4" s="58"/>
-      <x:c r="E4" s="58"/>
-      <x:c r="F4" s="58"/>
-      <x:c r="G4" s="58"/>
-      <x:c r="H4" s="58"/>
-      <x:c r="I4" s="58"/>
-      <x:c r="J4" s="58"/>
-      <x:c r="K4" s="58"/>
-      <x:c r="L4" s="58"/>
-      <x:c r="M4" s="58"/>
-      <x:c r="N4" s="58"/>
-      <x:c r="O4" s="58"/>
-      <x:c r="P4" s="58"/>
-      <x:c r="Q4" s="58"/>
-      <x:c r="R4" s="58"/>
-      <x:c r="S4" s="58"/>
-      <x:c r="T4" s="58"/>
+      <x:c r="B4" s="61"/>
+      <x:c r="C4" s="61"/>
+      <x:c r="D4" s="61"/>
+      <x:c r="E4" s="61"/>
+      <x:c r="F4" s="61"/>
+      <x:c r="G4" s="61"/>
+      <x:c r="H4" s="61"/>
+      <x:c r="I4" s="61"/>
+      <x:c r="J4" s="61"/>
+      <x:c r="K4" s="61"/>
+      <x:c r="L4" s="61"/>
+      <x:c r="M4" s="61"/>
+      <x:c r="N4" s="61"/>
+      <x:c r="O4" s="61"/>
+      <x:c r="P4" s="61"/>
+      <x:c r="Q4" s="61"/>
+      <x:c r="R4" s="61"/>
+      <x:c r="S4" s="61"/>
+      <x:c r="T4" s="61"/>
     </x:row>
     <x:row r="5" ht="30" customHeight="1">
       <x:c r="A5" s="37" t="str">
@@ -1972,23 +2188,23 @@
       <x:c r="A6" s="25" t="str">
         <x:v>Team / committee</x:v>
       </x:c>
-      <x:c r="B6" s="63" t="str"/>
-      <x:c r="C6" s="64" t="str"/>
+      <x:c r="B6" s="66" t="str"/>
+      <x:c r="C6" s="67" t="str"/>
       <x:c r="D6" s="25" t="str">
         <x:v>Assigned Client 1</x:v>
       </x:c>
-      <x:c r="E6" s="63" t="str"/>
-      <x:c r="F6" s="64" t="str"/>
+      <x:c r="E6" s="66" t="str"/>
+      <x:c r="F6" s="67" t="str"/>
       <x:c r="G6" s="25" t="str">
         <x:v>Assigned Client 2</x:v>
       </x:c>
-      <x:c r="H6" s="63" t="str"/>
-      <x:c r="I6" s="64" t="str"/>
+      <x:c r="H6" s="66" t="str"/>
+      <x:c r="I6" s="67" t="str"/>
       <x:c r="J6" s="25" t="str">
         <x:v>Assigned Client 3</x:v>
       </x:c>
-      <x:c r="K6" s="63" t="str"/>
-      <x:c r="L6" s="64" t="str"/>
+      <x:c r="K6" s="66" t="str"/>
+      <x:c r="L6" s="67" t="str"/>
     </x:row>
     <x:row r="7" ht="48" customHeight="1">
       <x:c r="A7" s="21" t="str">
@@ -2053,751 +2269,751 @@
       </x:c>
     </x:row>
     <x:row r="8" ht="66" customHeight="1">
-      <x:c r="A8" s="82"/>
-      <x:c r="B8" s="91"/>
-      <x:c r="C8" s="83"/>
-      <x:c r="D8" s="83"/>
-      <x:c r="E8" s="83"/>
-      <x:c r="F8" s="83"/>
-      <x:c r="G8" s="83"/>
-      <x:c r="H8" s="83"/>
-      <x:c r="I8" s="83"/>
-      <x:c r="J8" s="83"/>
-      <x:c r="K8" s="83"/>
-      <x:c r="L8" s="83"/>
-      <x:c r="M8" s="91"/>
-      <x:c r="N8" s="83"/>
-      <x:c r="O8" s="83"/>
-      <x:c r="P8" s="83"/>
-      <x:c r="Q8" s="83"/>
-      <x:c r="R8" s="83"/>
-      <x:c r="S8" s="84"/>
-      <x:c r="T8" s="96" t="str">
+      <x:c r="A8" s="85"/>
+      <x:c r="B8" s="94"/>
+      <x:c r="C8" s="86"/>
+      <x:c r="D8" s="86"/>
+      <x:c r="E8" s="86"/>
+      <x:c r="F8" s="86"/>
+      <x:c r="G8" s="86"/>
+      <x:c r="H8" s="86"/>
+      <x:c r="I8" s="86"/>
+      <x:c r="J8" s="86"/>
+      <x:c r="K8" s="86"/>
+      <x:c r="L8" s="86"/>
+      <x:c r="M8" s="94"/>
+      <x:c r="N8" s="86"/>
+      <x:c r="O8" s="86"/>
+      <x:c r="P8" s="86"/>
+      <x:c r="Q8" s="86"/>
+      <x:c r="R8" s="86"/>
+      <x:c r="S8" s="87"/>
+      <x:c r="T8" s="99" t="str">
         <x:f>IF(COUNTA(A8:S8)=0,"NOT STARTED",IF(OR(A8="",B8="",C8="",D8="",E8="",F8="",G8="",H8="",I8="",J8="",K8="",L8="",M8="",N8="",O8="",P8="",Q8="",R8="",S8=""),"INCOMPLETE",IF(OR(S8="Needs revision",AND(OR(N8="Contradicted",N8="Not verifiable"),S8&lt;&gt;"Cleared after revision")),"REVISE / FLAG","EVIDENCE READY")))</x:f>
         <x:v>NOT STARTED</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="66" customHeight="1">
-      <x:c r="A9" s="85"/>
-      <x:c r="B9" s="92"/>
-      <x:c r="C9" s="86"/>
-      <x:c r="D9" s="86"/>
-      <x:c r="E9" s="86"/>
-      <x:c r="F9" s="86"/>
-      <x:c r="G9" s="86"/>
-      <x:c r="H9" s="86"/>
-      <x:c r="I9" s="86"/>
-      <x:c r="J9" s="86"/>
-      <x:c r="K9" s="86"/>
-      <x:c r="L9" s="86"/>
-      <x:c r="M9" s="92"/>
-      <x:c r="N9" s="86"/>
-      <x:c r="O9" s="86"/>
-      <x:c r="P9" s="86"/>
-      <x:c r="Q9" s="86"/>
-      <x:c r="R9" s="86"/>
-      <x:c r="S9" s="87"/>
-      <x:c r="T9" s="96" t="str">
+      <x:c r="A9" s="88"/>
+      <x:c r="B9" s="95"/>
+      <x:c r="C9" s="89"/>
+      <x:c r="D9" s="89"/>
+      <x:c r="E9" s="89"/>
+      <x:c r="F9" s="89"/>
+      <x:c r="G9" s="89"/>
+      <x:c r="H9" s="89"/>
+      <x:c r="I9" s="89"/>
+      <x:c r="J9" s="89"/>
+      <x:c r="K9" s="89"/>
+      <x:c r="L9" s="89"/>
+      <x:c r="M9" s="95"/>
+      <x:c r="N9" s="89"/>
+      <x:c r="O9" s="89"/>
+      <x:c r="P9" s="89"/>
+      <x:c r="Q9" s="89"/>
+      <x:c r="R9" s="89"/>
+      <x:c r="S9" s="90"/>
+      <x:c r="T9" s="99" t="str">
         <x:f>IF(COUNTA(A9:S9)=0,"NOT STARTED",IF(OR(A9="",B9="",C9="",D9="",E9="",F9="",G9="",H9="",I9="",J9="",K9="",L9="",M9="",N9="",O9="",P9="",Q9="",R9="",S9=""),"INCOMPLETE",IF(OR(S9="Needs revision",AND(OR(N9="Contradicted",N9="Not verifiable"),S9&lt;&gt;"Cleared after revision")),"REVISE / FLAG","EVIDENCE READY")))</x:f>
         <x:v>NOT STARTED</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="66" customHeight="1">
-      <x:c r="A10" s="85"/>
-      <x:c r="B10" s="92"/>
-      <x:c r="C10" s="86"/>
-      <x:c r="D10" s="86"/>
-      <x:c r="E10" s="86"/>
-      <x:c r="F10" s="86"/>
-      <x:c r="G10" s="86"/>
-      <x:c r="H10" s="86"/>
-      <x:c r="I10" s="86"/>
-      <x:c r="J10" s="86"/>
-      <x:c r="K10" s="86"/>
-      <x:c r="L10" s="86"/>
-      <x:c r="M10" s="92"/>
-      <x:c r="N10" s="86"/>
-      <x:c r="O10" s="86"/>
-      <x:c r="P10" s="86"/>
-      <x:c r="Q10" s="86"/>
-      <x:c r="R10" s="86"/>
-      <x:c r="S10" s="87"/>
-      <x:c r="T10" s="96" t="str">
+      <x:c r="A10" s="88"/>
+      <x:c r="B10" s="95"/>
+      <x:c r="C10" s="89"/>
+      <x:c r="D10" s="89"/>
+      <x:c r="E10" s="89"/>
+      <x:c r="F10" s="89"/>
+      <x:c r="G10" s="89"/>
+      <x:c r="H10" s="89"/>
+      <x:c r="I10" s="89"/>
+      <x:c r="J10" s="89"/>
+      <x:c r="K10" s="89"/>
+      <x:c r="L10" s="89"/>
+      <x:c r="M10" s="95"/>
+      <x:c r="N10" s="89"/>
+      <x:c r="O10" s="89"/>
+      <x:c r="P10" s="89"/>
+      <x:c r="Q10" s="89"/>
+      <x:c r="R10" s="89"/>
+      <x:c r="S10" s="90"/>
+      <x:c r="T10" s="99" t="str">
         <x:f>IF(COUNTA(A10:S10)=0,"NOT STARTED",IF(OR(A10="",B10="",C10="",D10="",E10="",F10="",G10="",H10="",I10="",J10="",K10="",L10="",M10="",N10="",O10="",P10="",Q10="",R10="",S10=""),"INCOMPLETE",IF(OR(S10="Needs revision",AND(OR(N10="Contradicted",N10="Not verifiable"),S10&lt;&gt;"Cleared after revision")),"REVISE / FLAG","EVIDENCE READY")))</x:f>
         <x:v>NOT STARTED</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="66" customHeight="1">
-      <x:c r="A11" s="85"/>
-      <x:c r="B11" s="92"/>
-      <x:c r="C11" s="86"/>
-      <x:c r="D11" s="86"/>
-      <x:c r="E11" s="86"/>
-      <x:c r="F11" s="86"/>
-      <x:c r="G11" s="86"/>
-      <x:c r="H11" s="86"/>
-      <x:c r="I11" s="86"/>
-      <x:c r="J11" s="86"/>
-      <x:c r="K11" s="86"/>
-      <x:c r="L11" s="86"/>
-      <x:c r="M11" s="92"/>
-      <x:c r="N11" s="86"/>
-      <x:c r="O11" s="86"/>
-      <x:c r="P11" s="86"/>
-      <x:c r="Q11" s="86"/>
-      <x:c r="R11" s="86"/>
-      <x:c r="S11" s="87"/>
-      <x:c r="T11" s="96" t="str">
+      <x:c r="A11" s="88"/>
+      <x:c r="B11" s="95"/>
+      <x:c r="C11" s="89"/>
+      <x:c r="D11" s="89"/>
+      <x:c r="E11" s="89"/>
+      <x:c r="F11" s="89"/>
+      <x:c r="G11" s="89"/>
+      <x:c r="H11" s="89"/>
+      <x:c r="I11" s="89"/>
+      <x:c r="J11" s="89"/>
+      <x:c r="K11" s="89"/>
+      <x:c r="L11" s="89"/>
+      <x:c r="M11" s="95"/>
+      <x:c r="N11" s="89"/>
+      <x:c r="O11" s="89"/>
+      <x:c r="P11" s="89"/>
+      <x:c r="Q11" s="89"/>
+      <x:c r="R11" s="89"/>
+      <x:c r="S11" s="90"/>
+      <x:c r="T11" s="99" t="str">
         <x:f>IF(COUNTA(A11:S11)=0,"NOT STARTED",IF(OR(A11="",B11="",C11="",D11="",E11="",F11="",G11="",H11="",I11="",J11="",K11="",L11="",M11="",N11="",O11="",P11="",Q11="",R11="",S11=""),"INCOMPLETE",IF(OR(S11="Needs revision",AND(OR(N11="Contradicted",N11="Not verifiable"),S11&lt;&gt;"Cleared after revision")),"REVISE / FLAG","EVIDENCE READY")))</x:f>
         <x:v>NOT STARTED</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="66" customHeight="1">
-      <x:c r="A12" s="85"/>
-      <x:c r="B12" s="92"/>
-      <x:c r="C12" s="86"/>
-      <x:c r="D12" s="86"/>
-      <x:c r="E12" s="86"/>
-      <x:c r="F12" s="86"/>
-      <x:c r="G12" s="86"/>
-      <x:c r="H12" s="86"/>
-      <x:c r="I12" s="86"/>
-      <x:c r="J12" s="86"/>
-      <x:c r="K12" s="86"/>
-      <x:c r="L12" s="86"/>
-      <x:c r="M12" s="92"/>
-      <x:c r="N12" s="86"/>
-      <x:c r="O12" s="86"/>
-      <x:c r="P12" s="86"/>
-      <x:c r="Q12" s="86"/>
-      <x:c r="R12" s="86"/>
-      <x:c r="S12" s="87"/>
-      <x:c r="T12" s="96" t="str">
+      <x:c r="A12" s="88"/>
+      <x:c r="B12" s="95"/>
+      <x:c r="C12" s="89"/>
+      <x:c r="D12" s="89"/>
+      <x:c r="E12" s="89"/>
+      <x:c r="F12" s="89"/>
+      <x:c r="G12" s="89"/>
+      <x:c r="H12" s="89"/>
+      <x:c r="I12" s="89"/>
+      <x:c r="J12" s="89"/>
+      <x:c r="K12" s="89"/>
+      <x:c r="L12" s="89"/>
+      <x:c r="M12" s="95"/>
+      <x:c r="N12" s="89"/>
+      <x:c r="O12" s="89"/>
+      <x:c r="P12" s="89"/>
+      <x:c r="Q12" s="89"/>
+      <x:c r="R12" s="89"/>
+      <x:c r="S12" s="90"/>
+      <x:c r="T12" s="99" t="str">
         <x:f>IF(COUNTA(A12:S12)=0,"NOT STARTED",IF(OR(A12="",B12="",C12="",D12="",E12="",F12="",G12="",H12="",I12="",J12="",K12="",L12="",M12="",N12="",O12="",P12="",Q12="",R12="",S12=""),"INCOMPLETE",IF(OR(S12="Needs revision",AND(OR(N12="Contradicted",N12="Not verifiable"),S12&lt;&gt;"Cleared after revision")),"REVISE / FLAG","EVIDENCE READY")))</x:f>
         <x:v>NOT STARTED</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="66" customHeight="1">
-      <x:c r="A13" s="85"/>
-      <x:c r="B13" s="92"/>
-      <x:c r="C13" s="86"/>
-      <x:c r="D13" s="86"/>
-      <x:c r="E13" s="86"/>
-      <x:c r="F13" s="86"/>
-      <x:c r="G13" s="86"/>
-      <x:c r="H13" s="86"/>
-      <x:c r="I13" s="86"/>
-      <x:c r="J13" s="86"/>
-      <x:c r="K13" s="86"/>
-      <x:c r="L13" s="86"/>
-      <x:c r="M13" s="92"/>
-      <x:c r="N13" s="86"/>
-      <x:c r="O13" s="86"/>
-      <x:c r="P13" s="86"/>
-      <x:c r="Q13" s="86"/>
-      <x:c r="R13" s="86"/>
-      <x:c r="S13" s="87"/>
-      <x:c r="T13" s="96" t="str">
+      <x:c r="A13" s="88"/>
+      <x:c r="B13" s="95"/>
+      <x:c r="C13" s="89"/>
+      <x:c r="D13" s="89"/>
+      <x:c r="E13" s="89"/>
+      <x:c r="F13" s="89"/>
+      <x:c r="G13" s="89"/>
+      <x:c r="H13" s="89"/>
+      <x:c r="I13" s="89"/>
+      <x:c r="J13" s="89"/>
+      <x:c r="K13" s="89"/>
+      <x:c r="L13" s="89"/>
+      <x:c r="M13" s="95"/>
+      <x:c r="N13" s="89"/>
+      <x:c r="O13" s="89"/>
+      <x:c r="P13" s="89"/>
+      <x:c r="Q13" s="89"/>
+      <x:c r="R13" s="89"/>
+      <x:c r="S13" s="90"/>
+      <x:c r="T13" s="99" t="str">
         <x:f>IF(COUNTA(A13:S13)=0,"NOT STARTED",IF(OR(A13="",B13="",C13="",D13="",E13="",F13="",G13="",H13="",I13="",J13="",K13="",L13="",M13="",N13="",O13="",P13="",Q13="",R13="",S13=""),"INCOMPLETE",IF(OR(S13="Needs revision",AND(OR(N13="Contradicted",N13="Not verifiable"),S13&lt;&gt;"Cleared after revision")),"REVISE / FLAG","EVIDENCE READY")))</x:f>
         <x:v>NOT STARTED</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="66" customHeight="1">
-      <x:c r="A14" s="85"/>
-      <x:c r="B14" s="92"/>
-      <x:c r="C14" s="86"/>
-      <x:c r="D14" s="86"/>
-      <x:c r="E14" s="86"/>
-      <x:c r="F14" s="86"/>
-      <x:c r="G14" s="86"/>
-      <x:c r="H14" s="86"/>
-      <x:c r="I14" s="86"/>
-      <x:c r="J14" s="86"/>
-      <x:c r="K14" s="86"/>
-      <x:c r="L14" s="86"/>
-      <x:c r="M14" s="92"/>
-      <x:c r="N14" s="86"/>
-      <x:c r="O14" s="86"/>
-      <x:c r="P14" s="86"/>
-      <x:c r="Q14" s="86"/>
-      <x:c r="R14" s="86"/>
-      <x:c r="S14" s="87"/>
-      <x:c r="T14" s="96" t="str">
+      <x:c r="A14" s="88"/>
+      <x:c r="B14" s="95"/>
+      <x:c r="C14" s="89"/>
+      <x:c r="D14" s="89"/>
+      <x:c r="E14" s="89"/>
+      <x:c r="F14" s="89"/>
+      <x:c r="G14" s="89"/>
+      <x:c r="H14" s="89"/>
+      <x:c r="I14" s="89"/>
+      <x:c r="J14" s="89"/>
+      <x:c r="K14" s="89"/>
+      <x:c r="L14" s="89"/>
+      <x:c r="M14" s="95"/>
+      <x:c r="N14" s="89"/>
+      <x:c r="O14" s="89"/>
+      <x:c r="P14" s="89"/>
+      <x:c r="Q14" s="89"/>
+      <x:c r="R14" s="89"/>
+      <x:c r="S14" s="90"/>
+      <x:c r="T14" s="99" t="str">
         <x:f>IF(COUNTA(A14:S14)=0,"NOT STARTED",IF(OR(A14="",B14="",C14="",D14="",E14="",F14="",G14="",H14="",I14="",J14="",K14="",L14="",M14="",N14="",O14="",P14="",Q14="",R14="",S14=""),"INCOMPLETE",IF(OR(S14="Needs revision",AND(OR(N14="Contradicted",N14="Not verifiable"),S14&lt;&gt;"Cleared after revision")),"REVISE / FLAG","EVIDENCE READY")))</x:f>
         <x:v>NOT STARTED</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="66" customHeight="1">
-      <x:c r="A15" s="85"/>
-      <x:c r="B15" s="92"/>
-      <x:c r="C15" s="86"/>
-      <x:c r="D15" s="86"/>
-      <x:c r="E15" s="86"/>
-      <x:c r="F15" s="86"/>
-      <x:c r="G15" s="86"/>
-      <x:c r="H15" s="86"/>
-      <x:c r="I15" s="86"/>
-      <x:c r="J15" s="86"/>
-      <x:c r="K15" s="86"/>
-      <x:c r="L15" s="86"/>
-      <x:c r="M15" s="92"/>
-      <x:c r="N15" s="86"/>
-      <x:c r="O15" s="86"/>
-      <x:c r="P15" s="86"/>
-      <x:c r="Q15" s="86"/>
-      <x:c r="R15" s="86"/>
-      <x:c r="S15" s="87"/>
-      <x:c r="T15" s="96" t="str">
+      <x:c r="A15" s="88"/>
+      <x:c r="B15" s="95"/>
+      <x:c r="C15" s="89"/>
+      <x:c r="D15" s="89"/>
+      <x:c r="E15" s="89"/>
+      <x:c r="F15" s="89"/>
+      <x:c r="G15" s="89"/>
+      <x:c r="H15" s="89"/>
+      <x:c r="I15" s="89"/>
+      <x:c r="J15" s="89"/>
+      <x:c r="K15" s="89"/>
+      <x:c r="L15" s="89"/>
+      <x:c r="M15" s="95"/>
+      <x:c r="N15" s="89"/>
+      <x:c r="O15" s="89"/>
+      <x:c r="P15" s="89"/>
+      <x:c r="Q15" s="89"/>
+      <x:c r="R15" s="89"/>
+      <x:c r="S15" s="90"/>
+      <x:c r="T15" s="99" t="str">
         <x:f>IF(COUNTA(A15:S15)=0,"NOT STARTED",IF(OR(A15="",B15="",C15="",D15="",E15="",F15="",G15="",H15="",I15="",J15="",K15="",L15="",M15="",N15="",O15="",P15="",Q15="",R15="",S15=""),"INCOMPLETE",IF(OR(S15="Needs revision",AND(OR(N15="Contradicted",N15="Not verifiable"),S15&lt;&gt;"Cleared after revision")),"REVISE / FLAG","EVIDENCE READY")))</x:f>
         <x:v>NOT STARTED</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="66" customHeight="1">
-      <x:c r="A16" s="85"/>
-      <x:c r="B16" s="92"/>
-      <x:c r="C16" s="86"/>
-      <x:c r="D16" s="86"/>
-      <x:c r="E16" s="86"/>
-      <x:c r="F16" s="86"/>
-      <x:c r="G16" s="86"/>
-      <x:c r="H16" s="86"/>
-      <x:c r="I16" s="86"/>
-      <x:c r="J16" s="86"/>
-      <x:c r="K16" s="86"/>
-      <x:c r="L16" s="86"/>
-      <x:c r="M16" s="92"/>
-      <x:c r="N16" s="86"/>
-      <x:c r="O16" s="86"/>
-      <x:c r="P16" s="86"/>
-      <x:c r="Q16" s="86"/>
-      <x:c r="R16" s="86"/>
-      <x:c r="S16" s="87"/>
-      <x:c r="T16" s="96" t="str">
+      <x:c r="A16" s="88"/>
+      <x:c r="B16" s="95"/>
+      <x:c r="C16" s="89"/>
+      <x:c r="D16" s="89"/>
+      <x:c r="E16" s="89"/>
+      <x:c r="F16" s="89"/>
+      <x:c r="G16" s="89"/>
+      <x:c r="H16" s="89"/>
+      <x:c r="I16" s="89"/>
+      <x:c r="J16" s="89"/>
+      <x:c r="K16" s="89"/>
+      <x:c r="L16" s="89"/>
+      <x:c r="M16" s="95"/>
+      <x:c r="N16" s="89"/>
+      <x:c r="O16" s="89"/>
+      <x:c r="P16" s="89"/>
+      <x:c r="Q16" s="89"/>
+      <x:c r="R16" s="89"/>
+      <x:c r="S16" s="90"/>
+      <x:c r="T16" s="99" t="str">
         <x:f>IF(COUNTA(A16:S16)=0,"NOT STARTED",IF(OR(A16="",B16="",C16="",D16="",E16="",F16="",G16="",H16="",I16="",J16="",K16="",L16="",M16="",N16="",O16="",P16="",Q16="",R16="",S16=""),"INCOMPLETE",IF(OR(S16="Needs revision",AND(OR(N16="Contradicted",N16="Not verifiable"),S16&lt;&gt;"Cleared after revision")),"REVISE / FLAG","EVIDENCE READY")))</x:f>
         <x:v>NOT STARTED</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="66" customHeight="1">
-      <x:c r="A17" s="85"/>
-      <x:c r="B17" s="92"/>
-      <x:c r="C17" s="86"/>
-      <x:c r="D17" s="86"/>
-      <x:c r="E17" s="86"/>
-      <x:c r="F17" s="86"/>
-      <x:c r="G17" s="86"/>
-      <x:c r="H17" s="86"/>
-      <x:c r="I17" s="86"/>
-      <x:c r="J17" s="86"/>
-      <x:c r="K17" s="86"/>
-      <x:c r="L17" s="86"/>
-      <x:c r="M17" s="92"/>
-      <x:c r="N17" s="86"/>
-      <x:c r="O17" s="86"/>
-      <x:c r="P17" s="86"/>
-      <x:c r="Q17" s="86"/>
-      <x:c r="R17" s="86"/>
-      <x:c r="S17" s="87"/>
-      <x:c r="T17" s="96" t="str">
+      <x:c r="A17" s="88"/>
+      <x:c r="B17" s="95"/>
+      <x:c r="C17" s="89"/>
+      <x:c r="D17" s="89"/>
+      <x:c r="E17" s="89"/>
+      <x:c r="F17" s="89"/>
+      <x:c r="G17" s="89"/>
+      <x:c r="H17" s="89"/>
+      <x:c r="I17" s="89"/>
+      <x:c r="J17" s="89"/>
+      <x:c r="K17" s="89"/>
+      <x:c r="L17" s="89"/>
+      <x:c r="M17" s="95"/>
+      <x:c r="N17" s="89"/>
+      <x:c r="O17" s="89"/>
+      <x:c r="P17" s="89"/>
+      <x:c r="Q17" s="89"/>
+      <x:c r="R17" s="89"/>
+      <x:c r="S17" s="90"/>
+      <x:c r="T17" s="99" t="str">
         <x:f>IF(COUNTA(A17:S17)=0,"NOT STARTED",IF(OR(A17="",B17="",C17="",D17="",E17="",F17="",G17="",H17="",I17="",J17="",K17="",L17="",M17="",N17="",O17="",P17="",Q17="",R17="",S17=""),"INCOMPLETE",IF(OR(S17="Needs revision",AND(OR(N17="Contradicted",N17="Not verifiable"),S17&lt;&gt;"Cleared after revision")),"REVISE / FLAG","EVIDENCE READY")))</x:f>
         <x:v>NOT STARTED</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="66" customHeight="1">
-      <x:c r="A18" s="85"/>
-      <x:c r="B18" s="92"/>
-      <x:c r="C18" s="86"/>
-      <x:c r="D18" s="86"/>
-      <x:c r="E18" s="86"/>
-      <x:c r="F18" s="86"/>
-      <x:c r="G18" s="86"/>
-      <x:c r="H18" s="86"/>
-      <x:c r="I18" s="86"/>
-      <x:c r="J18" s="86"/>
-      <x:c r="K18" s="86"/>
-      <x:c r="L18" s="86"/>
-      <x:c r="M18" s="92"/>
-      <x:c r="N18" s="86"/>
-      <x:c r="O18" s="86"/>
-      <x:c r="P18" s="86"/>
-      <x:c r="Q18" s="86"/>
-      <x:c r="R18" s="86"/>
-      <x:c r="S18" s="87"/>
-      <x:c r="T18" s="96" t="str">
+      <x:c r="A18" s="88"/>
+      <x:c r="B18" s="95"/>
+      <x:c r="C18" s="89"/>
+      <x:c r="D18" s="89"/>
+      <x:c r="E18" s="89"/>
+      <x:c r="F18" s="89"/>
+      <x:c r="G18" s="89"/>
+      <x:c r="H18" s="89"/>
+      <x:c r="I18" s="89"/>
+      <x:c r="J18" s="89"/>
+      <x:c r="K18" s="89"/>
+      <x:c r="L18" s="89"/>
+      <x:c r="M18" s="95"/>
+      <x:c r="N18" s="89"/>
+      <x:c r="O18" s="89"/>
+      <x:c r="P18" s="89"/>
+      <x:c r="Q18" s="89"/>
+      <x:c r="R18" s="89"/>
+      <x:c r="S18" s="90"/>
+      <x:c r="T18" s="99" t="str">
         <x:f>IF(COUNTA(A18:S18)=0,"NOT STARTED",IF(OR(A18="",B18="",C18="",D18="",E18="",F18="",G18="",H18="",I18="",J18="",K18="",L18="",M18="",N18="",O18="",P18="",Q18="",R18="",S18=""),"INCOMPLETE",IF(OR(S18="Needs revision",AND(OR(N18="Contradicted",N18="Not verifiable"),S18&lt;&gt;"Cleared after revision")),"REVISE / FLAG","EVIDENCE READY")))</x:f>
         <x:v>NOT STARTED</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="66" customHeight="1">
-      <x:c r="A19" s="85"/>
-      <x:c r="B19" s="92"/>
-      <x:c r="C19" s="86"/>
-      <x:c r="D19" s="86"/>
-      <x:c r="E19" s="86"/>
-      <x:c r="F19" s="86"/>
-      <x:c r="G19" s="86"/>
-      <x:c r="H19" s="86"/>
-      <x:c r="I19" s="86"/>
-      <x:c r="J19" s="86"/>
-      <x:c r="K19" s="86"/>
-      <x:c r="L19" s="86"/>
-      <x:c r="M19" s="92"/>
-      <x:c r="N19" s="86"/>
-      <x:c r="O19" s="86"/>
-      <x:c r="P19" s="86"/>
-      <x:c r="Q19" s="86"/>
-      <x:c r="R19" s="86"/>
-      <x:c r="S19" s="87"/>
-      <x:c r="T19" s="96" t="str">
+      <x:c r="A19" s="88"/>
+      <x:c r="B19" s="95"/>
+      <x:c r="C19" s="89"/>
+      <x:c r="D19" s="89"/>
+      <x:c r="E19" s="89"/>
+      <x:c r="F19" s="89"/>
+      <x:c r="G19" s="89"/>
+      <x:c r="H19" s="89"/>
+      <x:c r="I19" s="89"/>
+      <x:c r="J19" s="89"/>
+      <x:c r="K19" s="89"/>
+      <x:c r="L19" s="89"/>
+      <x:c r="M19" s="95"/>
+      <x:c r="N19" s="89"/>
+      <x:c r="O19" s="89"/>
+      <x:c r="P19" s="89"/>
+      <x:c r="Q19" s="89"/>
+      <x:c r="R19" s="89"/>
+      <x:c r="S19" s="90"/>
+      <x:c r="T19" s="99" t="str">
         <x:f>IF(COUNTA(A19:S19)=0,"NOT STARTED",IF(OR(A19="",B19="",C19="",D19="",E19="",F19="",G19="",H19="",I19="",J19="",K19="",L19="",M19="",N19="",O19="",P19="",Q19="",R19="",S19=""),"INCOMPLETE",IF(OR(S19="Needs revision",AND(OR(N19="Contradicted",N19="Not verifiable"),S19&lt;&gt;"Cleared after revision")),"REVISE / FLAG","EVIDENCE READY")))</x:f>
         <x:v>NOT STARTED</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="66" customHeight="1">
-      <x:c r="A20" s="85"/>
-      <x:c r="B20" s="92"/>
-      <x:c r="C20" s="86"/>
-      <x:c r="D20" s="86"/>
-      <x:c r="E20" s="86"/>
-      <x:c r="F20" s="86"/>
-      <x:c r="G20" s="86"/>
-      <x:c r="H20" s="86"/>
-      <x:c r="I20" s="86"/>
-      <x:c r="J20" s="86"/>
-      <x:c r="K20" s="86"/>
-      <x:c r="L20" s="86"/>
-      <x:c r="M20" s="92"/>
-      <x:c r="N20" s="86"/>
-      <x:c r="O20" s="86"/>
-      <x:c r="P20" s="86"/>
-      <x:c r="Q20" s="86"/>
-      <x:c r="R20" s="86"/>
-      <x:c r="S20" s="87"/>
-      <x:c r="T20" s="96" t="str">
+      <x:c r="A20" s="88"/>
+      <x:c r="B20" s="95"/>
+      <x:c r="C20" s="89"/>
+      <x:c r="D20" s="89"/>
+      <x:c r="E20" s="89"/>
+      <x:c r="F20" s="89"/>
+      <x:c r="G20" s="89"/>
+      <x:c r="H20" s="89"/>
+      <x:c r="I20" s="89"/>
+      <x:c r="J20" s="89"/>
+      <x:c r="K20" s="89"/>
+      <x:c r="L20" s="89"/>
+      <x:c r="M20" s="95"/>
+      <x:c r="N20" s="89"/>
+      <x:c r="O20" s="89"/>
+      <x:c r="P20" s="89"/>
+      <x:c r="Q20" s="89"/>
+      <x:c r="R20" s="89"/>
+      <x:c r="S20" s="90"/>
+      <x:c r="T20" s="99" t="str">
         <x:f>IF(COUNTA(A20:S20)=0,"NOT STARTED",IF(OR(A20="",B20="",C20="",D20="",E20="",F20="",G20="",H20="",I20="",J20="",K20="",L20="",M20="",N20="",O20="",P20="",Q20="",R20="",S20=""),"INCOMPLETE",IF(OR(S20="Needs revision",AND(OR(N20="Contradicted",N20="Not verifiable"),S20&lt;&gt;"Cleared after revision")),"REVISE / FLAG","EVIDENCE READY")))</x:f>
         <x:v>NOT STARTED</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="66" customHeight="1">
-      <x:c r="A21" s="85"/>
-      <x:c r="B21" s="92"/>
-      <x:c r="C21" s="86"/>
-      <x:c r="D21" s="86"/>
-      <x:c r="E21" s="86"/>
-      <x:c r="F21" s="86"/>
-      <x:c r="G21" s="86"/>
-      <x:c r="H21" s="86"/>
-      <x:c r="I21" s="86"/>
-      <x:c r="J21" s="86"/>
-      <x:c r="K21" s="86"/>
-      <x:c r="L21" s="86"/>
-      <x:c r="M21" s="92"/>
-      <x:c r="N21" s="86"/>
-      <x:c r="O21" s="86"/>
-      <x:c r="P21" s="86"/>
-      <x:c r="Q21" s="86"/>
-      <x:c r="R21" s="86"/>
-      <x:c r="S21" s="87"/>
-      <x:c r="T21" s="96" t="str">
+      <x:c r="A21" s="88"/>
+      <x:c r="B21" s="95"/>
+      <x:c r="C21" s="89"/>
+      <x:c r="D21" s="89"/>
+      <x:c r="E21" s="89"/>
+      <x:c r="F21" s="89"/>
+      <x:c r="G21" s="89"/>
+      <x:c r="H21" s="89"/>
+      <x:c r="I21" s="89"/>
+      <x:c r="J21" s="89"/>
+      <x:c r="K21" s="89"/>
+      <x:c r="L21" s="89"/>
+      <x:c r="M21" s="95"/>
+      <x:c r="N21" s="89"/>
+      <x:c r="O21" s="89"/>
+      <x:c r="P21" s="89"/>
+      <x:c r="Q21" s="89"/>
+      <x:c r="R21" s="89"/>
+      <x:c r="S21" s="90"/>
+      <x:c r="T21" s="99" t="str">
         <x:f>IF(COUNTA(A21:S21)=0,"NOT STARTED",IF(OR(A21="",B21="",C21="",D21="",E21="",F21="",G21="",H21="",I21="",J21="",K21="",L21="",M21="",N21="",O21="",P21="",Q21="",R21="",S21=""),"INCOMPLETE",IF(OR(S21="Needs revision",AND(OR(N21="Contradicted",N21="Not verifiable"),S21&lt;&gt;"Cleared after revision")),"REVISE / FLAG","EVIDENCE READY")))</x:f>
         <x:v>NOT STARTED</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="66" customHeight="1">
-      <x:c r="A22" s="85"/>
-      <x:c r="B22" s="92"/>
-      <x:c r="C22" s="86"/>
-      <x:c r="D22" s="86"/>
-      <x:c r="E22" s="86"/>
-      <x:c r="F22" s="86"/>
-      <x:c r="G22" s="86"/>
-      <x:c r="H22" s="86"/>
-      <x:c r="I22" s="86"/>
-      <x:c r="J22" s="86"/>
-      <x:c r="K22" s="86"/>
-      <x:c r="L22" s="86"/>
-      <x:c r="M22" s="92"/>
-      <x:c r="N22" s="86"/>
-      <x:c r="O22" s="86"/>
-      <x:c r="P22" s="86"/>
-      <x:c r="Q22" s="86"/>
-      <x:c r="R22" s="86"/>
-      <x:c r="S22" s="87"/>
-      <x:c r="T22" s="96" t="str">
+      <x:c r="A22" s="88"/>
+      <x:c r="B22" s="95"/>
+      <x:c r="C22" s="89"/>
+      <x:c r="D22" s="89"/>
+      <x:c r="E22" s="89"/>
+      <x:c r="F22" s="89"/>
+      <x:c r="G22" s="89"/>
+      <x:c r="H22" s="89"/>
+      <x:c r="I22" s="89"/>
+      <x:c r="J22" s="89"/>
+      <x:c r="K22" s="89"/>
+      <x:c r="L22" s="89"/>
+      <x:c r="M22" s="95"/>
+      <x:c r="N22" s="89"/>
+      <x:c r="O22" s="89"/>
+      <x:c r="P22" s="89"/>
+      <x:c r="Q22" s="89"/>
+      <x:c r="R22" s="89"/>
+      <x:c r="S22" s="90"/>
+      <x:c r="T22" s="99" t="str">
         <x:f>IF(COUNTA(A22:S22)=0,"NOT STARTED",IF(OR(A22="",B22="",C22="",D22="",E22="",F22="",G22="",H22="",I22="",J22="",K22="",L22="",M22="",N22="",O22="",P22="",Q22="",R22="",S22=""),"INCOMPLETE",IF(OR(S22="Needs revision",AND(OR(N22="Contradicted",N22="Not verifiable"),S22&lt;&gt;"Cleared after revision")),"REVISE / FLAG","EVIDENCE READY")))</x:f>
         <x:v>NOT STARTED</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="66" customHeight="1">
-      <x:c r="A23" s="85"/>
-      <x:c r="B23" s="92"/>
-      <x:c r="C23" s="86"/>
-      <x:c r="D23" s="86"/>
-      <x:c r="E23" s="86"/>
-      <x:c r="F23" s="86"/>
-      <x:c r="G23" s="86"/>
-      <x:c r="H23" s="86"/>
-      <x:c r="I23" s="86"/>
-      <x:c r="J23" s="86"/>
-      <x:c r="K23" s="86"/>
-      <x:c r="L23" s="86"/>
-      <x:c r="M23" s="92"/>
-      <x:c r="N23" s="86"/>
-      <x:c r="O23" s="86"/>
-      <x:c r="P23" s="86"/>
-      <x:c r="Q23" s="86"/>
-      <x:c r="R23" s="86"/>
-      <x:c r="S23" s="87"/>
-      <x:c r="T23" s="96" t="str">
+      <x:c r="A23" s="88"/>
+      <x:c r="B23" s="95"/>
+      <x:c r="C23" s="89"/>
+      <x:c r="D23" s="89"/>
+      <x:c r="E23" s="89"/>
+      <x:c r="F23" s="89"/>
+      <x:c r="G23" s="89"/>
+      <x:c r="H23" s="89"/>
+      <x:c r="I23" s="89"/>
+      <x:c r="J23" s="89"/>
+      <x:c r="K23" s="89"/>
+      <x:c r="L23" s="89"/>
+      <x:c r="M23" s="95"/>
+      <x:c r="N23" s="89"/>
+      <x:c r="O23" s="89"/>
+      <x:c r="P23" s="89"/>
+      <x:c r="Q23" s="89"/>
+      <x:c r="R23" s="89"/>
+      <x:c r="S23" s="90"/>
+      <x:c r="T23" s="99" t="str">
         <x:f>IF(COUNTA(A23:S23)=0,"NOT STARTED",IF(OR(A23="",B23="",C23="",D23="",E23="",F23="",G23="",H23="",I23="",J23="",K23="",L23="",M23="",N23="",O23="",P23="",Q23="",R23="",S23=""),"INCOMPLETE",IF(OR(S23="Needs revision",AND(OR(N23="Contradicted",N23="Not verifiable"),S23&lt;&gt;"Cleared after revision")),"REVISE / FLAG","EVIDENCE READY")))</x:f>
         <x:v>NOT STARTED</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="66" customHeight="1">
-      <x:c r="A24" s="85"/>
-      <x:c r="B24" s="92"/>
-      <x:c r="C24" s="86"/>
-      <x:c r="D24" s="86"/>
-      <x:c r="E24" s="86"/>
-      <x:c r="F24" s="86"/>
-      <x:c r="G24" s="86"/>
-      <x:c r="H24" s="86"/>
-      <x:c r="I24" s="86"/>
-      <x:c r="J24" s="86"/>
-      <x:c r="K24" s="86"/>
-      <x:c r="L24" s="86"/>
-      <x:c r="M24" s="92"/>
-      <x:c r="N24" s="86"/>
-      <x:c r="O24" s="86"/>
-      <x:c r="P24" s="86"/>
-      <x:c r="Q24" s="86"/>
-      <x:c r="R24" s="86"/>
-      <x:c r="S24" s="87"/>
-      <x:c r="T24" s="96" t="str">
+      <x:c r="A24" s="88"/>
+      <x:c r="B24" s="95"/>
+      <x:c r="C24" s="89"/>
+      <x:c r="D24" s="89"/>
+      <x:c r="E24" s="89"/>
+      <x:c r="F24" s="89"/>
+      <x:c r="G24" s="89"/>
+      <x:c r="H24" s="89"/>
+      <x:c r="I24" s="89"/>
+      <x:c r="J24" s="89"/>
+      <x:c r="K24" s="89"/>
+      <x:c r="L24" s="89"/>
+      <x:c r="M24" s="95"/>
+      <x:c r="N24" s="89"/>
+      <x:c r="O24" s="89"/>
+      <x:c r="P24" s="89"/>
+      <x:c r="Q24" s="89"/>
+      <x:c r="R24" s="89"/>
+      <x:c r="S24" s="90"/>
+      <x:c r="T24" s="99" t="str">
         <x:f>IF(COUNTA(A24:S24)=0,"NOT STARTED",IF(OR(A24="",B24="",C24="",D24="",E24="",F24="",G24="",H24="",I24="",J24="",K24="",L24="",M24="",N24="",O24="",P24="",Q24="",R24="",S24=""),"INCOMPLETE",IF(OR(S24="Needs revision",AND(OR(N24="Contradicted",N24="Not verifiable"),S24&lt;&gt;"Cleared after revision")),"REVISE / FLAG","EVIDENCE READY")))</x:f>
         <x:v>NOT STARTED</x:v>
       </x:c>
     </x:row>
     <x:row r="25" ht="66" customHeight="1">
-      <x:c r="A25" s="85"/>
-      <x:c r="B25" s="92"/>
-      <x:c r="C25" s="86"/>
-      <x:c r="D25" s="86"/>
-      <x:c r="E25" s="86"/>
-      <x:c r="F25" s="86"/>
-      <x:c r="G25" s="86"/>
-      <x:c r="H25" s="86"/>
-      <x:c r="I25" s="86"/>
-      <x:c r="J25" s="86"/>
-      <x:c r="K25" s="86"/>
-      <x:c r="L25" s="86"/>
-      <x:c r="M25" s="92"/>
-      <x:c r="N25" s="86"/>
-      <x:c r="O25" s="86"/>
-      <x:c r="P25" s="86"/>
-      <x:c r="Q25" s="86"/>
-      <x:c r="R25" s="86"/>
-      <x:c r="S25" s="87"/>
-      <x:c r="T25" s="96" t="str">
+      <x:c r="A25" s="88"/>
+      <x:c r="B25" s="95"/>
+      <x:c r="C25" s="89"/>
+      <x:c r="D25" s="89"/>
+      <x:c r="E25" s="89"/>
+      <x:c r="F25" s="89"/>
+      <x:c r="G25" s="89"/>
+      <x:c r="H25" s="89"/>
+      <x:c r="I25" s="89"/>
+      <x:c r="J25" s="89"/>
+      <x:c r="K25" s="89"/>
+      <x:c r="L25" s="89"/>
+      <x:c r="M25" s="95"/>
+      <x:c r="N25" s="89"/>
+      <x:c r="O25" s="89"/>
+      <x:c r="P25" s="89"/>
+      <x:c r="Q25" s="89"/>
+      <x:c r="R25" s="89"/>
+      <x:c r="S25" s="90"/>
+      <x:c r="T25" s="99" t="str">
         <x:f>IF(COUNTA(A25:S25)=0,"NOT STARTED",IF(OR(A25="",B25="",C25="",D25="",E25="",F25="",G25="",H25="",I25="",J25="",K25="",L25="",M25="",N25="",O25="",P25="",Q25="",R25="",S25=""),"INCOMPLETE",IF(OR(S25="Needs revision",AND(OR(N25="Contradicted",N25="Not verifiable"),S25&lt;&gt;"Cleared after revision")),"REVISE / FLAG","EVIDENCE READY")))</x:f>
         <x:v>NOT STARTED</x:v>
       </x:c>
     </x:row>
     <x:row r="26" ht="66" customHeight="1">
-      <x:c r="A26" s="85"/>
-      <x:c r="B26" s="92"/>
-      <x:c r="C26" s="86"/>
-      <x:c r="D26" s="86"/>
-      <x:c r="E26" s="86"/>
-      <x:c r="F26" s="86"/>
-      <x:c r="G26" s="86"/>
-      <x:c r="H26" s="86"/>
-      <x:c r="I26" s="86"/>
-      <x:c r="J26" s="86"/>
-      <x:c r="K26" s="86"/>
-      <x:c r="L26" s="86"/>
-      <x:c r="M26" s="92"/>
-      <x:c r="N26" s="86"/>
-      <x:c r="O26" s="86"/>
-      <x:c r="P26" s="86"/>
-      <x:c r="Q26" s="86"/>
-      <x:c r="R26" s="86"/>
-      <x:c r="S26" s="87"/>
-      <x:c r="T26" s="96" t="str">
+      <x:c r="A26" s="88"/>
+      <x:c r="B26" s="95"/>
+      <x:c r="C26" s="89"/>
+      <x:c r="D26" s="89"/>
+      <x:c r="E26" s="89"/>
+      <x:c r="F26" s="89"/>
+      <x:c r="G26" s="89"/>
+      <x:c r="H26" s="89"/>
+      <x:c r="I26" s="89"/>
+      <x:c r="J26" s="89"/>
+      <x:c r="K26" s="89"/>
+      <x:c r="L26" s="89"/>
+      <x:c r="M26" s="95"/>
+      <x:c r="N26" s="89"/>
+      <x:c r="O26" s="89"/>
+      <x:c r="P26" s="89"/>
+      <x:c r="Q26" s="89"/>
+      <x:c r="R26" s="89"/>
+      <x:c r="S26" s="90"/>
+      <x:c r="T26" s="99" t="str">
         <x:f>IF(COUNTA(A26:S26)=0,"NOT STARTED",IF(OR(A26="",B26="",C26="",D26="",E26="",F26="",G26="",H26="",I26="",J26="",K26="",L26="",M26="",N26="",O26="",P26="",Q26="",R26="",S26=""),"INCOMPLETE",IF(OR(S26="Needs revision",AND(OR(N26="Contradicted",N26="Not verifiable"),S26&lt;&gt;"Cleared after revision")),"REVISE / FLAG","EVIDENCE READY")))</x:f>
         <x:v>NOT STARTED</x:v>
       </x:c>
     </x:row>
     <x:row r="27" ht="66" customHeight="1">
-      <x:c r="A27" s="85"/>
-      <x:c r="B27" s="92"/>
-      <x:c r="C27" s="86"/>
-      <x:c r="D27" s="86"/>
-      <x:c r="E27" s="86"/>
-      <x:c r="F27" s="86"/>
-      <x:c r="G27" s="86"/>
-      <x:c r="H27" s="86"/>
-      <x:c r="I27" s="86"/>
-      <x:c r="J27" s="86"/>
-      <x:c r="K27" s="86"/>
-      <x:c r="L27" s="86"/>
-      <x:c r="M27" s="92"/>
-      <x:c r="N27" s="86"/>
-      <x:c r="O27" s="86"/>
-      <x:c r="P27" s="86"/>
-      <x:c r="Q27" s="86"/>
-      <x:c r="R27" s="86"/>
-      <x:c r="S27" s="87"/>
-      <x:c r="T27" s="96" t="str">
+      <x:c r="A27" s="88"/>
+      <x:c r="B27" s="95"/>
+      <x:c r="C27" s="89"/>
+      <x:c r="D27" s="89"/>
+      <x:c r="E27" s="89"/>
+      <x:c r="F27" s="89"/>
+      <x:c r="G27" s="89"/>
+      <x:c r="H27" s="89"/>
+      <x:c r="I27" s="89"/>
+      <x:c r="J27" s="89"/>
+      <x:c r="K27" s="89"/>
+      <x:c r="L27" s="89"/>
+      <x:c r="M27" s="95"/>
+      <x:c r="N27" s="89"/>
+      <x:c r="O27" s="89"/>
+      <x:c r="P27" s="89"/>
+      <x:c r="Q27" s="89"/>
+      <x:c r="R27" s="89"/>
+      <x:c r="S27" s="90"/>
+      <x:c r="T27" s="99" t="str">
         <x:f>IF(COUNTA(A27:S27)=0,"NOT STARTED",IF(OR(A27="",B27="",C27="",D27="",E27="",F27="",G27="",H27="",I27="",J27="",K27="",L27="",M27="",N27="",O27="",P27="",Q27="",R27="",S27=""),"INCOMPLETE",IF(OR(S27="Needs revision",AND(OR(N27="Contradicted",N27="Not verifiable"),S27&lt;&gt;"Cleared after revision")),"REVISE / FLAG","EVIDENCE READY")))</x:f>
         <x:v>NOT STARTED</x:v>
       </x:c>
     </x:row>
     <x:row r="28" ht="66" customHeight="1">
-      <x:c r="A28" s="85"/>
-      <x:c r="B28" s="92"/>
-      <x:c r="C28" s="86"/>
-      <x:c r="D28" s="86"/>
-      <x:c r="E28" s="86"/>
-      <x:c r="F28" s="86"/>
-      <x:c r="G28" s="86"/>
-      <x:c r="H28" s="86"/>
-      <x:c r="I28" s="86"/>
-      <x:c r="J28" s="86"/>
-      <x:c r="K28" s="86"/>
-      <x:c r="L28" s="86"/>
-      <x:c r="M28" s="92"/>
-      <x:c r="N28" s="86"/>
-      <x:c r="O28" s="86"/>
-      <x:c r="P28" s="86"/>
-      <x:c r="Q28" s="86"/>
-      <x:c r="R28" s="86"/>
-      <x:c r="S28" s="87"/>
-      <x:c r="T28" s="96" t="str">
+      <x:c r="A28" s="88"/>
+      <x:c r="B28" s="95"/>
+      <x:c r="C28" s="89"/>
+      <x:c r="D28" s="89"/>
+      <x:c r="E28" s="89"/>
+      <x:c r="F28" s="89"/>
+      <x:c r="G28" s="89"/>
+      <x:c r="H28" s="89"/>
+      <x:c r="I28" s="89"/>
+      <x:c r="J28" s="89"/>
+      <x:c r="K28" s="89"/>
+      <x:c r="L28" s="89"/>
+      <x:c r="M28" s="95"/>
+      <x:c r="N28" s="89"/>
+      <x:c r="O28" s="89"/>
+      <x:c r="P28" s="89"/>
+      <x:c r="Q28" s="89"/>
+      <x:c r="R28" s="89"/>
+      <x:c r="S28" s="90"/>
+      <x:c r="T28" s="99" t="str">
         <x:f>IF(COUNTA(A28:S28)=0,"NOT STARTED",IF(OR(A28="",B28="",C28="",D28="",E28="",F28="",G28="",H28="",I28="",J28="",K28="",L28="",M28="",N28="",O28="",P28="",Q28="",R28="",S28=""),"INCOMPLETE",IF(OR(S28="Needs revision",AND(OR(N28="Contradicted",N28="Not verifiable"),S28&lt;&gt;"Cleared after revision")),"REVISE / FLAG","EVIDENCE READY")))</x:f>
         <x:v>NOT STARTED</x:v>
       </x:c>
     </x:row>
     <x:row r="29" ht="66" customHeight="1">
-      <x:c r="A29" s="85"/>
-      <x:c r="B29" s="92"/>
-      <x:c r="C29" s="86"/>
-      <x:c r="D29" s="86"/>
-      <x:c r="E29" s="86"/>
-      <x:c r="F29" s="86"/>
-      <x:c r="G29" s="86"/>
-      <x:c r="H29" s="86"/>
-      <x:c r="I29" s="86"/>
-      <x:c r="J29" s="86"/>
-      <x:c r="K29" s="86"/>
-      <x:c r="L29" s="86"/>
-      <x:c r="M29" s="92"/>
-      <x:c r="N29" s="86"/>
-      <x:c r="O29" s="86"/>
-      <x:c r="P29" s="86"/>
-      <x:c r="Q29" s="86"/>
-      <x:c r="R29" s="86"/>
-      <x:c r="S29" s="87"/>
-      <x:c r="T29" s="96" t="str">
+      <x:c r="A29" s="88"/>
+      <x:c r="B29" s="95"/>
+      <x:c r="C29" s="89"/>
+      <x:c r="D29" s="89"/>
+      <x:c r="E29" s="89"/>
+      <x:c r="F29" s="89"/>
+      <x:c r="G29" s="89"/>
+      <x:c r="H29" s="89"/>
+      <x:c r="I29" s="89"/>
+      <x:c r="J29" s="89"/>
+      <x:c r="K29" s="89"/>
+      <x:c r="L29" s="89"/>
+      <x:c r="M29" s="95"/>
+      <x:c r="N29" s="89"/>
+      <x:c r="O29" s="89"/>
+      <x:c r="P29" s="89"/>
+      <x:c r="Q29" s="89"/>
+      <x:c r="R29" s="89"/>
+      <x:c r="S29" s="90"/>
+      <x:c r="T29" s="99" t="str">
         <x:f>IF(COUNTA(A29:S29)=0,"NOT STARTED",IF(OR(A29="",B29="",C29="",D29="",E29="",F29="",G29="",H29="",I29="",J29="",K29="",L29="",M29="",N29="",O29="",P29="",Q29="",R29="",S29=""),"INCOMPLETE",IF(OR(S29="Needs revision",AND(OR(N29="Contradicted",N29="Not verifiable"),S29&lt;&gt;"Cleared after revision")),"REVISE / FLAG","EVIDENCE READY")))</x:f>
         <x:v>NOT STARTED</x:v>
       </x:c>
     </x:row>
     <x:row r="30" ht="66" customHeight="1">
-      <x:c r="A30" s="85"/>
-      <x:c r="B30" s="92"/>
-      <x:c r="C30" s="86"/>
-      <x:c r="D30" s="86"/>
-      <x:c r="E30" s="86"/>
-      <x:c r="F30" s="86"/>
-      <x:c r="G30" s="86"/>
-      <x:c r="H30" s="86"/>
-      <x:c r="I30" s="86"/>
-      <x:c r="J30" s="86"/>
-      <x:c r="K30" s="86"/>
-      <x:c r="L30" s="86"/>
-      <x:c r="M30" s="92"/>
-      <x:c r="N30" s="86"/>
-      <x:c r="O30" s="86"/>
-      <x:c r="P30" s="86"/>
-      <x:c r="Q30" s="86"/>
-      <x:c r="R30" s="86"/>
-      <x:c r="S30" s="87"/>
-      <x:c r="T30" s="96" t="str">
+      <x:c r="A30" s="88"/>
+      <x:c r="B30" s="95"/>
+      <x:c r="C30" s="89"/>
+      <x:c r="D30" s="89"/>
+      <x:c r="E30" s="89"/>
+      <x:c r="F30" s="89"/>
+      <x:c r="G30" s="89"/>
+      <x:c r="H30" s="89"/>
+      <x:c r="I30" s="89"/>
+      <x:c r="J30" s="89"/>
+      <x:c r="K30" s="89"/>
+      <x:c r="L30" s="89"/>
+      <x:c r="M30" s="95"/>
+      <x:c r="N30" s="89"/>
+      <x:c r="O30" s="89"/>
+      <x:c r="P30" s="89"/>
+      <x:c r="Q30" s="89"/>
+      <x:c r="R30" s="89"/>
+      <x:c r="S30" s="90"/>
+      <x:c r="T30" s="99" t="str">
         <x:f>IF(COUNTA(A30:S30)=0,"NOT STARTED",IF(OR(A30="",B30="",C30="",D30="",E30="",F30="",G30="",H30="",I30="",J30="",K30="",L30="",M30="",N30="",O30="",P30="",Q30="",R30="",S30=""),"INCOMPLETE",IF(OR(S30="Needs revision",AND(OR(N30="Contradicted",N30="Not verifiable"),S30&lt;&gt;"Cleared after revision")),"REVISE / FLAG","EVIDENCE READY")))</x:f>
         <x:v>NOT STARTED</x:v>
       </x:c>
     </x:row>
     <x:row r="31" ht="66" customHeight="1">
-      <x:c r="A31" s="85"/>
-      <x:c r="B31" s="92"/>
-      <x:c r="C31" s="86"/>
-      <x:c r="D31" s="86"/>
-      <x:c r="E31" s="86"/>
-      <x:c r="F31" s="86"/>
-      <x:c r="G31" s="86"/>
-      <x:c r="H31" s="86"/>
-      <x:c r="I31" s="86"/>
-      <x:c r="J31" s="86"/>
-      <x:c r="K31" s="86"/>
-      <x:c r="L31" s="86"/>
-      <x:c r="M31" s="92"/>
-      <x:c r="N31" s="86"/>
-      <x:c r="O31" s="86"/>
-      <x:c r="P31" s="86"/>
-      <x:c r="Q31" s="86"/>
-      <x:c r="R31" s="86"/>
-      <x:c r="S31" s="87"/>
-      <x:c r="T31" s="96" t="str">
+      <x:c r="A31" s="88"/>
+      <x:c r="B31" s="95"/>
+      <x:c r="C31" s="89"/>
+      <x:c r="D31" s="89"/>
+      <x:c r="E31" s="89"/>
+      <x:c r="F31" s="89"/>
+      <x:c r="G31" s="89"/>
+      <x:c r="H31" s="89"/>
+      <x:c r="I31" s="89"/>
+      <x:c r="J31" s="89"/>
+      <x:c r="K31" s="89"/>
+      <x:c r="L31" s="89"/>
+      <x:c r="M31" s="95"/>
+      <x:c r="N31" s="89"/>
+      <x:c r="O31" s="89"/>
+      <x:c r="P31" s="89"/>
+      <x:c r="Q31" s="89"/>
+      <x:c r="R31" s="89"/>
+      <x:c r="S31" s="90"/>
+      <x:c r="T31" s="99" t="str">
         <x:f>IF(COUNTA(A31:S31)=0,"NOT STARTED",IF(OR(A31="",B31="",C31="",D31="",E31="",F31="",G31="",H31="",I31="",J31="",K31="",L31="",M31="",N31="",O31="",P31="",Q31="",R31="",S31=""),"INCOMPLETE",IF(OR(S31="Needs revision",AND(OR(N31="Contradicted",N31="Not verifiable"),S31&lt;&gt;"Cleared after revision")),"REVISE / FLAG","EVIDENCE READY")))</x:f>
         <x:v>NOT STARTED</x:v>
       </x:c>
     </x:row>
     <x:row r="32" ht="66" customHeight="1">
-      <x:c r="A32" s="85"/>
-      <x:c r="B32" s="92"/>
-      <x:c r="C32" s="86"/>
-      <x:c r="D32" s="86"/>
-      <x:c r="E32" s="86"/>
-      <x:c r="F32" s="86"/>
-      <x:c r="G32" s="86"/>
-      <x:c r="H32" s="86"/>
-      <x:c r="I32" s="86"/>
-      <x:c r="J32" s="86"/>
-      <x:c r="K32" s="86"/>
-      <x:c r="L32" s="86"/>
-      <x:c r="M32" s="92"/>
-      <x:c r="N32" s="86"/>
-      <x:c r="O32" s="86"/>
-      <x:c r="P32" s="86"/>
-      <x:c r="Q32" s="86"/>
-      <x:c r="R32" s="86"/>
-      <x:c r="S32" s="87"/>
-      <x:c r="T32" s="96" t="str">
+      <x:c r="A32" s="88"/>
+      <x:c r="B32" s="95"/>
+      <x:c r="C32" s="89"/>
+      <x:c r="D32" s="89"/>
+      <x:c r="E32" s="89"/>
+      <x:c r="F32" s="89"/>
+      <x:c r="G32" s="89"/>
+      <x:c r="H32" s="89"/>
+      <x:c r="I32" s="89"/>
+      <x:c r="J32" s="89"/>
+      <x:c r="K32" s="89"/>
+      <x:c r="L32" s="89"/>
+      <x:c r="M32" s="95"/>
+      <x:c r="N32" s="89"/>
+      <x:c r="O32" s="89"/>
+      <x:c r="P32" s="89"/>
+      <x:c r="Q32" s="89"/>
+      <x:c r="R32" s="89"/>
+      <x:c r="S32" s="90"/>
+      <x:c r="T32" s="99" t="str">
         <x:f>IF(COUNTA(A32:S32)=0,"NOT STARTED",IF(OR(A32="",B32="",C32="",D32="",E32="",F32="",G32="",H32="",I32="",J32="",K32="",L32="",M32="",N32="",O32="",P32="",Q32="",R32="",S32=""),"INCOMPLETE",IF(OR(S32="Needs revision",AND(OR(N32="Contradicted",N32="Not verifiable"),S32&lt;&gt;"Cleared after revision")),"REVISE / FLAG","EVIDENCE READY")))</x:f>
         <x:v>NOT STARTED</x:v>
       </x:c>
     </x:row>
     <x:row r="33" ht="66" customHeight="1">
-      <x:c r="A33" s="85"/>
-      <x:c r="B33" s="92"/>
-      <x:c r="C33" s="86"/>
-      <x:c r="D33" s="86"/>
-      <x:c r="E33" s="86"/>
-      <x:c r="F33" s="86"/>
-      <x:c r="G33" s="86"/>
-      <x:c r="H33" s="86"/>
-      <x:c r="I33" s="86"/>
-      <x:c r="J33" s="86"/>
-      <x:c r="K33" s="86"/>
-      <x:c r="L33" s="86"/>
-      <x:c r="M33" s="92"/>
-      <x:c r="N33" s="86"/>
-      <x:c r="O33" s="86"/>
-      <x:c r="P33" s="86"/>
-      <x:c r="Q33" s="86"/>
-      <x:c r="R33" s="86"/>
-      <x:c r="S33" s="87"/>
-      <x:c r="T33" s="96" t="str">
+      <x:c r="A33" s="88"/>
+      <x:c r="B33" s="95"/>
+      <x:c r="C33" s="89"/>
+      <x:c r="D33" s="89"/>
+      <x:c r="E33" s="89"/>
+      <x:c r="F33" s="89"/>
+      <x:c r="G33" s="89"/>
+      <x:c r="H33" s="89"/>
+      <x:c r="I33" s="89"/>
+      <x:c r="J33" s="89"/>
+      <x:c r="K33" s="89"/>
+      <x:c r="L33" s="89"/>
+      <x:c r="M33" s="95"/>
+      <x:c r="N33" s="89"/>
+      <x:c r="O33" s="89"/>
+      <x:c r="P33" s="89"/>
+      <x:c r="Q33" s="89"/>
+      <x:c r="R33" s="89"/>
+      <x:c r="S33" s="90"/>
+      <x:c r="T33" s="99" t="str">
         <x:f>IF(COUNTA(A33:S33)=0,"NOT STARTED",IF(OR(A33="",B33="",C33="",D33="",E33="",F33="",G33="",H33="",I33="",J33="",K33="",L33="",M33="",N33="",O33="",P33="",Q33="",R33="",S33=""),"INCOMPLETE",IF(OR(S33="Needs revision",AND(OR(N33="Contradicted",N33="Not verifiable"),S33&lt;&gt;"Cleared after revision")),"REVISE / FLAG","EVIDENCE READY")))</x:f>
         <x:v>NOT STARTED</x:v>
       </x:c>
     </x:row>
     <x:row r="34" ht="66" customHeight="1">
-      <x:c r="A34" s="85"/>
-      <x:c r="B34" s="92"/>
-      <x:c r="C34" s="86"/>
-      <x:c r="D34" s="86"/>
-      <x:c r="E34" s="86"/>
-      <x:c r="F34" s="86"/>
-      <x:c r="G34" s="86"/>
-      <x:c r="H34" s="86"/>
-      <x:c r="I34" s="86"/>
-      <x:c r="J34" s="86"/>
-      <x:c r="K34" s="86"/>
-      <x:c r="L34" s="86"/>
-      <x:c r="M34" s="92"/>
-      <x:c r="N34" s="86"/>
-      <x:c r="O34" s="86"/>
-      <x:c r="P34" s="86"/>
-      <x:c r="Q34" s="86"/>
-      <x:c r="R34" s="86"/>
-      <x:c r="S34" s="87"/>
-      <x:c r="T34" s="96" t="str">
+      <x:c r="A34" s="88"/>
+      <x:c r="B34" s="95"/>
+      <x:c r="C34" s="89"/>
+      <x:c r="D34" s="89"/>
+      <x:c r="E34" s="89"/>
+      <x:c r="F34" s="89"/>
+      <x:c r="G34" s="89"/>
+      <x:c r="H34" s="89"/>
+      <x:c r="I34" s="89"/>
+      <x:c r="J34" s="89"/>
+      <x:c r="K34" s="89"/>
+      <x:c r="L34" s="89"/>
+      <x:c r="M34" s="95"/>
+      <x:c r="N34" s="89"/>
+      <x:c r="O34" s="89"/>
+      <x:c r="P34" s="89"/>
+      <x:c r="Q34" s="89"/>
+      <x:c r="R34" s="89"/>
+      <x:c r="S34" s="90"/>
+      <x:c r="T34" s="99" t="str">
         <x:f>IF(COUNTA(A34:S34)=0,"NOT STARTED",IF(OR(A34="",B34="",C34="",D34="",E34="",F34="",G34="",H34="",I34="",J34="",K34="",L34="",M34="",N34="",O34="",P34="",Q34="",R34="",S34=""),"INCOMPLETE",IF(OR(S34="Needs revision",AND(OR(N34="Contradicted",N34="Not verifiable"),S34&lt;&gt;"Cleared after revision")),"REVISE / FLAG","EVIDENCE READY")))</x:f>
         <x:v>NOT STARTED</x:v>
       </x:c>
     </x:row>
     <x:row r="35" ht="66" customHeight="1">
-      <x:c r="A35" s="85"/>
-      <x:c r="B35" s="92"/>
-      <x:c r="C35" s="86"/>
-      <x:c r="D35" s="86"/>
-      <x:c r="E35" s="86"/>
-      <x:c r="F35" s="86"/>
-      <x:c r="G35" s="86"/>
-      <x:c r="H35" s="86"/>
-      <x:c r="I35" s="86"/>
-      <x:c r="J35" s="86"/>
-      <x:c r="K35" s="86"/>
-      <x:c r="L35" s="86"/>
-      <x:c r="M35" s="92"/>
-      <x:c r="N35" s="86"/>
-      <x:c r="O35" s="86"/>
-      <x:c r="P35" s="86"/>
-      <x:c r="Q35" s="86"/>
-      <x:c r="R35" s="86"/>
-      <x:c r="S35" s="87"/>
-      <x:c r="T35" s="96" t="str">
+      <x:c r="A35" s="88"/>
+      <x:c r="B35" s="95"/>
+      <x:c r="C35" s="89"/>
+      <x:c r="D35" s="89"/>
+      <x:c r="E35" s="89"/>
+      <x:c r="F35" s="89"/>
+      <x:c r="G35" s="89"/>
+      <x:c r="H35" s="89"/>
+      <x:c r="I35" s="89"/>
+      <x:c r="J35" s="89"/>
+      <x:c r="K35" s="89"/>
+      <x:c r="L35" s="89"/>
+      <x:c r="M35" s="95"/>
+      <x:c r="N35" s="89"/>
+      <x:c r="O35" s="89"/>
+      <x:c r="P35" s="89"/>
+      <x:c r="Q35" s="89"/>
+      <x:c r="R35" s="89"/>
+      <x:c r="S35" s="90"/>
+      <x:c r="T35" s="99" t="str">
         <x:f>IF(COUNTA(A35:S35)=0,"NOT STARTED",IF(OR(A35="",B35="",C35="",D35="",E35="",F35="",G35="",H35="",I35="",J35="",K35="",L35="",M35="",N35="",O35="",P35="",Q35="",R35="",S35=""),"INCOMPLETE",IF(OR(S35="Needs revision",AND(OR(N35="Contradicted",N35="Not verifiable"),S35&lt;&gt;"Cleared after revision")),"REVISE / FLAG","EVIDENCE READY")))</x:f>
         <x:v>NOT STARTED</x:v>
       </x:c>
     </x:row>
     <x:row r="36" ht="66" customHeight="1">
-      <x:c r="A36" s="85"/>
-      <x:c r="B36" s="92"/>
-      <x:c r="C36" s="86"/>
-      <x:c r="D36" s="86"/>
-      <x:c r="E36" s="86"/>
-      <x:c r="F36" s="86"/>
-      <x:c r="G36" s="86"/>
-      <x:c r="H36" s="86"/>
-      <x:c r="I36" s="86"/>
-      <x:c r="J36" s="86"/>
-      <x:c r="K36" s="86"/>
-      <x:c r="L36" s="86"/>
-      <x:c r="M36" s="92"/>
-      <x:c r="N36" s="86"/>
-      <x:c r="O36" s="86"/>
-      <x:c r="P36" s="86"/>
-      <x:c r="Q36" s="86"/>
-      <x:c r="R36" s="86"/>
-      <x:c r="S36" s="87"/>
-      <x:c r="T36" s="96" t="str">
+      <x:c r="A36" s="88"/>
+      <x:c r="B36" s="95"/>
+      <x:c r="C36" s="89"/>
+      <x:c r="D36" s="89"/>
+      <x:c r="E36" s="89"/>
+      <x:c r="F36" s="89"/>
+      <x:c r="G36" s="89"/>
+      <x:c r="H36" s="89"/>
+      <x:c r="I36" s="89"/>
+      <x:c r="J36" s="89"/>
+      <x:c r="K36" s="89"/>
+      <x:c r="L36" s="89"/>
+      <x:c r="M36" s="95"/>
+      <x:c r="N36" s="89"/>
+      <x:c r="O36" s="89"/>
+      <x:c r="P36" s="89"/>
+      <x:c r="Q36" s="89"/>
+      <x:c r="R36" s="89"/>
+      <x:c r="S36" s="90"/>
+      <x:c r="T36" s="99" t="str">
         <x:f>IF(COUNTA(A36:S36)=0,"NOT STARTED",IF(OR(A36="",B36="",C36="",D36="",E36="",F36="",G36="",H36="",I36="",J36="",K36="",L36="",M36="",N36="",O36="",P36="",Q36="",R36="",S36=""),"INCOMPLETE",IF(OR(S36="Needs revision",AND(OR(N36="Contradicted",N36="Not verifiable"),S36&lt;&gt;"Cleared after revision")),"REVISE / FLAG","EVIDENCE READY")))</x:f>
         <x:v>NOT STARTED</x:v>
       </x:c>
     </x:row>
     <x:row r="37" ht="66" customHeight="1">
-      <x:c r="A37" s="88"/>
-      <x:c r="B37" s="93"/>
-      <x:c r="C37" s="89"/>
-      <x:c r="D37" s="89"/>
-      <x:c r="E37" s="89"/>
-      <x:c r="F37" s="89"/>
-      <x:c r="G37" s="89"/>
-      <x:c r="H37" s="89"/>
-      <x:c r="I37" s="89"/>
-      <x:c r="J37" s="89"/>
-      <x:c r="K37" s="89"/>
-      <x:c r="L37" s="89"/>
-      <x:c r="M37" s="93"/>
-      <x:c r="N37" s="89"/>
-      <x:c r="O37" s="89"/>
-      <x:c r="P37" s="89"/>
-      <x:c r="Q37" s="89"/>
-      <x:c r="R37" s="89"/>
-      <x:c r="S37" s="90"/>
-      <x:c r="T37" s="96" t="str">
+      <x:c r="A37" s="91"/>
+      <x:c r="B37" s="96"/>
+      <x:c r="C37" s="92"/>
+      <x:c r="D37" s="92"/>
+      <x:c r="E37" s="92"/>
+      <x:c r="F37" s="92"/>
+      <x:c r="G37" s="92"/>
+      <x:c r="H37" s="92"/>
+      <x:c r="I37" s="92"/>
+      <x:c r="J37" s="92"/>
+      <x:c r="K37" s="92"/>
+      <x:c r="L37" s="92"/>
+      <x:c r="M37" s="96"/>
+      <x:c r="N37" s="92"/>
+      <x:c r="O37" s="92"/>
+      <x:c r="P37" s="92"/>
+      <x:c r="Q37" s="92"/>
+      <x:c r="R37" s="92"/>
+      <x:c r="S37" s="93"/>
+      <x:c r="T37" s="99" t="str">
         <x:f>IF(COUNTA(A37:S37)=0,"NOT STARTED",IF(OR(A37="",B37="",C37="",D37="",E37="",F37="",G37="",H37="",I37="",J37="",K37="",L37="",M37="",N37="",O37="",P37="",Q37="",R37="",S37=""),"INCOMPLETE",IF(OR(S37="Needs revision",AND(OR(N37="Contradicted",N37="Not verifiable"),S37&lt;&gt;"Cleared after revision")),"REVISE / FLAG","EVIDENCE READY")))</x:f>
         <x:v>NOT STARTED</x:v>
       </x:c>
@@ -2830,58 +3046,58 @@
       <x:c r="A40" s="25" t="str">
         <x:v>Evidence-ready entries</x:v>
       </x:c>
-      <x:c r="B40" s="97" t="n">
+      <x:c r="B40" s="100" t="n">
         <x:f>COUNTIF(T8:T37,"EVIDENCE READY")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="C40" s="97" t="str"/>
+      <x:c r="C40" s="100" t="str"/>
       <x:c r="D40" s="25" t="str">
         <x:v>Entries to revise / flag</x:v>
       </x:c>
-      <x:c r="E40" s="99" t="n">
+      <x:c r="E40" s="102" t="n">
         <x:f>COUNTIF(T8:T37,"REVISE / FLAG")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F40" s="99" t="str"/>
+      <x:c r="F40" s="102" t="str"/>
       <x:c r="G40" s="25" t="str">
         <x:v>Minimum required</x:v>
       </x:c>
-      <x:c r="H40" s="57" t="n">
+      <x:c r="H40" s="60" t="n">
         <x:v>15</x:v>
       </x:c>
       <x:c r="J40" s="25" t="str">
         <x:v>Log readiness</x:v>
       </x:c>
-      <x:c r="K40" s="100" t="str">
+      <x:c r="K40" s="103" t="str">
         <x:f>IF(OR(E6="",H6="",K6=""),"ENTER 3 CLIENTS",IF(COUNTIF(B47:D51,"READY")&lt;H40,"COVERAGE INCOMPLETE",IF(COUNTIF(T8:T37,"INCOMPLETE")+E40&gt;0,"REVIEW LOG","READY FOR PHASE 1 GATE")))</x:f>
         <x:v>ENTER 3 CLIENTS</x:v>
       </x:c>
-      <x:c r="L40" s="101"/>
-      <x:c r="M40" s="102"/>
+      <x:c r="L40" s="104"/>
+      <x:c r="M40" s="105"/>
     </x:row>
     <x:row r="42" ht="34" customHeight="1">
-      <x:c r="A42" s="104" t="str">
+      <x:c r="A42" s="107" t="str">
         <x:v>Evidence-ready means the entry shows the recommendation or initial judgment, an alternative rejected, a key trade-off, a human-verified source and as-of date, what changed, the final reasoning, a downstream guardrail, and peer review. Portfolio Manager entries identify integration decisions; Risk and Derivatives entries identify residual risk and hedge/no-hedge evidence. Contradicted or unverifiable material claims must be revised or carried to the committee as an explicit open issue.</x:v>
       </x:c>
-      <x:c r="B42" s="104"/>
-      <x:c r="C42" s="104"/>
-      <x:c r="D42" s="104"/>
-      <x:c r="E42" s="104"/>
-      <x:c r="F42" s="104"/>
-      <x:c r="G42" s="104"/>
-      <x:c r="H42" s="104"/>
-      <x:c r="I42" s="104"/>
-      <x:c r="J42" s="104"/>
-      <x:c r="K42" s="104"/>
-      <x:c r="L42" s="104"/>
-      <x:c r="M42" s="104"/>
-      <x:c r="N42" s="104"/>
-      <x:c r="O42" s="104"/>
-      <x:c r="P42" s="104"/>
-      <x:c r="Q42" s="104"/>
-      <x:c r="R42" s="104"/>
-      <x:c r="S42" s="104"/>
-      <x:c r="T42" s="104"/>
+      <x:c r="B42" s="107"/>
+      <x:c r="C42" s="107"/>
+      <x:c r="D42" s="107"/>
+      <x:c r="E42" s="107"/>
+      <x:c r="F42" s="107"/>
+      <x:c r="G42" s="107"/>
+      <x:c r="H42" s="107"/>
+      <x:c r="I42" s="107"/>
+      <x:c r="J42" s="107"/>
+      <x:c r="K42" s="107"/>
+      <x:c r="L42" s="107"/>
+      <x:c r="M42" s="107"/>
+      <x:c r="N42" s="107"/>
+      <x:c r="O42" s="107"/>
+      <x:c r="P42" s="107"/>
+      <x:c r="Q42" s="107"/>
+      <x:c r="R42" s="107"/>
+      <x:c r="S42" s="107"/>
+      <x:c r="T42" s="107"/>
     </x:row>
     <x:row r="45" ht="23" customHeight="1">
       <x:c r="A45" s="11" t="str">
@@ -2928,19 +3144,19 @@
       <x:c r="A47" s="52" t="str">
         <x:v>Client and Macro Strategist</x:v>
       </x:c>
-      <x:c r="B47" s="107" t="str">
+      <x:c r="B47" s="110" t="str">
         <x:f>IF(OR($E$6="",COUNTIFS($C$8:$C$37,$E$6,$D$8:$D$37,$A47,$T$8:$T$37,"EVIDENCE READY")=0),"MISSING","READY")</x:f>
         <x:v>MISSING</x:v>
       </x:c>
-      <x:c r="C47" s="107" t="str">
+      <x:c r="C47" s="110" t="str">
         <x:f>IF(OR($H$6="",COUNTIFS($C$8:$C$37,$H$6,$D$8:$D$37,$A47,$T$8:$T$37,"EVIDENCE READY")=0),"MISSING","READY")</x:f>
         <x:v>MISSING</x:v>
       </x:c>
-      <x:c r="D47" s="107" t="str">
+      <x:c r="D47" s="110" t="str">
         <x:f>IF(OR($K$6="",COUNTIFS($C$8:$C$37,$K$6,$D$8:$D$37,$A47,$T$8:$T$37,"EVIDENCE READY")=0),"MISSING","READY")</x:f>
         <x:v>MISSING</x:v>
       </x:c>
-      <x:c r="E47" s="107" t="str">
+      <x:c r="E47" s="110" t="str">
         <x:f>IF(COUNTIF(B47:D47,"MISSING")&gt;0,"MISSING","READY")</x:f>
         <x:v>MISSING</x:v>
       </x:c>
@@ -2949,19 +3165,19 @@
       <x:c r="A48" s="52" t="str">
         <x:v>Fixed-Income Analyst</x:v>
       </x:c>
-      <x:c r="B48" s="107" t="str">
+      <x:c r="B48" s="110" t="str">
         <x:f>IF(OR($E$6="",COUNTIFS($C$8:$C$37,$E$6,$D$8:$D$37,$A48,$T$8:$T$37,"EVIDENCE READY")=0),"MISSING","READY")</x:f>
         <x:v>MISSING</x:v>
       </x:c>
-      <x:c r="C48" s="107" t="str">
+      <x:c r="C48" s="110" t="str">
         <x:f>IF(OR($H$6="",COUNTIFS($C$8:$C$37,$H$6,$D$8:$D$37,$A48,$T$8:$T$37,"EVIDENCE READY")=0),"MISSING","READY")</x:f>
         <x:v>MISSING</x:v>
       </x:c>
-      <x:c r="D48" s="107" t="str">
+      <x:c r="D48" s="110" t="str">
         <x:f>IF(OR($K$6="",COUNTIFS($C$8:$C$37,$K$6,$D$8:$D$37,$A48,$T$8:$T$37,"EVIDENCE READY")=0),"MISSING","READY")</x:f>
         <x:v>MISSING</x:v>
       </x:c>
-      <x:c r="E48" s="107" t="str">
+      <x:c r="E48" s="110" t="str">
         <x:f>IF(COUNTIF(B48:D48,"MISSING")&gt;0,"MISSING","READY")</x:f>
         <x:v>MISSING</x:v>
       </x:c>
@@ -2970,19 +3186,19 @@
       <x:c r="A49" s="52" t="str">
         <x:v>Equity Analyst</x:v>
       </x:c>
-      <x:c r="B49" s="107" t="str">
+      <x:c r="B49" s="110" t="str">
         <x:f>IF(OR($E$6="",COUNTIFS($C$8:$C$37,$E$6,$D$8:$D$37,$A49,$T$8:$T$37,"EVIDENCE READY")=0),"MISSING","READY")</x:f>
         <x:v>MISSING</x:v>
       </x:c>
-      <x:c r="C49" s="107" t="str">
+      <x:c r="C49" s="110" t="str">
         <x:f>IF(OR($H$6="",COUNTIFS($C$8:$C$37,$H$6,$D$8:$D$37,$A49,$T$8:$T$37,"EVIDENCE READY")=0),"MISSING","READY")</x:f>
         <x:v>MISSING</x:v>
       </x:c>
-      <x:c r="D49" s="107" t="str">
+      <x:c r="D49" s="110" t="str">
         <x:f>IF(OR($K$6="",COUNTIFS($C$8:$C$37,$K$6,$D$8:$D$37,$A49,$T$8:$T$37,"EVIDENCE READY")=0),"MISSING","READY")</x:f>
         <x:v>MISSING</x:v>
       </x:c>
-      <x:c r="E49" s="107" t="str">
+      <x:c r="E49" s="110" t="str">
         <x:f>IF(COUNTIF(B49:D49,"MISSING")&gt;0,"MISSING","READY")</x:f>
         <x:v>MISSING</x:v>
       </x:c>
@@ -2991,19 +3207,19 @@
       <x:c r="A50" s="52" t="str">
         <x:v>Portfolio Manager</x:v>
       </x:c>
-      <x:c r="B50" s="107" t="str">
+      <x:c r="B50" s="110" t="str">
         <x:f>IF(OR($E$6="",COUNTIFS($C$8:$C$37,$E$6,$D$8:$D$37,$A50,$T$8:$T$37,"EVIDENCE READY")=0),"MISSING","READY")</x:f>
         <x:v>MISSING</x:v>
       </x:c>
-      <x:c r="C50" s="107" t="str">
+      <x:c r="C50" s="110" t="str">
         <x:f>IF(OR($H$6="",COUNTIFS($C$8:$C$37,$H$6,$D$8:$D$37,$A50,$T$8:$T$37,"EVIDENCE READY")=0),"MISSING","READY")</x:f>
         <x:v>MISSING</x:v>
       </x:c>
-      <x:c r="D50" s="107" t="str">
+      <x:c r="D50" s="110" t="str">
         <x:f>IF(OR($K$6="",COUNTIFS($C$8:$C$37,$K$6,$D$8:$D$37,$A50,$T$8:$T$37,"EVIDENCE READY")=0),"MISSING","READY")</x:f>
         <x:v>MISSING</x:v>
       </x:c>
-      <x:c r="E50" s="107" t="str">
+      <x:c r="E50" s="110" t="str">
         <x:f>IF(COUNTIF(B50:D50,"MISSING")&gt;0,"MISSING","READY")</x:f>
         <x:v>MISSING</x:v>
       </x:c>
@@ -3012,46 +3228,46 @@
       <x:c r="A51" s="52" t="str">
         <x:v>Risk and Derivatives Analyst</x:v>
       </x:c>
-      <x:c r="B51" s="107" t="str">
+      <x:c r="B51" s="110" t="str">
         <x:f>IF(OR($E$6="",COUNTIFS($C$8:$C$37,$E$6,$D$8:$D$37,$A51,$T$8:$T$37,"EVIDENCE READY")=0),"MISSING","READY")</x:f>
         <x:v>MISSING</x:v>
       </x:c>
-      <x:c r="C51" s="107" t="str">
+      <x:c r="C51" s="110" t="str">
         <x:f>IF(OR($H$6="",COUNTIFS($C$8:$C$37,$H$6,$D$8:$D$37,$A51,$T$8:$T$37,"EVIDENCE READY")=0),"MISSING","READY")</x:f>
         <x:v>MISSING</x:v>
       </x:c>
-      <x:c r="D51" s="107" t="str">
+      <x:c r="D51" s="110" t="str">
         <x:f>IF(OR($K$6="",COUNTIFS($C$8:$C$37,$K$6,$D$8:$D$37,$A51,$T$8:$T$37,"EVIDENCE READY")=0),"MISSING","READY")</x:f>
         <x:v>MISSING</x:v>
       </x:c>
-      <x:c r="E51" s="107" t="str">
+      <x:c r="E51" s="110" t="str">
         <x:f>IF(COUNTIF(B51:D51,"MISSING")&gt;0,"MISSING","READY")</x:f>
         <x:v>MISSING</x:v>
       </x:c>
     </x:row>
     <x:row r="52" ht="30" customHeight="1">
-      <x:c r="A52" s="104" t="str">
+      <x:c r="A52" s="107" t="str">
         <x:v>The Phase 1 gate remains closed until every one of the five roles has at least one evidence-ready entry for each of the three assigned clients. The client names in row 6 must match the Client column exactly.</x:v>
       </x:c>
-      <x:c r="B52" s="104"/>
-      <x:c r="C52" s="104"/>
-      <x:c r="D52" s="104"/>
-      <x:c r="E52" s="104"/>
-      <x:c r="F52" s="104"/>
-      <x:c r="G52" s="104"/>
-      <x:c r="H52" s="104"/>
-      <x:c r="I52" s="104"/>
-      <x:c r="J52" s="104"/>
-      <x:c r="K52" s="104"/>
-      <x:c r="L52" s="104"/>
-      <x:c r="M52" s="104"/>
-      <x:c r="N52" s="104"/>
-      <x:c r="O52" s="104"/>
-      <x:c r="P52" s="104"/>
-      <x:c r="Q52" s="104"/>
-      <x:c r="R52" s="104"/>
-      <x:c r="S52" s="104"/>
-      <x:c r="T52" s="104"/>
+      <x:c r="B52" s="107"/>
+      <x:c r="C52" s="107"/>
+      <x:c r="D52" s="107"/>
+      <x:c r="E52" s="107"/>
+      <x:c r="F52" s="107"/>
+      <x:c r="G52" s="107"/>
+      <x:c r="H52" s="107"/>
+      <x:c r="I52" s="107"/>
+      <x:c r="J52" s="107"/>
+      <x:c r="K52" s="107"/>
+      <x:c r="L52" s="107"/>
+      <x:c r="M52" s="107"/>
+      <x:c r="N52" s="107"/>
+      <x:c r="O52" s="107"/>
+      <x:c r="P52" s="107"/>
+      <x:c r="Q52" s="107"/>
+      <x:c r="R52" s="107"/>
+      <x:c r="S52" s="107"/>
+      <x:c r="T52" s="107"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -3072,31 +3288,31 @@
     <x:mergeCell ref="A52:T52"/>
   </x:mergeCells>
   <x:conditionalFormatting sqref="T8:T37">
-    <x:cfRule type="containsText" dxfId="13" priority="1" operator="containsText" text="EVIDENCE READY"/>
-    <x:cfRule type="containsText" dxfId="14" priority="2" operator="containsText" text="REVISE"/>
-    <x:cfRule type="containsText" dxfId="15" priority="3" operator="containsText" text="INCOMPLETE"/>
-    <x:cfRule type="containsText" dxfId="16" priority="4" operator="containsText" text="MINIMUM"/>
-    <x:cfRule type="containsText" dxfId="17" priority="5" operator="containsText" text="REVIEW"/>
-    <x:cfRule type="containsText" dxfId="18" priority="6" operator="containsText" text="MISSING"/>
-    <x:cfRule type="containsText" dxfId="19" priority="7" operator="containsText" text="ENTER"/>
+    <x:cfRule type="containsText" dxfId="20" priority="1" operator="containsText" text="EVIDENCE READY"/>
+    <x:cfRule type="containsText" dxfId="21" priority="2" operator="containsText" text="REVISE"/>
+    <x:cfRule type="containsText" dxfId="22" priority="3" operator="containsText" text="INCOMPLETE"/>
+    <x:cfRule type="containsText" dxfId="23" priority="4" operator="containsText" text="MINIMUM"/>
+    <x:cfRule type="containsText" dxfId="24" priority="5" operator="containsText" text="REVIEW"/>
+    <x:cfRule type="containsText" dxfId="25" priority="6" operator="containsText" text="MISSING"/>
+    <x:cfRule type="containsText" dxfId="26" priority="7" operator="containsText" text="ENTER"/>
   </x:conditionalFormatting>
   <x:conditionalFormatting sqref="K40:M40">
-    <x:cfRule type="containsText" dxfId="20" priority="8" operator="containsText" text="EVIDENCE READY"/>
-    <x:cfRule type="containsText" dxfId="21" priority="9" operator="containsText" text="REVISE"/>
-    <x:cfRule type="containsText" dxfId="22" priority="10" operator="containsText" text="INCOMPLETE"/>
-    <x:cfRule type="containsText" dxfId="23" priority="11" operator="containsText" text="MINIMUM"/>
-    <x:cfRule type="containsText" dxfId="24" priority="12" operator="containsText" text="REVIEW"/>
-    <x:cfRule type="containsText" dxfId="25" priority="13" operator="containsText" text="MISSING"/>
-    <x:cfRule type="containsText" dxfId="26" priority="14" operator="containsText" text="ENTER"/>
+    <x:cfRule type="containsText" dxfId="27" priority="8" operator="containsText" text="EVIDENCE READY"/>
+    <x:cfRule type="containsText" dxfId="28" priority="9" operator="containsText" text="REVISE"/>
+    <x:cfRule type="containsText" dxfId="29" priority="10" operator="containsText" text="INCOMPLETE"/>
+    <x:cfRule type="containsText" dxfId="30" priority="11" operator="containsText" text="MINIMUM"/>
+    <x:cfRule type="containsText" dxfId="31" priority="12" operator="containsText" text="REVIEW"/>
+    <x:cfRule type="containsText" dxfId="32" priority="13" operator="containsText" text="MISSING"/>
+    <x:cfRule type="containsText" dxfId="33" priority="14" operator="containsText" text="ENTER"/>
   </x:conditionalFormatting>
   <x:conditionalFormatting sqref="B47:E51">
-    <x:cfRule type="containsText" dxfId="27" priority="15" operator="containsText" text="EVIDENCE READY"/>
-    <x:cfRule type="containsText" dxfId="28" priority="16" operator="containsText" text="REVISE"/>
-    <x:cfRule type="containsText" dxfId="29" priority="17" operator="containsText" text="INCOMPLETE"/>
-    <x:cfRule type="containsText" dxfId="30" priority="18" operator="containsText" text="MINIMUM"/>
-    <x:cfRule type="containsText" dxfId="31" priority="19" operator="containsText" text="REVIEW"/>
-    <x:cfRule type="containsText" dxfId="32" priority="20" operator="containsText" text="MISSING"/>
-    <x:cfRule type="containsText" dxfId="33" priority="21" operator="containsText" text="ENTER"/>
+    <x:cfRule type="containsText" dxfId="34" priority="15" operator="containsText" text="EVIDENCE READY"/>
+    <x:cfRule type="containsText" dxfId="35" priority="16" operator="containsText" text="REVISE"/>
+    <x:cfRule type="containsText" dxfId="36" priority="17" operator="containsText" text="INCOMPLETE"/>
+    <x:cfRule type="containsText" dxfId="37" priority="18" operator="containsText" text="MINIMUM"/>
+    <x:cfRule type="containsText" dxfId="38" priority="19" operator="containsText" text="REVIEW"/>
+    <x:cfRule type="containsText" dxfId="39" priority="20" operator="containsText" text="MISSING"/>
+    <x:cfRule type="containsText" dxfId="40" priority="21" operator="containsText" text="ENTER"/>
   </x:conditionalFormatting>
   <x:dataValidations count="5">
     <x:dataValidation type="list" sqref="D8:D37">
@@ -3147,7 +3363,7 @@
     </x:row>
     <x:row r="2" ht="24" customHeight="1">
       <x:c r="A2" s="6" t="str">
-        <x:v>Frame the Mandate | All five committee members review, vote, and sign this record.</x:v>
+        <x:v>Frame the Mandate | All four or five members review and cast one vote each.</x:v>
       </x:c>
       <x:c r="B2" s="6"/>
       <x:c r="C2" s="6"/>
@@ -3161,21 +3377,21 @@
       <x:c r="A4" s="25" t="str">
         <x:v>Team / Committee Name</x:v>
       </x:c>
-      <x:c r="B4" s="82"/>
-      <x:c r="C4" s="84"/>
+      <x:c r="B4" s="85"/>
+      <x:c r="C4" s="87"/>
       <x:c r="D4" s="25" t="str">
         <x:v>Recorder</x:v>
       </x:c>
-      <x:c r="E4" s="63"/>
-      <x:c r="F4" s="110"/>
-      <x:c r="G4" s="64"/>
+      <x:c r="E4" s="66"/>
+      <x:c r="F4" s="113"/>
+      <x:c r="G4" s="67"/>
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="25" t="str">
         <x:v>Scope: all three clients</x:v>
       </x:c>
-      <x:c r="B5" s="85"/>
-      <x:c r="C5" s="87"/>
+      <x:c r="B5" s="88"/>
+      <x:c r="C5" s="90"/>
       <x:c r="D5" s="25" t="str">
         <x:v>Gate</x:v>
       </x:c>
@@ -3189,14 +3405,14 @@
       <x:c r="A6" s="25" t="str">
         <x:v>Meeting Date</x:v>
       </x:c>
-      <x:c r="B6" s="111"/>
-      <x:c r="C6" s="112"/>
+      <x:c r="B6" s="114"/>
+      <x:c r="C6" s="115"/>
       <x:c r="D6" s="25" t="str">
         <x:v>Meeting Chair</x:v>
       </x:c>
-      <x:c r="E6" s="63"/>
-      <x:c r="F6" s="110"/>
-      <x:c r="G6" s="64"/>
+      <x:c r="E6" s="66"/>
+      <x:c r="F6" s="113"/>
+      <x:c r="G6" s="67"/>
     </x:row>
     <x:row r="8" ht="23" customHeight="1">
       <x:c r="A8" s="11" t="str">
@@ -3234,68 +3450,68 @@
       </x:c>
     </x:row>
     <x:row r="10">
-      <x:c r="A10" s="82" t="str"/>
-      <x:c r="B10" s="83" t="str"/>
-      <x:c r="C10" s="91" t="str"/>
-      <x:c r="D10" s="83" t="str"/>
-      <x:c r="E10" s="83" t="str"/>
-      <x:c r="F10" s="83" t="str"/>
-      <x:c r="G10" s="84" t="str">
+      <x:c r="A10" s="85" t="str"/>
+      <x:c r="B10" s="86" t="str"/>
+      <x:c r="C10" s="94" t="str"/>
+      <x:c r="D10" s="86" t="str"/>
+      <x:c r="E10" s="86" t="str"/>
+      <x:c r="F10" s="86" t="str"/>
+      <x:c r="G10" s="87" t="str">
         <x:v>Not reviewed</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
-      <x:c r="A11" s="85" t="str"/>
-      <x:c r="B11" s="86" t="str"/>
-      <x:c r="C11" s="92" t="str"/>
-      <x:c r="D11" s="86" t="str"/>
-      <x:c r="E11" s="86" t="str"/>
-      <x:c r="F11" s="86" t="str"/>
-      <x:c r="G11" s="87" t="str">
+      <x:c r="A11" s="88" t="str"/>
+      <x:c r="B11" s="89" t="str"/>
+      <x:c r="C11" s="95" t="str"/>
+      <x:c r="D11" s="89" t="str"/>
+      <x:c r="E11" s="89" t="str"/>
+      <x:c r="F11" s="89" t="str"/>
+      <x:c r="G11" s="90" t="str">
         <x:v>Not reviewed</x:v>
       </x:c>
     </x:row>
     <x:row r="12">
-      <x:c r="A12" s="85" t="str"/>
-      <x:c r="B12" s="86" t="str"/>
-      <x:c r="C12" s="92" t="str"/>
-      <x:c r="D12" s="86" t="str"/>
-      <x:c r="E12" s="86" t="str"/>
-      <x:c r="F12" s="86" t="str"/>
-      <x:c r="G12" s="87" t="str">
+      <x:c r="A12" s="88" t="str"/>
+      <x:c r="B12" s="89" t="str"/>
+      <x:c r="C12" s="95" t="str"/>
+      <x:c r="D12" s="89" t="str"/>
+      <x:c r="E12" s="89" t="str"/>
+      <x:c r="F12" s="89" t="str"/>
+      <x:c r="G12" s="90" t="str">
         <x:v>Not reviewed</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
-      <x:c r="A13" s="85" t="str"/>
-      <x:c r="B13" s="86" t="str"/>
-      <x:c r="C13" s="92" t="str"/>
-      <x:c r="D13" s="86" t="str"/>
-      <x:c r="E13" s="86" t="str"/>
-      <x:c r="F13" s="86" t="str"/>
-      <x:c r="G13" s="87" t="str">
+      <x:c r="A13" s="88" t="str"/>
+      <x:c r="B13" s="89" t="str"/>
+      <x:c r="C13" s="95" t="str"/>
+      <x:c r="D13" s="89" t="str"/>
+      <x:c r="E13" s="89" t="str"/>
+      <x:c r="F13" s="89" t="str"/>
+      <x:c r="G13" s="90" t="str">
         <x:v>Not reviewed</x:v>
       </x:c>
     </x:row>
     <x:row r="14">
-      <x:c r="A14" s="85" t="str"/>
-      <x:c r="B14" s="86" t="str"/>
-      <x:c r="C14" s="92" t="str"/>
-      <x:c r="D14" s="86" t="str"/>
-      <x:c r="E14" s="86" t="str"/>
-      <x:c r="F14" s="86" t="str"/>
-      <x:c r="G14" s="87" t="str">
+      <x:c r="A14" s="88" t="str"/>
+      <x:c r="B14" s="89" t="str"/>
+      <x:c r="C14" s="95" t="str"/>
+      <x:c r="D14" s="89" t="str"/>
+      <x:c r="E14" s="89" t="str"/>
+      <x:c r="F14" s="89" t="str"/>
+      <x:c r="G14" s="90" t="str">
         <x:v>Not reviewed</x:v>
       </x:c>
     </x:row>
     <x:row r="15">
-      <x:c r="A15" s="88" t="str"/>
-      <x:c r="B15" s="89" t="str"/>
-      <x:c r="C15" s="93" t="str"/>
-      <x:c r="D15" s="89" t="str"/>
-      <x:c r="E15" s="89" t="str"/>
-      <x:c r="F15" s="89" t="str"/>
-      <x:c r="G15" s="90" t="str">
+      <x:c r="A15" s="91" t="str"/>
+      <x:c r="B15" s="92" t="str"/>
+      <x:c r="C15" s="96" t="str"/>
+      <x:c r="D15" s="92" t="str"/>
+      <x:c r="E15" s="92" t="str"/>
+      <x:c r="F15" s="92" t="str"/>
+      <x:c r="G15" s="93" t="str">
         <x:v>Not reviewed</x:v>
       </x:c>
     </x:row>
@@ -3333,13 +3549,13 @@
       <x:c r="G20" s="37"/>
     </x:row>
     <x:row r="21" ht="42" customHeight="1">
-      <x:c r="A21" s="63"/>
-      <x:c r="B21" s="110"/>
-      <x:c r="C21" s="110"/>
-      <x:c r="D21" s="110"/>
-      <x:c r="E21" s="110"/>
-      <x:c r="F21" s="110"/>
-      <x:c r="G21" s="64"/>
+      <x:c r="A21" s="66"/>
+      <x:c r="B21" s="113"/>
+      <x:c r="C21" s="113"/>
+      <x:c r="D21" s="113"/>
+      <x:c r="E21" s="113"/>
+      <x:c r="F21" s="113"/>
+      <x:c r="G21" s="67"/>
     </x:row>
     <x:row r="23" ht="23" customHeight="1">
       <x:c r="A23" s="11" t="str">
@@ -3355,7 +3571,7 @@
     </x:row>
     <x:row r="24">
       <x:c r="A24" s="21" t="str">
-        <x:v>Committee seat</x:v>
+        <x:v>Member slot</x:v>
       </x:c>
       <x:c r="B24" s="21" t="str">
         <x:v>Member name</x:v>
@@ -3377,66 +3593,76 @@
       </x:c>
     </x:row>
     <x:row r="25">
-      <x:c r="A25" s="114" t="str">
-        <x:v>Client &amp; Macro</x:v>
-      </x:c>
-      <x:c r="B25" s="82" t="str"/>
-      <x:c r="C25" s="83" t="str"/>
-      <x:c r="D25" s="83" t="str"/>
-      <x:c r="E25" s="83" t="str"/>
-      <x:c r="F25" s="83" t="str"/>
-      <x:c r="G25" s="84" t="str"/>
+      <x:c r="A25" s="117" t="str">
+        <x:v>Member 1</x:v>
+      </x:c>
+      <x:c r="B25" s="121" t="str">
+        <x:f>IF('COMMITTEE ROSTER'!B18="","",'COMMITTEE ROSTER'!B18)</x:f>
+      </x:c>
+      <x:c r="C25" s="86" t="str"/>
+      <x:c r="D25" s="86" t="str"/>
+      <x:c r="E25" s="86" t="str"/>
+      <x:c r="F25" s="86" t="str"/>
+      <x:c r="G25" s="87" t="str"/>
     </x:row>
     <x:row r="26">
-      <x:c r="A26" s="114" t="str">
-        <x:v>Fixed Income</x:v>
-      </x:c>
-      <x:c r="B26" s="85" t="str"/>
-      <x:c r="C26" s="86" t="str"/>
-      <x:c r="D26" s="86" t="str"/>
-      <x:c r="E26" s="86" t="str"/>
-      <x:c r="F26" s="86" t="str"/>
-      <x:c r="G26" s="87" t="str"/>
+      <x:c r="A26" s="117" t="str">
+        <x:v>Member 2</x:v>
+      </x:c>
+      <x:c r="B26" s="122" t="str">
+        <x:f>IF('COMMITTEE ROSTER'!B19="","",'COMMITTEE ROSTER'!B19)</x:f>
+      </x:c>
+      <x:c r="C26" s="89" t="str"/>
+      <x:c r="D26" s="89" t="str"/>
+      <x:c r="E26" s="89" t="str"/>
+      <x:c r="F26" s="89" t="str"/>
+      <x:c r="G26" s="90" t="str"/>
     </x:row>
     <x:row r="27">
-      <x:c r="A27" s="114" t="str">
-        <x:v>Equity</x:v>
-      </x:c>
-      <x:c r="B27" s="85" t="str"/>
-      <x:c r="C27" s="86" t="str"/>
-      <x:c r="D27" s="86" t="str"/>
-      <x:c r="E27" s="86" t="str"/>
-      <x:c r="F27" s="86" t="str"/>
-      <x:c r="G27" s="87" t="str"/>
+      <x:c r="A27" s="117" t="str">
+        <x:v>Member 3</x:v>
+      </x:c>
+      <x:c r="B27" s="122" t="str">
+        <x:f>IF('COMMITTEE ROSTER'!B20="","",'COMMITTEE ROSTER'!B20)</x:f>
+      </x:c>
+      <x:c r="C27" s="89" t="str"/>
+      <x:c r="D27" s="89" t="str"/>
+      <x:c r="E27" s="89" t="str"/>
+      <x:c r="F27" s="89" t="str"/>
+      <x:c r="G27" s="90" t="str"/>
     </x:row>
     <x:row r="28">
-      <x:c r="A28" s="114" t="str">
-        <x:v>Portfolio Manager</x:v>
-      </x:c>
-      <x:c r="B28" s="85" t="str"/>
-      <x:c r="C28" s="86" t="str"/>
-      <x:c r="D28" s="86" t="str"/>
-      <x:c r="E28" s="86" t="str"/>
-      <x:c r="F28" s="86" t="str"/>
-      <x:c r="G28" s="87" t="str"/>
+      <x:c r="A28" s="117" t="str">
+        <x:v>Member 4</x:v>
+      </x:c>
+      <x:c r="B28" s="122" t="str">
+        <x:f>IF('COMMITTEE ROSTER'!B21="","",'COMMITTEE ROSTER'!B21)</x:f>
+      </x:c>
+      <x:c r="C28" s="89" t="str"/>
+      <x:c r="D28" s="89" t="str"/>
+      <x:c r="E28" s="89" t="str"/>
+      <x:c r="F28" s="89" t="str"/>
+      <x:c r="G28" s="90" t="str"/>
     </x:row>
     <x:row r="29">
-      <x:c r="A29" s="114" t="str">
-        <x:v>Risk &amp; Derivatives</x:v>
-      </x:c>
-      <x:c r="B29" s="88" t="str"/>
-      <x:c r="C29" s="89" t="str"/>
-      <x:c r="D29" s="89" t="str"/>
-      <x:c r="E29" s="89" t="str"/>
-      <x:c r="F29" s="89" t="str"/>
-      <x:c r="G29" s="90" t="str"/>
+      <x:c r="A29" s="117" t="str">
+        <x:v>Member 5</x:v>
+      </x:c>
+      <x:c r="B29" s="123" t="str">
+        <x:f>IF('COMMITTEE ROSTER'!B22="","",'COMMITTEE ROSTER'!B22)</x:f>
+      </x:c>
+      <x:c r="C29" s="92" t="str"/>
+      <x:c r="D29" s="92" t="str"/>
+      <x:c r="E29" s="92" t="str"/>
+      <x:c r="F29" s="92" t="str"/>
+      <x:c r="G29" s="93" t="str"/>
     </x:row>
     <x:row r="30">
       <x:c r="A30" s="25" t="str">
         <x:v>Decision status</x:v>
       </x:c>
       <x:c r="B30" s="28" t="str">
-        <x:f>IF(COUNTIF(C25:C29,"Revise")+COUNTIF(C25:C29,"Reject")&gt;0,"REVISION REQUIRED",IF(COUNTIF(C25:C29,"Approve")=5,"APPROVED","INCOMPLETE"))</x:f>
+        <x:f>IF('COMMITTEE ROSTER'!B23&lt;&gt;"READY","INCOMPLETE",IF(COUNTIF(C25:C29,"Revise")+COUNTIF(C25:C29,"Reject")&gt;0,"REVISION REQUIRED",IF(COUNTIF(C25:C29,"Approve")='COMMITTEE ROSTER'!E19,"APPROVED","INCOMPLETE")))</x:f>
         <x:v>INCOMPLETE</x:v>
       </x:c>
       <x:c r="C30" s="29"/>
@@ -3454,22 +3680,22 @@
       <x:c r="H32" s="11"/>
     </x:row>
     <x:row r="33" ht="34" customHeight="1">
-      <x:c r="A33" s="82"/>
-      <x:c r="B33" s="83"/>
-      <x:c r="C33" s="83"/>
-      <x:c r="D33" s="83"/>
-      <x:c r="E33" s="83"/>
-      <x:c r="F33" s="83"/>
-      <x:c r="G33" s="84"/>
+      <x:c r="A33" s="85"/>
+      <x:c r="B33" s="86"/>
+      <x:c r="C33" s="86"/>
+      <x:c r="D33" s="86"/>
+      <x:c r="E33" s="86"/>
+      <x:c r="F33" s="86"/>
+      <x:c r="G33" s="87"/>
     </x:row>
     <x:row r="34" ht="34" customHeight="1">
-      <x:c r="A34" s="88"/>
-      <x:c r="B34" s="89"/>
-      <x:c r="C34" s="89"/>
-      <x:c r="D34" s="89"/>
-      <x:c r="E34" s="89"/>
-      <x:c r="F34" s="89"/>
-      <x:c r="G34" s="90"/>
+      <x:c r="A34" s="91"/>
+      <x:c r="B34" s="92"/>
+      <x:c r="C34" s="92"/>
+      <x:c r="D34" s="92"/>
+      <x:c r="E34" s="92"/>
+      <x:c r="F34" s="92"/>
+      <x:c r="G34" s="93"/>
     </x:row>
     <x:row r="36" ht="23" customHeight="1">
       <x:c r="A36" s="11" t="str">
@@ -3507,70 +3733,70 @@
       </x:c>
     </x:row>
     <x:row r="38">
-      <x:c r="A38" s="82" t="str"/>
-      <x:c r="B38" s="83" t="str"/>
-      <x:c r="C38" s="91" t="str"/>
-      <x:c r="D38" s="83" t="str"/>
-      <x:c r="E38" s="83" t="str">
+      <x:c r="A38" s="85" t="str"/>
+      <x:c r="B38" s="86" t="str"/>
+      <x:c r="C38" s="94" t="str"/>
+      <x:c r="D38" s="86" t="str"/>
+      <x:c r="E38" s="86" t="str">
         <x:v>Open</x:v>
       </x:c>
-      <x:c r="F38" s="83" t="str"/>
-      <x:c r="G38" s="84" t="str"/>
+      <x:c r="F38" s="86" t="str"/>
+      <x:c r="G38" s="87" t="str"/>
     </x:row>
     <x:row r="39">
-      <x:c r="A39" s="85" t="str"/>
-      <x:c r="B39" s="86" t="str"/>
-      <x:c r="C39" s="92" t="str"/>
-      <x:c r="D39" s="86" t="str"/>
-      <x:c r="E39" s="86" t="str">
+      <x:c r="A39" s="88" t="str"/>
+      <x:c r="B39" s="89" t="str"/>
+      <x:c r="C39" s="95" t="str"/>
+      <x:c r="D39" s="89" t="str"/>
+      <x:c r="E39" s="89" t="str">
         <x:v>Open</x:v>
       </x:c>
-      <x:c r="F39" s="86" t="str"/>
-      <x:c r="G39" s="87" t="str"/>
+      <x:c r="F39" s="89" t="str"/>
+      <x:c r="G39" s="90" t="str"/>
     </x:row>
     <x:row r="40">
-      <x:c r="A40" s="85" t="str"/>
-      <x:c r="B40" s="86" t="str"/>
-      <x:c r="C40" s="92" t="str"/>
-      <x:c r="D40" s="86" t="str"/>
-      <x:c r="E40" s="86" t="str">
+      <x:c r="A40" s="88" t="str"/>
+      <x:c r="B40" s="89" t="str"/>
+      <x:c r="C40" s="95" t="str"/>
+      <x:c r="D40" s="89" t="str"/>
+      <x:c r="E40" s="89" t="str">
         <x:v>Open</x:v>
       </x:c>
-      <x:c r="F40" s="86" t="str"/>
-      <x:c r="G40" s="87" t="str"/>
+      <x:c r="F40" s="89" t="str"/>
+      <x:c r="G40" s="90" t="str"/>
     </x:row>
     <x:row r="41">
-      <x:c r="A41" s="85" t="str"/>
-      <x:c r="B41" s="86" t="str"/>
-      <x:c r="C41" s="92" t="str"/>
-      <x:c r="D41" s="86" t="str"/>
-      <x:c r="E41" s="86" t="str">
+      <x:c r="A41" s="88" t="str"/>
+      <x:c r="B41" s="89" t="str"/>
+      <x:c r="C41" s="95" t="str"/>
+      <x:c r="D41" s="89" t="str"/>
+      <x:c r="E41" s="89" t="str">
         <x:v>Open</x:v>
       </x:c>
-      <x:c r="F41" s="86" t="str"/>
-      <x:c r="G41" s="87" t="str"/>
+      <x:c r="F41" s="89" t="str"/>
+      <x:c r="G41" s="90" t="str"/>
     </x:row>
     <x:row r="42">
-      <x:c r="A42" s="88" t="str"/>
-      <x:c r="B42" s="89" t="str"/>
-      <x:c r="C42" s="93" t="str"/>
-      <x:c r="D42" s="89" t="str"/>
-      <x:c r="E42" s="89" t="str">
+      <x:c r="A42" s="91" t="str"/>
+      <x:c r="B42" s="92" t="str"/>
+      <x:c r="C42" s="96" t="str"/>
+      <x:c r="D42" s="92" t="str"/>
+      <x:c r="E42" s="92" t="str">
         <x:v>Open</x:v>
       </x:c>
-      <x:c r="F42" s="89" t="str"/>
-      <x:c r="G42" s="90" t="str"/>
+      <x:c r="F42" s="92" t="str"/>
+      <x:c r="G42" s="93" t="str"/>
     </x:row>
     <x:row r="44" ht="32" customHeight="1">
-      <x:c r="A44" s="104" t="str">
-        <x:v>Approval requires five Approve votes. Any Revise or Reject vote produces REVISION REQUIRED; document the change and reconvene before the next gate.</x:v>
-      </x:c>
-      <x:c r="B44" s="104"/>
-      <x:c r="C44" s="104"/>
-      <x:c r="D44" s="104"/>
-      <x:c r="E44" s="104"/>
-      <x:c r="F44" s="104"/>
-      <x:c r="G44" s="104"/>
+      <x:c r="A44" s="107" t="str">
+        <x:v>Approval requires one Approve vote from each of the four or five distinct members listed on the roster. A dual-role member votes once. Any Revise or Reject vote requires revision and a new meeting.</x:v>
+      </x:c>
+      <x:c r="B44" s="107"/>
+      <x:c r="C44" s="107"/>
+      <x:c r="D44" s="107"/>
+      <x:c r="E44" s="107"/>
+      <x:c r="F44" s="107"/>
+      <x:c r="G44" s="107"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -3595,9 +3821,9 @@
     <x:mergeCell ref="A44:G44"/>
   </x:mergeCells>
   <x:conditionalFormatting sqref="B30:C30">
-    <x:cfRule type="containsText" dxfId="34" priority="1" operator="containsText" text="APPROVED"/>
-    <x:cfRule type="containsText" dxfId="35" priority="2" operator="containsText" text="REVISION"/>
-    <x:cfRule type="containsText" dxfId="36" priority="3" operator="containsText" text="INCOMPLETE"/>
+    <x:cfRule type="containsText" dxfId="41" priority="1" operator="containsText" text="APPROVED"/>
+    <x:cfRule type="containsText" dxfId="42" priority="2" operator="containsText" text="REVISION"/>
+    <x:cfRule type="containsText" dxfId="43" priority="3" operator="containsText" text="INCOMPLETE"/>
   </x:conditionalFormatting>
   <x:dataValidations count="3">
     <x:dataValidation type="list" sqref="G10:G15">
@@ -3642,7 +3868,7 @@
     </x:row>
     <x:row r="2" ht="24" customHeight="1">
       <x:c r="A2" s="6" t="str">
-        <x:v>Build &amp; Challenge | All five committee members review, vote, and sign this record.</x:v>
+        <x:v>Build &amp; Challenge | All four or five members review and cast one vote each.</x:v>
       </x:c>
       <x:c r="B2" s="6"/>
       <x:c r="C2" s="6"/>
@@ -3656,21 +3882,21 @@
       <x:c r="A4" s="25" t="str">
         <x:v>Team / Committee Name</x:v>
       </x:c>
-      <x:c r="B4" s="82"/>
-      <x:c r="C4" s="84"/>
+      <x:c r="B4" s="85"/>
+      <x:c r="C4" s="87"/>
       <x:c r="D4" s="25" t="str">
         <x:v>Recorder</x:v>
       </x:c>
-      <x:c r="E4" s="63"/>
-      <x:c r="F4" s="110"/>
-      <x:c r="G4" s="64"/>
+      <x:c r="E4" s="66"/>
+      <x:c r="F4" s="113"/>
+      <x:c r="G4" s="67"/>
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="25" t="str">
         <x:v>Client name / case</x:v>
       </x:c>
-      <x:c r="B5" s="85"/>
-      <x:c r="C5" s="87"/>
+      <x:c r="B5" s="88"/>
+      <x:c r="C5" s="90"/>
       <x:c r="D5" s="25" t="str">
         <x:v>Gate</x:v>
       </x:c>
@@ -3684,14 +3910,14 @@
       <x:c r="A6" s="25" t="str">
         <x:v>Meeting Date</x:v>
       </x:c>
-      <x:c r="B6" s="111"/>
-      <x:c r="C6" s="112"/>
+      <x:c r="B6" s="114"/>
+      <x:c r="C6" s="115"/>
       <x:c r="D6" s="25" t="str">
         <x:v>Meeting Chair</x:v>
       </x:c>
-      <x:c r="E6" s="63"/>
-      <x:c r="F6" s="110"/>
-      <x:c r="G6" s="64"/>
+      <x:c r="E6" s="66"/>
+      <x:c r="F6" s="113"/>
+      <x:c r="G6" s="67"/>
     </x:row>
     <x:row r="8" ht="23" customHeight="1">
       <x:c r="A8" s="11" t="str">
@@ -3729,68 +3955,68 @@
       </x:c>
     </x:row>
     <x:row r="10">
-      <x:c r="A10" s="82" t="str"/>
-      <x:c r="B10" s="83" t="str"/>
-      <x:c r="C10" s="91" t="str"/>
-      <x:c r="D10" s="83" t="str"/>
-      <x:c r="E10" s="83" t="str"/>
-      <x:c r="F10" s="83" t="str"/>
-      <x:c r="G10" s="84" t="str">
+      <x:c r="A10" s="85" t="str"/>
+      <x:c r="B10" s="86" t="str"/>
+      <x:c r="C10" s="94" t="str"/>
+      <x:c r="D10" s="86" t="str"/>
+      <x:c r="E10" s="86" t="str"/>
+      <x:c r="F10" s="86" t="str"/>
+      <x:c r="G10" s="87" t="str">
         <x:v>Not reviewed</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
-      <x:c r="A11" s="85" t="str"/>
-      <x:c r="B11" s="86" t="str"/>
-      <x:c r="C11" s="92" t="str"/>
-      <x:c r="D11" s="86" t="str"/>
-      <x:c r="E11" s="86" t="str"/>
-      <x:c r="F11" s="86" t="str"/>
-      <x:c r="G11" s="87" t="str">
+      <x:c r="A11" s="88" t="str"/>
+      <x:c r="B11" s="89" t="str"/>
+      <x:c r="C11" s="95" t="str"/>
+      <x:c r="D11" s="89" t="str"/>
+      <x:c r="E11" s="89" t="str"/>
+      <x:c r="F11" s="89" t="str"/>
+      <x:c r="G11" s="90" t="str">
         <x:v>Not reviewed</x:v>
       </x:c>
     </x:row>
     <x:row r="12">
-      <x:c r="A12" s="85" t="str"/>
-      <x:c r="B12" s="86" t="str"/>
-      <x:c r="C12" s="92" t="str"/>
-      <x:c r="D12" s="86" t="str"/>
-      <x:c r="E12" s="86" t="str"/>
-      <x:c r="F12" s="86" t="str"/>
-      <x:c r="G12" s="87" t="str">
+      <x:c r="A12" s="88" t="str"/>
+      <x:c r="B12" s="89" t="str"/>
+      <x:c r="C12" s="95" t="str"/>
+      <x:c r="D12" s="89" t="str"/>
+      <x:c r="E12" s="89" t="str"/>
+      <x:c r="F12" s="89" t="str"/>
+      <x:c r="G12" s="90" t="str">
         <x:v>Not reviewed</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
-      <x:c r="A13" s="85" t="str"/>
-      <x:c r="B13" s="86" t="str"/>
-      <x:c r="C13" s="92" t="str"/>
-      <x:c r="D13" s="86" t="str"/>
-      <x:c r="E13" s="86" t="str"/>
-      <x:c r="F13" s="86" t="str"/>
-      <x:c r="G13" s="87" t="str">
+      <x:c r="A13" s="88" t="str"/>
+      <x:c r="B13" s="89" t="str"/>
+      <x:c r="C13" s="95" t="str"/>
+      <x:c r="D13" s="89" t="str"/>
+      <x:c r="E13" s="89" t="str"/>
+      <x:c r="F13" s="89" t="str"/>
+      <x:c r="G13" s="90" t="str">
         <x:v>Not reviewed</x:v>
       </x:c>
     </x:row>
     <x:row r="14">
-      <x:c r="A14" s="85" t="str"/>
-      <x:c r="B14" s="86" t="str"/>
-      <x:c r="C14" s="92" t="str"/>
-      <x:c r="D14" s="86" t="str"/>
-      <x:c r="E14" s="86" t="str"/>
-      <x:c r="F14" s="86" t="str"/>
-      <x:c r="G14" s="87" t="str">
+      <x:c r="A14" s="88" t="str"/>
+      <x:c r="B14" s="89" t="str"/>
+      <x:c r="C14" s="95" t="str"/>
+      <x:c r="D14" s="89" t="str"/>
+      <x:c r="E14" s="89" t="str"/>
+      <x:c r="F14" s="89" t="str"/>
+      <x:c r="G14" s="90" t="str">
         <x:v>Not reviewed</x:v>
       </x:c>
     </x:row>
     <x:row r="15">
-      <x:c r="A15" s="88" t="str"/>
-      <x:c r="B15" s="89" t="str"/>
-      <x:c r="C15" s="93" t="str"/>
-      <x:c r="D15" s="89" t="str"/>
-      <x:c r="E15" s="89" t="str"/>
-      <x:c r="F15" s="89" t="str"/>
-      <x:c r="G15" s="90" t="str">
+      <x:c r="A15" s="91" t="str"/>
+      <x:c r="B15" s="92" t="str"/>
+      <x:c r="C15" s="96" t="str"/>
+      <x:c r="D15" s="92" t="str"/>
+      <x:c r="E15" s="92" t="str"/>
+      <x:c r="F15" s="92" t="str"/>
+      <x:c r="G15" s="93" t="str">
         <x:v>Not reviewed</x:v>
       </x:c>
     </x:row>
@@ -3828,13 +4054,13 @@
       <x:c r="G20" s="37"/>
     </x:row>
     <x:row r="21" ht="42" customHeight="1">
-      <x:c r="A21" s="63"/>
-      <x:c r="B21" s="110"/>
-      <x:c r="C21" s="110"/>
-      <x:c r="D21" s="110"/>
-      <x:c r="E21" s="110"/>
-      <x:c r="F21" s="110"/>
-      <x:c r="G21" s="64"/>
+      <x:c r="A21" s="66"/>
+      <x:c r="B21" s="113"/>
+      <x:c r="C21" s="113"/>
+      <x:c r="D21" s="113"/>
+      <x:c r="E21" s="113"/>
+      <x:c r="F21" s="113"/>
+      <x:c r="G21" s="67"/>
     </x:row>
     <x:row r="23" ht="23" customHeight="1">
       <x:c r="A23" s="11" t="str">
@@ -3850,7 +4076,7 @@
     </x:row>
     <x:row r="24">
       <x:c r="A24" s="21" t="str">
-        <x:v>Committee seat</x:v>
+        <x:v>Member slot</x:v>
       </x:c>
       <x:c r="B24" s="21" t="str">
         <x:v>Member name</x:v>
@@ -3872,66 +4098,76 @@
       </x:c>
     </x:row>
     <x:row r="25">
-      <x:c r="A25" s="114" t="str">
-        <x:v>Client &amp; Macro</x:v>
-      </x:c>
-      <x:c r="B25" s="82" t="str"/>
-      <x:c r="C25" s="83" t="str"/>
-      <x:c r="D25" s="83" t="str"/>
-      <x:c r="E25" s="83" t="str"/>
-      <x:c r="F25" s="83" t="str"/>
-      <x:c r="G25" s="84" t="str"/>
+      <x:c r="A25" s="117" t="str">
+        <x:v>Member 1</x:v>
+      </x:c>
+      <x:c r="B25" s="121" t="str">
+        <x:f>IF('COMMITTEE ROSTER'!B18="","",'COMMITTEE ROSTER'!B18)</x:f>
+      </x:c>
+      <x:c r="C25" s="86" t="str"/>
+      <x:c r="D25" s="86" t="str"/>
+      <x:c r="E25" s="86" t="str"/>
+      <x:c r="F25" s="86" t="str"/>
+      <x:c r="G25" s="87" t="str"/>
     </x:row>
     <x:row r="26">
-      <x:c r="A26" s="114" t="str">
-        <x:v>Fixed Income</x:v>
-      </x:c>
-      <x:c r="B26" s="85" t="str"/>
-      <x:c r="C26" s="86" t="str"/>
-      <x:c r="D26" s="86" t="str"/>
-      <x:c r="E26" s="86" t="str"/>
-      <x:c r="F26" s="86" t="str"/>
-      <x:c r="G26" s="87" t="str"/>
+      <x:c r="A26" s="117" t="str">
+        <x:v>Member 2</x:v>
+      </x:c>
+      <x:c r="B26" s="122" t="str">
+        <x:f>IF('COMMITTEE ROSTER'!B19="","",'COMMITTEE ROSTER'!B19)</x:f>
+      </x:c>
+      <x:c r="C26" s="89" t="str"/>
+      <x:c r="D26" s="89" t="str"/>
+      <x:c r="E26" s="89" t="str"/>
+      <x:c r="F26" s="89" t="str"/>
+      <x:c r="G26" s="90" t="str"/>
     </x:row>
     <x:row r="27">
-      <x:c r="A27" s="114" t="str">
-        <x:v>Equity</x:v>
-      </x:c>
-      <x:c r="B27" s="85" t="str"/>
-      <x:c r="C27" s="86" t="str"/>
-      <x:c r="D27" s="86" t="str"/>
-      <x:c r="E27" s="86" t="str"/>
-      <x:c r="F27" s="86" t="str"/>
-      <x:c r="G27" s="87" t="str"/>
+      <x:c r="A27" s="117" t="str">
+        <x:v>Member 3</x:v>
+      </x:c>
+      <x:c r="B27" s="122" t="str">
+        <x:f>IF('COMMITTEE ROSTER'!B20="","",'COMMITTEE ROSTER'!B20)</x:f>
+      </x:c>
+      <x:c r="C27" s="89" t="str"/>
+      <x:c r="D27" s="89" t="str"/>
+      <x:c r="E27" s="89" t="str"/>
+      <x:c r="F27" s="89" t="str"/>
+      <x:c r="G27" s="90" t="str"/>
     </x:row>
     <x:row r="28">
-      <x:c r="A28" s="114" t="str">
-        <x:v>Portfolio Manager</x:v>
-      </x:c>
-      <x:c r="B28" s="85" t="str"/>
-      <x:c r="C28" s="86" t="str"/>
-      <x:c r="D28" s="86" t="str"/>
-      <x:c r="E28" s="86" t="str"/>
-      <x:c r="F28" s="86" t="str"/>
-      <x:c r="G28" s="87" t="str"/>
+      <x:c r="A28" s="117" t="str">
+        <x:v>Member 4</x:v>
+      </x:c>
+      <x:c r="B28" s="122" t="str">
+        <x:f>IF('COMMITTEE ROSTER'!B21="","",'COMMITTEE ROSTER'!B21)</x:f>
+      </x:c>
+      <x:c r="C28" s="89" t="str"/>
+      <x:c r="D28" s="89" t="str"/>
+      <x:c r="E28" s="89" t="str"/>
+      <x:c r="F28" s="89" t="str"/>
+      <x:c r="G28" s="90" t="str"/>
     </x:row>
     <x:row r="29">
-      <x:c r="A29" s="114" t="str">
-        <x:v>Risk &amp; Derivatives</x:v>
-      </x:c>
-      <x:c r="B29" s="88" t="str"/>
-      <x:c r="C29" s="89" t="str"/>
-      <x:c r="D29" s="89" t="str"/>
-      <x:c r="E29" s="89" t="str"/>
-      <x:c r="F29" s="89" t="str"/>
-      <x:c r="G29" s="90" t="str"/>
+      <x:c r="A29" s="117" t="str">
+        <x:v>Member 5</x:v>
+      </x:c>
+      <x:c r="B29" s="123" t="str">
+        <x:f>IF('COMMITTEE ROSTER'!B22="","",'COMMITTEE ROSTER'!B22)</x:f>
+      </x:c>
+      <x:c r="C29" s="92" t="str"/>
+      <x:c r="D29" s="92" t="str"/>
+      <x:c r="E29" s="92" t="str"/>
+      <x:c r="F29" s="92" t="str"/>
+      <x:c r="G29" s="93" t="str"/>
     </x:row>
     <x:row r="30">
       <x:c r="A30" s="25" t="str">
         <x:v>Decision status</x:v>
       </x:c>
       <x:c r="B30" s="28" t="str">
-        <x:f>IF(COUNTIF(C25:C29,"Revise")+COUNTIF(C25:C29,"Reject")&gt;0,"REVISION REQUIRED",IF(COUNTIF(C25:C29,"Approve")=5,"APPROVED","INCOMPLETE"))</x:f>
+        <x:f>IF('COMMITTEE ROSTER'!B23&lt;&gt;"READY","INCOMPLETE",IF(COUNTIF(C25:C29,"Revise")+COUNTIF(C25:C29,"Reject")&gt;0,"REVISION REQUIRED",IF(COUNTIF(C25:C29,"Approve")='COMMITTEE ROSTER'!E19,"APPROVED","INCOMPLETE")))</x:f>
         <x:v>INCOMPLETE</x:v>
       </x:c>
       <x:c r="C30" s="29"/>
@@ -3949,22 +4185,22 @@
       <x:c r="H32" s="11"/>
     </x:row>
     <x:row r="33" ht="34" customHeight="1">
-      <x:c r="A33" s="82"/>
-      <x:c r="B33" s="83"/>
-      <x:c r="C33" s="83"/>
-      <x:c r="D33" s="83"/>
-      <x:c r="E33" s="83"/>
-      <x:c r="F33" s="83"/>
-      <x:c r="G33" s="84"/>
+      <x:c r="A33" s="85"/>
+      <x:c r="B33" s="86"/>
+      <x:c r="C33" s="86"/>
+      <x:c r="D33" s="86"/>
+      <x:c r="E33" s="86"/>
+      <x:c r="F33" s="86"/>
+      <x:c r="G33" s="87"/>
     </x:row>
     <x:row r="34" ht="34" customHeight="1">
-      <x:c r="A34" s="88"/>
-      <x:c r="B34" s="89"/>
-      <x:c r="C34" s="89"/>
-      <x:c r="D34" s="89"/>
-      <x:c r="E34" s="89"/>
-      <x:c r="F34" s="89"/>
-      <x:c r="G34" s="90"/>
+      <x:c r="A34" s="91"/>
+      <x:c r="B34" s="92"/>
+      <x:c r="C34" s="92"/>
+      <x:c r="D34" s="92"/>
+      <x:c r="E34" s="92"/>
+      <x:c r="F34" s="92"/>
+      <x:c r="G34" s="93"/>
     </x:row>
     <x:row r="36" ht="23" customHeight="1">
       <x:c r="A36" s="11" t="str">
@@ -4002,70 +4238,70 @@
       </x:c>
     </x:row>
     <x:row r="38">
-      <x:c r="A38" s="82" t="str"/>
-      <x:c r="B38" s="83" t="str"/>
-      <x:c r="C38" s="91" t="str"/>
-      <x:c r="D38" s="83" t="str"/>
-      <x:c r="E38" s="83" t="str">
+      <x:c r="A38" s="85" t="str"/>
+      <x:c r="B38" s="86" t="str"/>
+      <x:c r="C38" s="94" t="str"/>
+      <x:c r="D38" s="86" t="str"/>
+      <x:c r="E38" s="86" t="str">
         <x:v>Open</x:v>
       </x:c>
-      <x:c r="F38" s="83" t="str"/>
-      <x:c r="G38" s="84" t="str"/>
+      <x:c r="F38" s="86" t="str"/>
+      <x:c r="G38" s="87" t="str"/>
     </x:row>
     <x:row r="39">
-      <x:c r="A39" s="85" t="str"/>
-      <x:c r="B39" s="86" t="str"/>
-      <x:c r="C39" s="92" t="str"/>
-      <x:c r="D39" s="86" t="str"/>
-      <x:c r="E39" s="86" t="str">
+      <x:c r="A39" s="88" t="str"/>
+      <x:c r="B39" s="89" t="str"/>
+      <x:c r="C39" s="95" t="str"/>
+      <x:c r="D39" s="89" t="str"/>
+      <x:c r="E39" s="89" t="str">
         <x:v>Open</x:v>
       </x:c>
-      <x:c r="F39" s="86" t="str"/>
-      <x:c r="G39" s="87" t="str"/>
+      <x:c r="F39" s="89" t="str"/>
+      <x:c r="G39" s="90" t="str"/>
     </x:row>
     <x:row r="40">
-      <x:c r="A40" s="85" t="str"/>
-      <x:c r="B40" s="86" t="str"/>
-      <x:c r="C40" s="92" t="str"/>
-      <x:c r="D40" s="86" t="str"/>
-      <x:c r="E40" s="86" t="str">
+      <x:c r="A40" s="88" t="str"/>
+      <x:c r="B40" s="89" t="str"/>
+      <x:c r="C40" s="95" t="str"/>
+      <x:c r="D40" s="89" t="str"/>
+      <x:c r="E40" s="89" t="str">
         <x:v>Open</x:v>
       </x:c>
-      <x:c r="F40" s="86" t="str"/>
-      <x:c r="G40" s="87" t="str"/>
+      <x:c r="F40" s="89" t="str"/>
+      <x:c r="G40" s="90" t="str"/>
     </x:row>
     <x:row r="41">
-      <x:c r="A41" s="85" t="str"/>
-      <x:c r="B41" s="86" t="str"/>
-      <x:c r="C41" s="92" t="str"/>
-      <x:c r="D41" s="86" t="str"/>
-      <x:c r="E41" s="86" t="str">
+      <x:c r="A41" s="88" t="str"/>
+      <x:c r="B41" s="89" t="str"/>
+      <x:c r="C41" s="95" t="str"/>
+      <x:c r="D41" s="89" t="str"/>
+      <x:c r="E41" s="89" t="str">
         <x:v>Open</x:v>
       </x:c>
-      <x:c r="F41" s="86" t="str"/>
-      <x:c r="G41" s="87" t="str"/>
+      <x:c r="F41" s="89" t="str"/>
+      <x:c r="G41" s="90" t="str"/>
     </x:row>
     <x:row r="42">
-      <x:c r="A42" s="88" t="str"/>
-      <x:c r="B42" s="89" t="str"/>
-      <x:c r="C42" s="93" t="str"/>
-      <x:c r="D42" s="89" t="str"/>
-      <x:c r="E42" s="89" t="str">
+      <x:c r="A42" s="91" t="str"/>
+      <x:c r="B42" s="92" t="str"/>
+      <x:c r="C42" s="96" t="str"/>
+      <x:c r="D42" s="92" t="str"/>
+      <x:c r="E42" s="92" t="str">
         <x:v>Open</x:v>
       </x:c>
-      <x:c r="F42" s="89" t="str"/>
-      <x:c r="G42" s="90" t="str"/>
+      <x:c r="F42" s="92" t="str"/>
+      <x:c r="G42" s="93" t="str"/>
     </x:row>
     <x:row r="44" ht="32" customHeight="1">
-      <x:c r="A44" s="104" t="str">
-        <x:v>Approval requires five Approve votes. Any Revise or Reject vote produces REVISION REQUIRED; document the change and reconvene before the next gate.</x:v>
-      </x:c>
-      <x:c r="B44" s="104"/>
-      <x:c r="C44" s="104"/>
-      <x:c r="D44" s="104"/>
-      <x:c r="E44" s="104"/>
-      <x:c r="F44" s="104"/>
-      <x:c r="G44" s="104"/>
+      <x:c r="A44" s="107" t="str">
+        <x:v>Approval requires one Approve vote from each of the four or five distinct members listed on the roster. A dual-role member votes once. Any Revise or Reject vote requires revision and a new meeting.</x:v>
+      </x:c>
+      <x:c r="B44" s="107"/>
+      <x:c r="C44" s="107"/>
+      <x:c r="D44" s="107"/>
+      <x:c r="E44" s="107"/>
+      <x:c r="F44" s="107"/>
+      <x:c r="G44" s="107"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -4090,9 +4326,9 @@
     <x:mergeCell ref="A44:G44"/>
   </x:mergeCells>
   <x:conditionalFormatting sqref="B30:C30">
-    <x:cfRule type="containsText" dxfId="37" priority="1" operator="containsText" text="APPROVED"/>
-    <x:cfRule type="containsText" dxfId="38" priority="2" operator="containsText" text="REVISION"/>
-    <x:cfRule type="containsText" dxfId="39" priority="3" operator="containsText" text="INCOMPLETE"/>
+    <x:cfRule type="containsText" dxfId="44" priority="1" operator="containsText" text="APPROVED"/>
+    <x:cfRule type="containsText" dxfId="45" priority="2" operator="containsText" text="REVISION"/>
+    <x:cfRule type="containsText" dxfId="46" priority="3" operator="containsText" text="INCOMPLETE"/>
   </x:conditionalFormatting>
   <x:dataValidations count="3">
     <x:dataValidation type="list" sqref="G10:G15">
@@ -4137,7 +4373,7 @@
     </x:row>
     <x:row r="2" ht="24" customHeight="1">
       <x:c r="A2" s="6" t="str">
-        <x:v>Build &amp; Challenge | All five committee members review, vote, and sign this record.</x:v>
+        <x:v>Build &amp; Challenge | All four or five members review and cast one vote each.</x:v>
       </x:c>
       <x:c r="B2" s="6"/>
       <x:c r="C2" s="6"/>
@@ -4151,21 +4387,21 @@
       <x:c r="A4" s="25" t="str">
         <x:v>Team / Committee Name</x:v>
       </x:c>
-      <x:c r="B4" s="82"/>
-      <x:c r="C4" s="84"/>
+      <x:c r="B4" s="85"/>
+      <x:c r="C4" s="87"/>
       <x:c r="D4" s="25" t="str">
         <x:v>Recorder</x:v>
       </x:c>
-      <x:c r="E4" s="63"/>
-      <x:c r="F4" s="110"/>
-      <x:c r="G4" s="64"/>
+      <x:c r="E4" s="66"/>
+      <x:c r="F4" s="113"/>
+      <x:c r="G4" s="67"/>
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="25" t="str">
         <x:v>Client name / case</x:v>
       </x:c>
-      <x:c r="B5" s="85"/>
-      <x:c r="C5" s="87"/>
+      <x:c r="B5" s="88"/>
+      <x:c r="C5" s="90"/>
       <x:c r="D5" s="25" t="str">
         <x:v>Gate</x:v>
       </x:c>
@@ -4179,14 +4415,14 @@
       <x:c r="A6" s="25" t="str">
         <x:v>Meeting Date</x:v>
       </x:c>
-      <x:c r="B6" s="111"/>
-      <x:c r="C6" s="112"/>
+      <x:c r="B6" s="114"/>
+      <x:c r="C6" s="115"/>
       <x:c r="D6" s="25" t="str">
         <x:v>Meeting Chair</x:v>
       </x:c>
-      <x:c r="E6" s="63"/>
-      <x:c r="F6" s="110"/>
-      <x:c r="G6" s="64"/>
+      <x:c r="E6" s="66"/>
+      <x:c r="F6" s="113"/>
+      <x:c r="G6" s="67"/>
     </x:row>
     <x:row r="8" ht="23" customHeight="1">
       <x:c r="A8" s="11" t="str">
@@ -4224,68 +4460,68 @@
       </x:c>
     </x:row>
     <x:row r="10">
-      <x:c r="A10" s="82" t="str"/>
-      <x:c r="B10" s="83" t="str"/>
-      <x:c r="C10" s="91" t="str"/>
-      <x:c r="D10" s="83" t="str"/>
-      <x:c r="E10" s="83" t="str"/>
-      <x:c r="F10" s="83" t="str"/>
-      <x:c r="G10" s="84" t="str">
+      <x:c r="A10" s="85" t="str"/>
+      <x:c r="B10" s="86" t="str"/>
+      <x:c r="C10" s="94" t="str"/>
+      <x:c r="D10" s="86" t="str"/>
+      <x:c r="E10" s="86" t="str"/>
+      <x:c r="F10" s="86" t="str"/>
+      <x:c r="G10" s="87" t="str">
         <x:v>Not reviewed</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
-      <x:c r="A11" s="85" t="str"/>
-      <x:c r="B11" s="86" t="str"/>
-      <x:c r="C11" s="92" t="str"/>
-      <x:c r="D11" s="86" t="str"/>
-      <x:c r="E11" s="86" t="str"/>
-      <x:c r="F11" s="86" t="str"/>
-      <x:c r="G11" s="87" t="str">
+      <x:c r="A11" s="88" t="str"/>
+      <x:c r="B11" s="89" t="str"/>
+      <x:c r="C11" s="95" t="str"/>
+      <x:c r="D11" s="89" t="str"/>
+      <x:c r="E11" s="89" t="str"/>
+      <x:c r="F11" s="89" t="str"/>
+      <x:c r="G11" s="90" t="str">
         <x:v>Not reviewed</x:v>
       </x:c>
     </x:row>
     <x:row r="12">
-      <x:c r="A12" s="85" t="str"/>
-      <x:c r="B12" s="86" t="str"/>
-      <x:c r="C12" s="92" t="str"/>
-      <x:c r="D12" s="86" t="str"/>
-      <x:c r="E12" s="86" t="str"/>
-      <x:c r="F12" s="86" t="str"/>
-      <x:c r="G12" s="87" t="str">
+      <x:c r="A12" s="88" t="str"/>
+      <x:c r="B12" s="89" t="str"/>
+      <x:c r="C12" s="95" t="str"/>
+      <x:c r="D12" s="89" t="str"/>
+      <x:c r="E12" s="89" t="str"/>
+      <x:c r="F12" s="89" t="str"/>
+      <x:c r="G12" s="90" t="str">
         <x:v>Not reviewed</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
-      <x:c r="A13" s="85" t="str"/>
-      <x:c r="B13" s="86" t="str"/>
-      <x:c r="C13" s="92" t="str"/>
-      <x:c r="D13" s="86" t="str"/>
-      <x:c r="E13" s="86" t="str"/>
-      <x:c r="F13" s="86" t="str"/>
-      <x:c r="G13" s="87" t="str">
+      <x:c r="A13" s="88" t="str"/>
+      <x:c r="B13" s="89" t="str"/>
+      <x:c r="C13" s="95" t="str"/>
+      <x:c r="D13" s="89" t="str"/>
+      <x:c r="E13" s="89" t="str"/>
+      <x:c r="F13" s="89" t="str"/>
+      <x:c r="G13" s="90" t="str">
         <x:v>Not reviewed</x:v>
       </x:c>
     </x:row>
     <x:row r="14">
-      <x:c r="A14" s="85" t="str"/>
-      <x:c r="B14" s="86" t="str"/>
-      <x:c r="C14" s="92" t="str"/>
-      <x:c r="D14" s="86" t="str"/>
-      <x:c r="E14" s="86" t="str"/>
-      <x:c r="F14" s="86" t="str"/>
-      <x:c r="G14" s="87" t="str">
+      <x:c r="A14" s="88" t="str"/>
+      <x:c r="B14" s="89" t="str"/>
+      <x:c r="C14" s="95" t="str"/>
+      <x:c r="D14" s="89" t="str"/>
+      <x:c r="E14" s="89" t="str"/>
+      <x:c r="F14" s="89" t="str"/>
+      <x:c r="G14" s="90" t="str">
         <x:v>Not reviewed</x:v>
       </x:c>
     </x:row>
     <x:row r="15">
-      <x:c r="A15" s="88" t="str"/>
-      <x:c r="B15" s="89" t="str"/>
-      <x:c r="C15" s="93" t="str"/>
-      <x:c r="D15" s="89" t="str"/>
-      <x:c r="E15" s="89" t="str"/>
-      <x:c r="F15" s="89" t="str"/>
-      <x:c r="G15" s="90" t="str">
+      <x:c r="A15" s="91" t="str"/>
+      <x:c r="B15" s="92" t="str"/>
+      <x:c r="C15" s="96" t="str"/>
+      <x:c r="D15" s="92" t="str"/>
+      <x:c r="E15" s="92" t="str"/>
+      <x:c r="F15" s="92" t="str"/>
+      <x:c r="G15" s="93" t="str">
         <x:v>Not reviewed</x:v>
       </x:c>
     </x:row>
@@ -4323,13 +4559,13 @@
       <x:c r="G20" s="37"/>
     </x:row>
     <x:row r="21" ht="42" customHeight="1">
-      <x:c r="A21" s="63"/>
-      <x:c r="B21" s="110"/>
-      <x:c r="C21" s="110"/>
-      <x:c r="D21" s="110"/>
-      <x:c r="E21" s="110"/>
-      <x:c r="F21" s="110"/>
-      <x:c r="G21" s="64"/>
+      <x:c r="A21" s="66"/>
+      <x:c r="B21" s="113"/>
+      <x:c r="C21" s="113"/>
+      <x:c r="D21" s="113"/>
+      <x:c r="E21" s="113"/>
+      <x:c r="F21" s="113"/>
+      <x:c r="G21" s="67"/>
     </x:row>
     <x:row r="23" ht="23" customHeight="1">
       <x:c r="A23" s="11" t="str">
@@ -4345,7 +4581,7 @@
     </x:row>
     <x:row r="24">
       <x:c r="A24" s="21" t="str">
-        <x:v>Committee seat</x:v>
+        <x:v>Member slot</x:v>
       </x:c>
       <x:c r="B24" s="21" t="str">
         <x:v>Member name</x:v>
@@ -4367,66 +4603,76 @@
       </x:c>
     </x:row>
     <x:row r="25">
-      <x:c r="A25" s="114" t="str">
-        <x:v>Client &amp; Macro</x:v>
-      </x:c>
-      <x:c r="B25" s="82" t="str"/>
-      <x:c r="C25" s="83" t="str"/>
-      <x:c r="D25" s="83" t="str"/>
-      <x:c r="E25" s="83" t="str"/>
-      <x:c r="F25" s="83" t="str"/>
-      <x:c r="G25" s="84" t="str"/>
+      <x:c r="A25" s="117" t="str">
+        <x:v>Member 1</x:v>
+      </x:c>
+      <x:c r="B25" s="121" t="str">
+        <x:f>IF('COMMITTEE ROSTER'!B18="","",'COMMITTEE ROSTER'!B18)</x:f>
+      </x:c>
+      <x:c r="C25" s="86" t="str"/>
+      <x:c r="D25" s="86" t="str"/>
+      <x:c r="E25" s="86" t="str"/>
+      <x:c r="F25" s="86" t="str"/>
+      <x:c r="G25" s="87" t="str"/>
     </x:row>
     <x:row r="26">
-      <x:c r="A26" s="114" t="str">
-        <x:v>Fixed Income</x:v>
-      </x:c>
-      <x:c r="B26" s="85" t="str"/>
-      <x:c r="C26" s="86" t="str"/>
-      <x:c r="D26" s="86" t="str"/>
-      <x:c r="E26" s="86" t="str"/>
-      <x:c r="F26" s="86" t="str"/>
-      <x:c r="G26" s="87" t="str"/>
+      <x:c r="A26" s="117" t="str">
+        <x:v>Member 2</x:v>
+      </x:c>
+      <x:c r="B26" s="122" t="str">
+        <x:f>IF('COMMITTEE ROSTER'!B19="","",'COMMITTEE ROSTER'!B19)</x:f>
+      </x:c>
+      <x:c r="C26" s="89" t="str"/>
+      <x:c r="D26" s="89" t="str"/>
+      <x:c r="E26" s="89" t="str"/>
+      <x:c r="F26" s="89" t="str"/>
+      <x:c r="G26" s="90" t="str"/>
     </x:row>
     <x:row r="27">
-      <x:c r="A27" s="114" t="str">
-        <x:v>Equity</x:v>
-      </x:c>
-      <x:c r="B27" s="85" t="str"/>
-      <x:c r="C27" s="86" t="str"/>
-      <x:c r="D27" s="86" t="str"/>
-      <x:c r="E27" s="86" t="str"/>
-      <x:c r="F27" s="86" t="str"/>
-      <x:c r="G27" s="87" t="str"/>
+      <x:c r="A27" s="117" t="str">
+        <x:v>Member 3</x:v>
+      </x:c>
+      <x:c r="B27" s="122" t="str">
+        <x:f>IF('COMMITTEE ROSTER'!B20="","",'COMMITTEE ROSTER'!B20)</x:f>
+      </x:c>
+      <x:c r="C27" s="89" t="str"/>
+      <x:c r="D27" s="89" t="str"/>
+      <x:c r="E27" s="89" t="str"/>
+      <x:c r="F27" s="89" t="str"/>
+      <x:c r="G27" s="90" t="str"/>
     </x:row>
     <x:row r="28">
-      <x:c r="A28" s="114" t="str">
-        <x:v>Portfolio Manager</x:v>
-      </x:c>
-      <x:c r="B28" s="85" t="str"/>
-      <x:c r="C28" s="86" t="str"/>
-      <x:c r="D28" s="86" t="str"/>
-      <x:c r="E28" s="86" t="str"/>
-      <x:c r="F28" s="86" t="str"/>
-      <x:c r="G28" s="87" t="str"/>
+      <x:c r="A28" s="117" t="str">
+        <x:v>Member 4</x:v>
+      </x:c>
+      <x:c r="B28" s="122" t="str">
+        <x:f>IF('COMMITTEE ROSTER'!B21="","",'COMMITTEE ROSTER'!B21)</x:f>
+      </x:c>
+      <x:c r="C28" s="89" t="str"/>
+      <x:c r="D28" s="89" t="str"/>
+      <x:c r="E28" s="89" t="str"/>
+      <x:c r="F28" s="89" t="str"/>
+      <x:c r="G28" s="90" t="str"/>
     </x:row>
     <x:row r="29">
-      <x:c r="A29" s="114" t="str">
-        <x:v>Risk &amp; Derivatives</x:v>
-      </x:c>
-      <x:c r="B29" s="88" t="str"/>
-      <x:c r="C29" s="89" t="str"/>
-      <x:c r="D29" s="89" t="str"/>
-      <x:c r="E29" s="89" t="str"/>
-      <x:c r="F29" s="89" t="str"/>
-      <x:c r="G29" s="90" t="str"/>
+      <x:c r="A29" s="117" t="str">
+        <x:v>Member 5</x:v>
+      </x:c>
+      <x:c r="B29" s="123" t="str">
+        <x:f>IF('COMMITTEE ROSTER'!B22="","",'COMMITTEE ROSTER'!B22)</x:f>
+      </x:c>
+      <x:c r="C29" s="92" t="str"/>
+      <x:c r="D29" s="92" t="str"/>
+      <x:c r="E29" s="92" t="str"/>
+      <x:c r="F29" s="92" t="str"/>
+      <x:c r="G29" s="93" t="str"/>
     </x:row>
     <x:row r="30">
       <x:c r="A30" s="25" t="str">
         <x:v>Decision status</x:v>
       </x:c>
       <x:c r="B30" s="28" t="str">
-        <x:f>IF(COUNTIF(C25:C29,"Revise")+COUNTIF(C25:C29,"Reject")&gt;0,"REVISION REQUIRED",IF(COUNTIF(C25:C29,"Approve")=5,"APPROVED","INCOMPLETE"))</x:f>
+        <x:f>IF('COMMITTEE ROSTER'!B23&lt;&gt;"READY","INCOMPLETE",IF(COUNTIF(C25:C29,"Revise")+COUNTIF(C25:C29,"Reject")&gt;0,"REVISION REQUIRED",IF(COUNTIF(C25:C29,"Approve")='COMMITTEE ROSTER'!E19,"APPROVED","INCOMPLETE")))</x:f>
         <x:v>INCOMPLETE</x:v>
       </x:c>
       <x:c r="C30" s="29"/>
@@ -4444,22 +4690,22 @@
       <x:c r="H32" s="11"/>
     </x:row>
     <x:row r="33" ht="34" customHeight="1">
-      <x:c r="A33" s="82"/>
-      <x:c r="B33" s="83"/>
-      <x:c r="C33" s="83"/>
-      <x:c r="D33" s="83"/>
-      <x:c r="E33" s="83"/>
-      <x:c r="F33" s="83"/>
-      <x:c r="G33" s="84"/>
+      <x:c r="A33" s="85"/>
+      <x:c r="B33" s="86"/>
+      <x:c r="C33" s="86"/>
+      <x:c r="D33" s="86"/>
+      <x:c r="E33" s="86"/>
+      <x:c r="F33" s="86"/>
+      <x:c r="G33" s="87"/>
     </x:row>
     <x:row r="34" ht="34" customHeight="1">
-      <x:c r="A34" s="88"/>
-      <x:c r="B34" s="89"/>
-      <x:c r="C34" s="89"/>
-      <x:c r="D34" s="89"/>
-      <x:c r="E34" s="89"/>
-      <x:c r="F34" s="89"/>
-      <x:c r="G34" s="90"/>
+      <x:c r="A34" s="91"/>
+      <x:c r="B34" s="92"/>
+      <x:c r="C34" s="92"/>
+      <x:c r="D34" s="92"/>
+      <x:c r="E34" s="92"/>
+      <x:c r="F34" s="92"/>
+      <x:c r="G34" s="93"/>
     </x:row>
     <x:row r="36" ht="23" customHeight="1">
       <x:c r="A36" s="11" t="str">
@@ -4497,70 +4743,70 @@
       </x:c>
     </x:row>
     <x:row r="38">
-      <x:c r="A38" s="82" t="str"/>
-      <x:c r="B38" s="83" t="str"/>
-      <x:c r="C38" s="91" t="str"/>
-      <x:c r="D38" s="83" t="str"/>
-      <x:c r="E38" s="83" t="str">
+      <x:c r="A38" s="85" t="str"/>
+      <x:c r="B38" s="86" t="str"/>
+      <x:c r="C38" s="94" t="str"/>
+      <x:c r="D38" s="86" t="str"/>
+      <x:c r="E38" s="86" t="str">
         <x:v>Open</x:v>
       </x:c>
-      <x:c r="F38" s="83" t="str"/>
-      <x:c r="G38" s="84" t="str"/>
+      <x:c r="F38" s="86" t="str"/>
+      <x:c r="G38" s="87" t="str"/>
     </x:row>
     <x:row r="39">
-      <x:c r="A39" s="85" t="str"/>
-      <x:c r="B39" s="86" t="str"/>
-      <x:c r="C39" s="92" t="str"/>
-      <x:c r="D39" s="86" t="str"/>
-      <x:c r="E39" s="86" t="str">
+      <x:c r="A39" s="88" t="str"/>
+      <x:c r="B39" s="89" t="str"/>
+      <x:c r="C39" s="95" t="str"/>
+      <x:c r="D39" s="89" t="str"/>
+      <x:c r="E39" s="89" t="str">
         <x:v>Open</x:v>
       </x:c>
-      <x:c r="F39" s="86" t="str"/>
-      <x:c r="G39" s="87" t="str"/>
+      <x:c r="F39" s="89" t="str"/>
+      <x:c r="G39" s="90" t="str"/>
     </x:row>
     <x:row r="40">
-      <x:c r="A40" s="85" t="str"/>
-      <x:c r="B40" s="86" t="str"/>
-      <x:c r="C40" s="92" t="str"/>
-      <x:c r="D40" s="86" t="str"/>
-      <x:c r="E40" s="86" t="str">
+      <x:c r="A40" s="88" t="str"/>
+      <x:c r="B40" s="89" t="str"/>
+      <x:c r="C40" s="95" t="str"/>
+      <x:c r="D40" s="89" t="str"/>
+      <x:c r="E40" s="89" t="str">
         <x:v>Open</x:v>
       </x:c>
-      <x:c r="F40" s="86" t="str"/>
-      <x:c r="G40" s="87" t="str"/>
+      <x:c r="F40" s="89" t="str"/>
+      <x:c r="G40" s="90" t="str"/>
     </x:row>
     <x:row r="41">
-      <x:c r="A41" s="85" t="str"/>
-      <x:c r="B41" s="86" t="str"/>
-      <x:c r="C41" s="92" t="str"/>
-      <x:c r="D41" s="86" t="str"/>
-      <x:c r="E41" s="86" t="str">
+      <x:c r="A41" s="88" t="str"/>
+      <x:c r="B41" s="89" t="str"/>
+      <x:c r="C41" s="95" t="str"/>
+      <x:c r="D41" s="89" t="str"/>
+      <x:c r="E41" s="89" t="str">
         <x:v>Open</x:v>
       </x:c>
-      <x:c r="F41" s="86" t="str"/>
-      <x:c r="G41" s="87" t="str"/>
+      <x:c r="F41" s="89" t="str"/>
+      <x:c r="G41" s="90" t="str"/>
     </x:row>
     <x:row r="42">
-      <x:c r="A42" s="88" t="str"/>
-      <x:c r="B42" s="89" t="str"/>
-      <x:c r="C42" s="93" t="str"/>
-      <x:c r="D42" s="89" t="str"/>
-      <x:c r="E42" s="89" t="str">
+      <x:c r="A42" s="91" t="str"/>
+      <x:c r="B42" s="92" t="str"/>
+      <x:c r="C42" s="96" t="str"/>
+      <x:c r="D42" s="92" t="str"/>
+      <x:c r="E42" s="92" t="str">
         <x:v>Open</x:v>
       </x:c>
-      <x:c r="F42" s="89" t="str"/>
-      <x:c r="G42" s="90" t="str"/>
+      <x:c r="F42" s="92" t="str"/>
+      <x:c r="G42" s="93" t="str"/>
     </x:row>
     <x:row r="44" ht="32" customHeight="1">
-      <x:c r="A44" s="104" t="str">
-        <x:v>Approval requires five Approve votes. Any Revise or Reject vote produces REVISION REQUIRED; document the change and reconvene before the next gate.</x:v>
-      </x:c>
-      <x:c r="B44" s="104"/>
-      <x:c r="C44" s="104"/>
-      <x:c r="D44" s="104"/>
-      <x:c r="E44" s="104"/>
-      <x:c r="F44" s="104"/>
-      <x:c r="G44" s="104"/>
+      <x:c r="A44" s="107" t="str">
+        <x:v>Approval requires one Approve vote from each of the four or five distinct members listed on the roster. A dual-role member votes once. Any Revise or Reject vote requires revision and a new meeting.</x:v>
+      </x:c>
+      <x:c r="B44" s="107"/>
+      <x:c r="C44" s="107"/>
+      <x:c r="D44" s="107"/>
+      <x:c r="E44" s="107"/>
+      <x:c r="F44" s="107"/>
+      <x:c r="G44" s="107"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -4585,9 +4831,9 @@
     <x:mergeCell ref="A44:G44"/>
   </x:mergeCells>
   <x:conditionalFormatting sqref="B30:C30">
-    <x:cfRule type="containsText" dxfId="40" priority="1" operator="containsText" text="APPROVED"/>
-    <x:cfRule type="containsText" dxfId="41" priority="2" operator="containsText" text="REVISION"/>
-    <x:cfRule type="containsText" dxfId="42" priority="3" operator="containsText" text="INCOMPLETE"/>
+    <x:cfRule type="containsText" dxfId="47" priority="1" operator="containsText" text="APPROVED"/>
+    <x:cfRule type="containsText" dxfId="48" priority="2" operator="containsText" text="REVISION"/>
+    <x:cfRule type="containsText" dxfId="49" priority="3" operator="containsText" text="INCOMPLETE"/>
   </x:conditionalFormatting>
   <x:dataValidations count="3">
     <x:dataValidation type="list" sqref="G10:G15">
@@ -4632,7 +4878,7 @@
     </x:row>
     <x:row r="2" ht="24" customHeight="1">
       <x:c r="A2" s="6" t="str">
-        <x:v>Build &amp; Challenge | All five committee members review, vote, and sign this record.</x:v>
+        <x:v>Build &amp; Challenge | All four or five members review and cast one vote each.</x:v>
       </x:c>
       <x:c r="B2" s="6"/>
       <x:c r="C2" s="6"/>
@@ -4646,21 +4892,21 @@
       <x:c r="A4" s="25" t="str">
         <x:v>Team / Committee Name</x:v>
       </x:c>
-      <x:c r="B4" s="82"/>
-      <x:c r="C4" s="84"/>
+      <x:c r="B4" s="85"/>
+      <x:c r="C4" s="87"/>
       <x:c r="D4" s="25" t="str">
         <x:v>Recorder</x:v>
       </x:c>
-      <x:c r="E4" s="63"/>
-      <x:c r="F4" s="110"/>
-      <x:c r="G4" s="64"/>
+      <x:c r="E4" s="66"/>
+      <x:c r="F4" s="113"/>
+      <x:c r="G4" s="67"/>
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="25" t="str">
         <x:v>Client name / case</x:v>
       </x:c>
-      <x:c r="B5" s="85"/>
-      <x:c r="C5" s="87"/>
+      <x:c r="B5" s="88"/>
+      <x:c r="C5" s="90"/>
       <x:c r="D5" s="25" t="str">
         <x:v>Gate</x:v>
       </x:c>
@@ -4674,14 +4920,14 @@
       <x:c r="A6" s="25" t="str">
         <x:v>Meeting Date</x:v>
       </x:c>
-      <x:c r="B6" s="111"/>
-      <x:c r="C6" s="112"/>
+      <x:c r="B6" s="114"/>
+      <x:c r="C6" s="115"/>
       <x:c r="D6" s="25" t="str">
         <x:v>Meeting Chair</x:v>
       </x:c>
-      <x:c r="E6" s="63"/>
-      <x:c r="F6" s="110"/>
-      <x:c r="G6" s="64"/>
+      <x:c r="E6" s="66"/>
+      <x:c r="F6" s="113"/>
+      <x:c r="G6" s="67"/>
     </x:row>
     <x:row r="8" ht="23" customHeight="1">
       <x:c r="A8" s="11" t="str">
@@ -4719,68 +4965,68 @@
       </x:c>
     </x:row>
     <x:row r="10">
-      <x:c r="A10" s="82" t="str"/>
-      <x:c r="B10" s="83" t="str"/>
-      <x:c r="C10" s="91" t="str"/>
-      <x:c r="D10" s="83" t="str"/>
-      <x:c r="E10" s="83" t="str"/>
-      <x:c r="F10" s="83" t="str"/>
-      <x:c r="G10" s="84" t="str">
+      <x:c r="A10" s="85" t="str"/>
+      <x:c r="B10" s="86" t="str"/>
+      <x:c r="C10" s="94" t="str"/>
+      <x:c r="D10" s="86" t="str"/>
+      <x:c r="E10" s="86" t="str"/>
+      <x:c r="F10" s="86" t="str"/>
+      <x:c r="G10" s="87" t="str">
         <x:v>Not reviewed</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
-      <x:c r="A11" s="85" t="str"/>
-      <x:c r="B11" s="86" t="str"/>
-      <x:c r="C11" s="92" t="str"/>
-      <x:c r="D11" s="86" t="str"/>
-      <x:c r="E11" s="86" t="str"/>
-      <x:c r="F11" s="86" t="str"/>
-      <x:c r="G11" s="87" t="str">
+      <x:c r="A11" s="88" t="str"/>
+      <x:c r="B11" s="89" t="str"/>
+      <x:c r="C11" s="95" t="str"/>
+      <x:c r="D11" s="89" t="str"/>
+      <x:c r="E11" s="89" t="str"/>
+      <x:c r="F11" s="89" t="str"/>
+      <x:c r="G11" s="90" t="str">
         <x:v>Not reviewed</x:v>
       </x:c>
     </x:row>
     <x:row r="12">
-      <x:c r="A12" s="85" t="str"/>
-      <x:c r="B12" s="86" t="str"/>
-      <x:c r="C12" s="92" t="str"/>
-      <x:c r="D12" s="86" t="str"/>
-      <x:c r="E12" s="86" t="str"/>
-      <x:c r="F12" s="86" t="str"/>
-      <x:c r="G12" s="87" t="str">
+      <x:c r="A12" s="88" t="str"/>
+      <x:c r="B12" s="89" t="str"/>
+      <x:c r="C12" s="95" t="str"/>
+      <x:c r="D12" s="89" t="str"/>
+      <x:c r="E12" s="89" t="str"/>
+      <x:c r="F12" s="89" t="str"/>
+      <x:c r="G12" s="90" t="str">
         <x:v>Not reviewed</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
-      <x:c r="A13" s="85" t="str"/>
-      <x:c r="B13" s="86" t="str"/>
-      <x:c r="C13" s="92" t="str"/>
-      <x:c r="D13" s="86" t="str"/>
-      <x:c r="E13" s="86" t="str"/>
-      <x:c r="F13" s="86" t="str"/>
-      <x:c r="G13" s="87" t="str">
+      <x:c r="A13" s="88" t="str"/>
+      <x:c r="B13" s="89" t="str"/>
+      <x:c r="C13" s="95" t="str"/>
+      <x:c r="D13" s="89" t="str"/>
+      <x:c r="E13" s="89" t="str"/>
+      <x:c r="F13" s="89" t="str"/>
+      <x:c r="G13" s="90" t="str">
         <x:v>Not reviewed</x:v>
       </x:c>
     </x:row>
     <x:row r="14">
-      <x:c r="A14" s="85" t="str"/>
-      <x:c r="B14" s="86" t="str"/>
-      <x:c r="C14" s="92" t="str"/>
-      <x:c r="D14" s="86" t="str"/>
-      <x:c r="E14" s="86" t="str"/>
-      <x:c r="F14" s="86" t="str"/>
-      <x:c r="G14" s="87" t="str">
+      <x:c r="A14" s="88" t="str"/>
+      <x:c r="B14" s="89" t="str"/>
+      <x:c r="C14" s="95" t="str"/>
+      <x:c r="D14" s="89" t="str"/>
+      <x:c r="E14" s="89" t="str"/>
+      <x:c r="F14" s="89" t="str"/>
+      <x:c r="G14" s="90" t="str">
         <x:v>Not reviewed</x:v>
       </x:c>
     </x:row>
     <x:row r="15">
-      <x:c r="A15" s="88" t="str"/>
-      <x:c r="B15" s="89" t="str"/>
-      <x:c r="C15" s="93" t="str"/>
-      <x:c r="D15" s="89" t="str"/>
-      <x:c r="E15" s="89" t="str"/>
-      <x:c r="F15" s="89" t="str"/>
-      <x:c r="G15" s="90" t="str">
+      <x:c r="A15" s="91" t="str"/>
+      <x:c r="B15" s="92" t="str"/>
+      <x:c r="C15" s="96" t="str"/>
+      <x:c r="D15" s="92" t="str"/>
+      <x:c r="E15" s="92" t="str"/>
+      <x:c r="F15" s="92" t="str"/>
+      <x:c r="G15" s="93" t="str">
         <x:v>Not reviewed</x:v>
       </x:c>
     </x:row>
@@ -4818,13 +5064,13 @@
       <x:c r="G20" s="37"/>
     </x:row>
     <x:row r="21" ht="42" customHeight="1">
-      <x:c r="A21" s="63"/>
-      <x:c r="B21" s="110"/>
-      <x:c r="C21" s="110"/>
-      <x:c r="D21" s="110"/>
-      <x:c r="E21" s="110"/>
-      <x:c r="F21" s="110"/>
-      <x:c r="G21" s="64"/>
+      <x:c r="A21" s="66"/>
+      <x:c r="B21" s="113"/>
+      <x:c r="C21" s="113"/>
+      <x:c r="D21" s="113"/>
+      <x:c r="E21" s="113"/>
+      <x:c r="F21" s="113"/>
+      <x:c r="G21" s="67"/>
     </x:row>
     <x:row r="23" ht="23" customHeight="1">
       <x:c r="A23" s="11" t="str">
@@ -4840,7 +5086,7 @@
     </x:row>
     <x:row r="24">
       <x:c r="A24" s="21" t="str">
-        <x:v>Committee seat</x:v>
+        <x:v>Member slot</x:v>
       </x:c>
       <x:c r="B24" s="21" t="str">
         <x:v>Member name</x:v>
@@ -4862,66 +5108,76 @@
       </x:c>
     </x:row>
     <x:row r="25">
-      <x:c r="A25" s="114" t="str">
-        <x:v>Client &amp; Macro</x:v>
-      </x:c>
-      <x:c r="B25" s="82" t="str"/>
-      <x:c r="C25" s="83" t="str"/>
-      <x:c r="D25" s="83" t="str"/>
-      <x:c r="E25" s="83" t="str"/>
-      <x:c r="F25" s="83" t="str"/>
-      <x:c r="G25" s="84" t="str"/>
+      <x:c r="A25" s="117" t="str">
+        <x:v>Member 1</x:v>
+      </x:c>
+      <x:c r="B25" s="121" t="str">
+        <x:f>IF('COMMITTEE ROSTER'!B18="","",'COMMITTEE ROSTER'!B18)</x:f>
+      </x:c>
+      <x:c r="C25" s="86" t="str"/>
+      <x:c r="D25" s="86" t="str"/>
+      <x:c r="E25" s="86" t="str"/>
+      <x:c r="F25" s="86" t="str"/>
+      <x:c r="G25" s="87" t="str"/>
     </x:row>
     <x:row r="26">
-      <x:c r="A26" s="114" t="str">
-        <x:v>Fixed Income</x:v>
-      </x:c>
-      <x:c r="B26" s="85" t="str"/>
-      <x:c r="C26" s="86" t="str"/>
-      <x:c r="D26" s="86" t="str"/>
-      <x:c r="E26" s="86" t="str"/>
-      <x:c r="F26" s="86" t="str"/>
-      <x:c r="G26" s="87" t="str"/>
+      <x:c r="A26" s="117" t="str">
+        <x:v>Member 2</x:v>
+      </x:c>
+      <x:c r="B26" s="122" t="str">
+        <x:f>IF('COMMITTEE ROSTER'!B19="","",'COMMITTEE ROSTER'!B19)</x:f>
+      </x:c>
+      <x:c r="C26" s="89" t="str"/>
+      <x:c r="D26" s="89" t="str"/>
+      <x:c r="E26" s="89" t="str"/>
+      <x:c r="F26" s="89" t="str"/>
+      <x:c r="G26" s="90" t="str"/>
     </x:row>
     <x:row r="27">
-      <x:c r="A27" s="114" t="str">
-        <x:v>Equity</x:v>
-      </x:c>
-      <x:c r="B27" s="85" t="str"/>
-      <x:c r="C27" s="86" t="str"/>
-      <x:c r="D27" s="86" t="str"/>
-      <x:c r="E27" s="86" t="str"/>
-      <x:c r="F27" s="86" t="str"/>
-      <x:c r="G27" s="87" t="str"/>
+      <x:c r="A27" s="117" t="str">
+        <x:v>Member 3</x:v>
+      </x:c>
+      <x:c r="B27" s="122" t="str">
+        <x:f>IF('COMMITTEE ROSTER'!B20="","",'COMMITTEE ROSTER'!B20)</x:f>
+      </x:c>
+      <x:c r="C27" s="89" t="str"/>
+      <x:c r="D27" s="89" t="str"/>
+      <x:c r="E27" s="89" t="str"/>
+      <x:c r="F27" s="89" t="str"/>
+      <x:c r="G27" s="90" t="str"/>
     </x:row>
     <x:row r="28">
-      <x:c r="A28" s="114" t="str">
-        <x:v>Portfolio Manager</x:v>
-      </x:c>
-      <x:c r="B28" s="85" t="str"/>
-      <x:c r="C28" s="86" t="str"/>
-      <x:c r="D28" s="86" t="str"/>
-      <x:c r="E28" s="86" t="str"/>
-      <x:c r="F28" s="86" t="str"/>
-      <x:c r="G28" s="87" t="str"/>
+      <x:c r="A28" s="117" t="str">
+        <x:v>Member 4</x:v>
+      </x:c>
+      <x:c r="B28" s="122" t="str">
+        <x:f>IF('COMMITTEE ROSTER'!B21="","",'COMMITTEE ROSTER'!B21)</x:f>
+      </x:c>
+      <x:c r="C28" s="89" t="str"/>
+      <x:c r="D28" s="89" t="str"/>
+      <x:c r="E28" s="89" t="str"/>
+      <x:c r="F28" s="89" t="str"/>
+      <x:c r="G28" s="90" t="str"/>
     </x:row>
     <x:row r="29">
-      <x:c r="A29" s="114" t="str">
-        <x:v>Risk &amp; Derivatives</x:v>
-      </x:c>
-      <x:c r="B29" s="88" t="str"/>
-      <x:c r="C29" s="89" t="str"/>
-      <x:c r="D29" s="89" t="str"/>
-      <x:c r="E29" s="89" t="str"/>
-      <x:c r="F29" s="89" t="str"/>
-      <x:c r="G29" s="90" t="str"/>
+      <x:c r="A29" s="117" t="str">
+        <x:v>Member 5</x:v>
+      </x:c>
+      <x:c r="B29" s="123" t="str">
+        <x:f>IF('COMMITTEE ROSTER'!B22="","",'COMMITTEE ROSTER'!B22)</x:f>
+      </x:c>
+      <x:c r="C29" s="92" t="str"/>
+      <x:c r="D29" s="92" t="str"/>
+      <x:c r="E29" s="92" t="str"/>
+      <x:c r="F29" s="92" t="str"/>
+      <x:c r="G29" s="93" t="str"/>
     </x:row>
     <x:row r="30">
       <x:c r="A30" s="25" t="str">
         <x:v>Decision status</x:v>
       </x:c>
       <x:c r="B30" s="28" t="str">
-        <x:f>IF(COUNTIF(C25:C29,"Revise")+COUNTIF(C25:C29,"Reject")&gt;0,"REVISION REQUIRED",IF(COUNTIF(C25:C29,"Approve")=5,"APPROVED","INCOMPLETE"))</x:f>
+        <x:f>IF('COMMITTEE ROSTER'!B23&lt;&gt;"READY","INCOMPLETE",IF(COUNTIF(C25:C29,"Revise")+COUNTIF(C25:C29,"Reject")&gt;0,"REVISION REQUIRED",IF(COUNTIF(C25:C29,"Approve")='COMMITTEE ROSTER'!E19,"APPROVED","INCOMPLETE")))</x:f>
         <x:v>INCOMPLETE</x:v>
       </x:c>
       <x:c r="C30" s="29"/>
@@ -4939,22 +5195,22 @@
       <x:c r="H32" s="11"/>
     </x:row>
     <x:row r="33" ht="34" customHeight="1">
-      <x:c r="A33" s="82"/>
-      <x:c r="B33" s="83"/>
-      <x:c r="C33" s="83"/>
-      <x:c r="D33" s="83"/>
-      <x:c r="E33" s="83"/>
-      <x:c r="F33" s="83"/>
-      <x:c r="G33" s="84"/>
+      <x:c r="A33" s="85"/>
+      <x:c r="B33" s="86"/>
+      <x:c r="C33" s="86"/>
+      <x:c r="D33" s="86"/>
+      <x:c r="E33" s="86"/>
+      <x:c r="F33" s="86"/>
+      <x:c r="G33" s="87"/>
     </x:row>
     <x:row r="34" ht="34" customHeight="1">
-      <x:c r="A34" s="88"/>
-      <x:c r="B34" s="89"/>
-      <x:c r="C34" s="89"/>
-      <x:c r="D34" s="89"/>
-      <x:c r="E34" s="89"/>
-      <x:c r="F34" s="89"/>
-      <x:c r="G34" s="90"/>
+      <x:c r="A34" s="91"/>
+      <x:c r="B34" s="92"/>
+      <x:c r="C34" s="92"/>
+      <x:c r="D34" s="92"/>
+      <x:c r="E34" s="92"/>
+      <x:c r="F34" s="92"/>
+      <x:c r="G34" s="93"/>
     </x:row>
     <x:row r="36" ht="23" customHeight="1">
       <x:c r="A36" s="11" t="str">
@@ -4992,70 +5248,70 @@
       </x:c>
     </x:row>
     <x:row r="38">
-      <x:c r="A38" s="82" t="str"/>
-      <x:c r="B38" s="83" t="str"/>
-      <x:c r="C38" s="91" t="str"/>
-      <x:c r="D38" s="83" t="str"/>
-      <x:c r="E38" s="83" t="str">
+      <x:c r="A38" s="85" t="str"/>
+      <x:c r="B38" s="86" t="str"/>
+      <x:c r="C38" s="94" t="str"/>
+      <x:c r="D38" s="86" t="str"/>
+      <x:c r="E38" s="86" t="str">
         <x:v>Open</x:v>
       </x:c>
-      <x:c r="F38" s="83" t="str"/>
-      <x:c r="G38" s="84" t="str"/>
+      <x:c r="F38" s="86" t="str"/>
+      <x:c r="G38" s="87" t="str"/>
     </x:row>
     <x:row r="39">
-      <x:c r="A39" s="85" t="str"/>
-      <x:c r="B39" s="86" t="str"/>
-      <x:c r="C39" s="92" t="str"/>
-      <x:c r="D39" s="86" t="str"/>
-      <x:c r="E39" s="86" t="str">
+      <x:c r="A39" s="88" t="str"/>
+      <x:c r="B39" s="89" t="str"/>
+      <x:c r="C39" s="95" t="str"/>
+      <x:c r="D39" s="89" t="str"/>
+      <x:c r="E39" s="89" t="str">
         <x:v>Open</x:v>
       </x:c>
-      <x:c r="F39" s="86" t="str"/>
-      <x:c r="G39" s="87" t="str"/>
+      <x:c r="F39" s="89" t="str"/>
+      <x:c r="G39" s="90" t="str"/>
     </x:row>
     <x:row r="40">
-      <x:c r="A40" s="85" t="str"/>
-      <x:c r="B40" s="86" t="str"/>
-      <x:c r="C40" s="92" t="str"/>
-      <x:c r="D40" s="86" t="str"/>
-      <x:c r="E40" s="86" t="str">
+      <x:c r="A40" s="88" t="str"/>
+      <x:c r="B40" s="89" t="str"/>
+      <x:c r="C40" s="95" t="str"/>
+      <x:c r="D40" s="89" t="str"/>
+      <x:c r="E40" s="89" t="str">
         <x:v>Open</x:v>
       </x:c>
-      <x:c r="F40" s="86" t="str"/>
-      <x:c r="G40" s="87" t="str"/>
+      <x:c r="F40" s="89" t="str"/>
+      <x:c r="G40" s="90" t="str"/>
     </x:row>
     <x:row r="41">
-      <x:c r="A41" s="85" t="str"/>
-      <x:c r="B41" s="86" t="str"/>
-      <x:c r="C41" s="92" t="str"/>
-      <x:c r="D41" s="86" t="str"/>
-      <x:c r="E41" s="86" t="str">
+      <x:c r="A41" s="88" t="str"/>
+      <x:c r="B41" s="89" t="str"/>
+      <x:c r="C41" s="95" t="str"/>
+      <x:c r="D41" s="89" t="str"/>
+      <x:c r="E41" s="89" t="str">
         <x:v>Open</x:v>
       </x:c>
-      <x:c r="F41" s="86" t="str"/>
-      <x:c r="G41" s="87" t="str"/>
+      <x:c r="F41" s="89" t="str"/>
+      <x:c r="G41" s="90" t="str"/>
     </x:row>
     <x:row r="42">
-      <x:c r="A42" s="88" t="str"/>
-      <x:c r="B42" s="89" t="str"/>
-      <x:c r="C42" s="93" t="str"/>
-      <x:c r="D42" s="89" t="str"/>
-      <x:c r="E42" s="89" t="str">
+      <x:c r="A42" s="91" t="str"/>
+      <x:c r="B42" s="92" t="str"/>
+      <x:c r="C42" s="96" t="str"/>
+      <x:c r="D42" s="92" t="str"/>
+      <x:c r="E42" s="92" t="str">
         <x:v>Open</x:v>
       </x:c>
-      <x:c r="F42" s="89" t="str"/>
-      <x:c r="G42" s="90" t="str"/>
+      <x:c r="F42" s="92" t="str"/>
+      <x:c r="G42" s="93" t="str"/>
     </x:row>
     <x:row r="44" ht="32" customHeight="1">
-      <x:c r="A44" s="104" t="str">
-        <x:v>Approval requires five Approve votes. Any Revise or Reject vote produces REVISION REQUIRED; document the change and reconvene before the next gate.</x:v>
-      </x:c>
-      <x:c r="B44" s="104"/>
-      <x:c r="C44" s="104"/>
-      <x:c r="D44" s="104"/>
-      <x:c r="E44" s="104"/>
-      <x:c r="F44" s="104"/>
-      <x:c r="G44" s="104"/>
+      <x:c r="A44" s="107" t="str">
+        <x:v>Approval requires one Approve vote from each of the four or five distinct members listed on the roster. A dual-role member votes once. Any Revise or Reject vote requires revision and a new meeting.</x:v>
+      </x:c>
+      <x:c r="B44" s="107"/>
+      <x:c r="C44" s="107"/>
+      <x:c r="D44" s="107"/>
+      <x:c r="E44" s="107"/>
+      <x:c r="F44" s="107"/>
+      <x:c r="G44" s="107"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -5080,9 +5336,9 @@
     <x:mergeCell ref="A44:G44"/>
   </x:mergeCells>
   <x:conditionalFormatting sqref="B30:C30">
-    <x:cfRule type="containsText" dxfId="43" priority="1" operator="containsText" text="APPROVED"/>
-    <x:cfRule type="containsText" dxfId="44" priority="2" operator="containsText" text="REVISION"/>
-    <x:cfRule type="containsText" dxfId="45" priority="3" operator="containsText" text="INCOMPLETE"/>
+    <x:cfRule type="containsText" dxfId="50" priority="1" operator="containsText" text="APPROVED"/>
+    <x:cfRule type="containsText" dxfId="51" priority="2" operator="containsText" text="REVISION"/>
+    <x:cfRule type="containsText" dxfId="52" priority="3" operator="containsText" text="INCOMPLETE"/>
   </x:conditionalFormatting>
   <x:dataValidations count="3">
     <x:dataValidation type="list" sqref="G10:G15">
@@ -5127,7 +5383,7 @@
     </x:row>
     <x:row r="2" ht="24" customHeight="1">
       <x:c r="A2" s="6" t="str">
-        <x:v>Defend the Recommendation | All five committee members review, vote, and sign this record.</x:v>
+        <x:v>Defend the Recommendation | All four or five members review and cast one vote each.</x:v>
       </x:c>
       <x:c r="B2" s="6"/>
       <x:c r="C2" s="6"/>
@@ -5141,21 +5397,21 @@
       <x:c r="A4" s="25" t="str">
         <x:v>Team / Committee Name</x:v>
       </x:c>
-      <x:c r="B4" s="82"/>
-      <x:c r="C4" s="84"/>
+      <x:c r="B4" s="85"/>
+      <x:c r="C4" s="87"/>
       <x:c r="D4" s="25" t="str">
         <x:v>Recorder</x:v>
       </x:c>
-      <x:c r="E4" s="63"/>
-      <x:c r="F4" s="110"/>
-      <x:c r="G4" s="64"/>
+      <x:c r="E4" s="66"/>
+      <x:c r="F4" s="113"/>
+      <x:c r="G4" s="67"/>
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="25" t="str">
         <x:v>Scope: integrated recommendation</x:v>
       </x:c>
-      <x:c r="B5" s="85"/>
-      <x:c r="C5" s="87"/>
+      <x:c r="B5" s="88"/>
+      <x:c r="C5" s="90"/>
       <x:c r="D5" s="25" t="str">
         <x:v>Gate</x:v>
       </x:c>
@@ -5169,14 +5425,14 @@
       <x:c r="A6" s="25" t="str">
         <x:v>Meeting Date</x:v>
       </x:c>
-      <x:c r="B6" s="111"/>
-      <x:c r="C6" s="112"/>
+      <x:c r="B6" s="114"/>
+      <x:c r="C6" s="115"/>
       <x:c r="D6" s="25" t="str">
         <x:v>Meeting Chair</x:v>
       </x:c>
-      <x:c r="E6" s="63"/>
-      <x:c r="F6" s="110"/>
-      <x:c r="G6" s="64"/>
+      <x:c r="E6" s="66"/>
+      <x:c r="F6" s="113"/>
+      <x:c r="G6" s="67"/>
     </x:row>
     <x:row r="8" ht="23" customHeight="1">
       <x:c r="A8" s="11" t="str">
@@ -5214,68 +5470,68 @@
       </x:c>
     </x:row>
     <x:row r="10">
-      <x:c r="A10" s="82" t="str"/>
-      <x:c r="B10" s="83" t="str"/>
-      <x:c r="C10" s="91" t="str"/>
-      <x:c r="D10" s="83" t="str"/>
-      <x:c r="E10" s="83" t="str"/>
-      <x:c r="F10" s="83" t="str"/>
-      <x:c r="G10" s="84" t="str">
+      <x:c r="A10" s="85" t="str"/>
+      <x:c r="B10" s="86" t="str"/>
+      <x:c r="C10" s="94" t="str"/>
+      <x:c r="D10" s="86" t="str"/>
+      <x:c r="E10" s="86" t="str"/>
+      <x:c r="F10" s="86" t="str"/>
+      <x:c r="G10" s="87" t="str">
         <x:v>Not reviewed</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
-      <x:c r="A11" s="85" t="str"/>
-      <x:c r="B11" s="86" t="str"/>
-      <x:c r="C11" s="92" t="str"/>
-      <x:c r="D11" s="86" t="str"/>
-      <x:c r="E11" s="86" t="str"/>
-      <x:c r="F11" s="86" t="str"/>
-      <x:c r="G11" s="87" t="str">
+      <x:c r="A11" s="88" t="str"/>
+      <x:c r="B11" s="89" t="str"/>
+      <x:c r="C11" s="95" t="str"/>
+      <x:c r="D11" s="89" t="str"/>
+      <x:c r="E11" s="89" t="str"/>
+      <x:c r="F11" s="89" t="str"/>
+      <x:c r="G11" s="90" t="str">
         <x:v>Not reviewed</x:v>
       </x:c>
     </x:row>
     <x:row r="12">
-      <x:c r="A12" s="85" t="str"/>
-      <x:c r="B12" s="86" t="str"/>
-      <x:c r="C12" s="92" t="str"/>
-      <x:c r="D12" s="86" t="str"/>
-      <x:c r="E12" s="86" t="str"/>
-      <x:c r="F12" s="86" t="str"/>
-      <x:c r="G12" s="87" t="str">
+      <x:c r="A12" s="88" t="str"/>
+      <x:c r="B12" s="89" t="str"/>
+      <x:c r="C12" s="95" t="str"/>
+      <x:c r="D12" s="89" t="str"/>
+      <x:c r="E12" s="89" t="str"/>
+      <x:c r="F12" s="89" t="str"/>
+      <x:c r="G12" s="90" t="str">
         <x:v>Not reviewed</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
-      <x:c r="A13" s="85" t="str"/>
-      <x:c r="B13" s="86" t="str"/>
-      <x:c r="C13" s="92" t="str"/>
-      <x:c r="D13" s="86" t="str"/>
-      <x:c r="E13" s="86" t="str"/>
-      <x:c r="F13" s="86" t="str"/>
-      <x:c r="G13" s="87" t="str">
+      <x:c r="A13" s="88" t="str"/>
+      <x:c r="B13" s="89" t="str"/>
+      <x:c r="C13" s="95" t="str"/>
+      <x:c r="D13" s="89" t="str"/>
+      <x:c r="E13" s="89" t="str"/>
+      <x:c r="F13" s="89" t="str"/>
+      <x:c r="G13" s="90" t="str">
         <x:v>Not reviewed</x:v>
       </x:c>
     </x:row>
     <x:row r="14">
-      <x:c r="A14" s="85" t="str"/>
-      <x:c r="B14" s="86" t="str"/>
-      <x:c r="C14" s="92" t="str"/>
-      <x:c r="D14" s="86" t="str"/>
-      <x:c r="E14" s="86" t="str"/>
-      <x:c r="F14" s="86" t="str"/>
-      <x:c r="G14" s="87" t="str">
+      <x:c r="A14" s="88" t="str"/>
+      <x:c r="B14" s="89" t="str"/>
+      <x:c r="C14" s="95" t="str"/>
+      <x:c r="D14" s="89" t="str"/>
+      <x:c r="E14" s="89" t="str"/>
+      <x:c r="F14" s="89" t="str"/>
+      <x:c r="G14" s="90" t="str">
         <x:v>Not reviewed</x:v>
       </x:c>
     </x:row>
     <x:row r="15">
-      <x:c r="A15" s="88" t="str"/>
-      <x:c r="B15" s="89" t="str"/>
-      <x:c r="C15" s="93" t="str"/>
-      <x:c r="D15" s="89" t="str"/>
-      <x:c r="E15" s="89" t="str"/>
-      <x:c r="F15" s="89" t="str"/>
-      <x:c r="G15" s="90" t="str">
+      <x:c r="A15" s="91" t="str"/>
+      <x:c r="B15" s="92" t="str"/>
+      <x:c r="C15" s="96" t="str"/>
+      <x:c r="D15" s="92" t="str"/>
+      <x:c r="E15" s="92" t="str"/>
+      <x:c r="F15" s="92" t="str"/>
+      <x:c r="G15" s="93" t="str">
         <x:v>Not reviewed</x:v>
       </x:c>
     </x:row>
@@ -5313,13 +5569,13 @@
       <x:c r="G20" s="37"/>
     </x:row>
     <x:row r="21" ht="42" customHeight="1">
-      <x:c r="A21" s="63"/>
-      <x:c r="B21" s="110"/>
-      <x:c r="C21" s="110"/>
-      <x:c r="D21" s="110"/>
-      <x:c r="E21" s="110"/>
-      <x:c r="F21" s="110"/>
-      <x:c r="G21" s="64"/>
+      <x:c r="A21" s="66"/>
+      <x:c r="B21" s="113"/>
+      <x:c r="C21" s="113"/>
+      <x:c r="D21" s="113"/>
+      <x:c r="E21" s="113"/>
+      <x:c r="F21" s="113"/>
+      <x:c r="G21" s="67"/>
     </x:row>
     <x:row r="23" ht="23" customHeight="1">
       <x:c r="A23" s="11" t="str">
@@ -5335,7 +5591,7 @@
     </x:row>
     <x:row r="24">
       <x:c r="A24" s="21" t="str">
-        <x:v>Committee seat</x:v>
+        <x:v>Member slot</x:v>
       </x:c>
       <x:c r="B24" s="21" t="str">
         <x:v>Member name</x:v>
@@ -5357,66 +5613,76 @@
       </x:c>
     </x:row>
     <x:row r="25">
-      <x:c r="A25" s="114" t="str">
-        <x:v>Client &amp; Macro</x:v>
-      </x:c>
-      <x:c r="B25" s="82" t="str"/>
-      <x:c r="C25" s="83" t="str"/>
-      <x:c r="D25" s="83" t="str"/>
-      <x:c r="E25" s="83" t="str"/>
-      <x:c r="F25" s="83" t="str"/>
-      <x:c r="G25" s="84" t="str"/>
+      <x:c r="A25" s="117" t="str">
+        <x:v>Member 1</x:v>
+      </x:c>
+      <x:c r="B25" s="121" t="str">
+        <x:f>IF('COMMITTEE ROSTER'!B18="","",'COMMITTEE ROSTER'!B18)</x:f>
+      </x:c>
+      <x:c r="C25" s="86" t="str"/>
+      <x:c r="D25" s="86" t="str"/>
+      <x:c r="E25" s="86" t="str"/>
+      <x:c r="F25" s="86" t="str"/>
+      <x:c r="G25" s="87" t="str"/>
     </x:row>
     <x:row r="26">
-      <x:c r="A26" s="114" t="str">
-        <x:v>Fixed Income</x:v>
-      </x:c>
-      <x:c r="B26" s="85" t="str"/>
-      <x:c r="C26" s="86" t="str"/>
-      <x:c r="D26" s="86" t="str"/>
-      <x:c r="E26" s="86" t="str"/>
-      <x:c r="F26" s="86" t="str"/>
-      <x:c r="G26" s="87" t="str"/>
+      <x:c r="A26" s="117" t="str">
+        <x:v>Member 2</x:v>
+      </x:c>
+      <x:c r="B26" s="122" t="str">
+        <x:f>IF('COMMITTEE ROSTER'!B19="","",'COMMITTEE ROSTER'!B19)</x:f>
+      </x:c>
+      <x:c r="C26" s="89" t="str"/>
+      <x:c r="D26" s="89" t="str"/>
+      <x:c r="E26" s="89" t="str"/>
+      <x:c r="F26" s="89" t="str"/>
+      <x:c r="G26" s="90" t="str"/>
     </x:row>
     <x:row r="27">
-      <x:c r="A27" s="114" t="str">
-        <x:v>Equity</x:v>
-      </x:c>
-      <x:c r="B27" s="85" t="str"/>
-      <x:c r="C27" s="86" t="str"/>
-      <x:c r="D27" s="86" t="str"/>
-      <x:c r="E27" s="86" t="str"/>
-      <x:c r="F27" s="86" t="str"/>
-      <x:c r="G27" s="87" t="str"/>
+      <x:c r="A27" s="117" t="str">
+        <x:v>Member 3</x:v>
+      </x:c>
+      <x:c r="B27" s="122" t="str">
+        <x:f>IF('COMMITTEE ROSTER'!B20="","",'COMMITTEE ROSTER'!B20)</x:f>
+      </x:c>
+      <x:c r="C27" s="89" t="str"/>
+      <x:c r="D27" s="89" t="str"/>
+      <x:c r="E27" s="89" t="str"/>
+      <x:c r="F27" s="89" t="str"/>
+      <x:c r="G27" s="90" t="str"/>
     </x:row>
     <x:row r="28">
-      <x:c r="A28" s="114" t="str">
-        <x:v>Portfolio Manager</x:v>
-      </x:c>
-      <x:c r="B28" s="85" t="str"/>
-      <x:c r="C28" s="86" t="str"/>
-      <x:c r="D28" s="86" t="str"/>
-      <x:c r="E28" s="86" t="str"/>
-      <x:c r="F28" s="86" t="str"/>
-      <x:c r="G28" s="87" t="str"/>
+      <x:c r="A28" s="117" t="str">
+        <x:v>Member 4</x:v>
+      </x:c>
+      <x:c r="B28" s="122" t="str">
+        <x:f>IF('COMMITTEE ROSTER'!B21="","",'COMMITTEE ROSTER'!B21)</x:f>
+      </x:c>
+      <x:c r="C28" s="89" t="str"/>
+      <x:c r="D28" s="89" t="str"/>
+      <x:c r="E28" s="89" t="str"/>
+      <x:c r="F28" s="89" t="str"/>
+      <x:c r="G28" s="90" t="str"/>
     </x:row>
     <x:row r="29">
-      <x:c r="A29" s="114" t="str">
-        <x:v>Risk &amp; Derivatives</x:v>
-      </x:c>
-      <x:c r="B29" s="88" t="str"/>
-      <x:c r="C29" s="89" t="str"/>
-      <x:c r="D29" s="89" t="str"/>
-      <x:c r="E29" s="89" t="str"/>
-      <x:c r="F29" s="89" t="str"/>
-      <x:c r="G29" s="90" t="str"/>
+      <x:c r="A29" s="117" t="str">
+        <x:v>Member 5</x:v>
+      </x:c>
+      <x:c r="B29" s="123" t="str">
+        <x:f>IF('COMMITTEE ROSTER'!B22="","",'COMMITTEE ROSTER'!B22)</x:f>
+      </x:c>
+      <x:c r="C29" s="92" t="str"/>
+      <x:c r="D29" s="92" t="str"/>
+      <x:c r="E29" s="92" t="str"/>
+      <x:c r="F29" s="92" t="str"/>
+      <x:c r="G29" s="93" t="str"/>
     </x:row>
     <x:row r="30">
       <x:c r="A30" s="25" t="str">
         <x:v>Decision status</x:v>
       </x:c>
       <x:c r="B30" s="28" t="str">
-        <x:f>IF(COUNTIF(C25:C29,"Revise")+COUNTIF(C25:C29,"Reject")&gt;0,"REVISION REQUIRED",IF(COUNTIF(C25:C29,"Approve")=5,"APPROVED","INCOMPLETE"))</x:f>
+        <x:f>IF('COMMITTEE ROSTER'!B23&lt;&gt;"READY","INCOMPLETE",IF(COUNTIF(C25:C29,"Revise")+COUNTIF(C25:C29,"Reject")&gt;0,"REVISION REQUIRED",IF(COUNTIF(C25:C29,"Approve")='COMMITTEE ROSTER'!E19,"APPROVED","INCOMPLETE")))</x:f>
         <x:v>INCOMPLETE</x:v>
       </x:c>
       <x:c r="C30" s="29"/>
@@ -5434,22 +5700,22 @@
       <x:c r="H32" s="11"/>
     </x:row>
     <x:row r="33" ht="34" customHeight="1">
-      <x:c r="A33" s="82"/>
-      <x:c r="B33" s="83"/>
-      <x:c r="C33" s="83"/>
-      <x:c r="D33" s="83"/>
-      <x:c r="E33" s="83"/>
-      <x:c r="F33" s="83"/>
-      <x:c r="G33" s="84"/>
+      <x:c r="A33" s="85"/>
+      <x:c r="B33" s="86"/>
+      <x:c r="C33" s="86"/>
+      <x:c r="D33" s="86"/>
+      <x:c r="E33" s="86"/>
+      <x:c r="F33" s="86"/>
+      <x:c r="G33" s="87"/>
     </x:row>
     <x:row r="34" ht="34" customHeight="1">
-      <x:c r="A34" s="88"/>
-      <x:c r="B34" s="89"/>
-      <x:c r="C34" s="89"/>
-      <x:c r="D34" s="89"/>
-      <x:c r="E34" s="89"/>
-      <x:c r="F34" s="89"/>
-      <x:c r="G34" s="90"/>
+      <x:c r="A34" s="91"/>
+      <x:c r="B34" s="92"/>
+      <x:c r="C34" s="92"/>
+      <x:c r="D34" s="92"/>
+      <x:c r="E34" s="92"/>
+      <x:c r="F34" s="92"/>
+      <x:c r="G34" s="93"/>
     </x:row>
     <x:row r="36" ht="23" customHeight="1">
       <x:c r="A36" s="11" t="str">
@@ -5487,70 +5753,70 @@
       </x:c>
     </x:row>
     <x:row r="38">
-      <x:c r="A38" s="82" t="str"/>
-      <x:c r="B38" s="83" t="str"/>
-      <x:c r="C38" s="91" t="str"/>
-      <x:c r="D38" s="83" t="str"/>
-      <x:c r="E38" s="83" t="str">
+      <x:c r="A38" s="85" t="str"/>
+      <x:c r="B38" s="86" t="str"/>
+      <x:c r="C38" s="94" t="str"/>
+      <x:c r="D38" s="86" t="str"/>
+      <x:c r="E38" s="86" t="str">
         <x:v>Open</x:v>
       </x:c>
-      <x:c r="F38" s="83" t="str"/>
-      <x:c r="G38" s="84" t="str"/>
+      <x:c r="F38" s="86" t="str"/>
+      <x:c r="G38" s="87" t="str"/>
     </x:row>
     <x:row r="39">
-      <x:c r="A39" s="85" t="str"/>
-      <x:c r="B39" s="86" t="str"/>
-      <x:c r="C39" s="92" t="str"/>
-      <x:c r="D39" s="86" t="str"/>
-      <x:c r="E39" s="86" t="str">
+      <x:c r="A39" s="88" t="str"/>
+      <x:c r="B39" s="89" t="str"/>
+      <x:c r="C39" s="95" t="str"/>
+      <x:c r="D39" s="89" t="str"/>
+      <x:c r="E39" s="89" t="str">
         <x:v>Open</x:v>
       </x:c>
-      <x:c r="F39" s="86" t="str"/>
-      <x:c r="G39" s="87" t="str"/>
+      <x:c r="F39" s="89" t="str"/>
+      <x:c r="G39" s="90" t="str"/>
     </x:row>
     <x:row r="40">
-      <x:c r="A40" s="85" t="str"/>
-      <x:c r="B40" s="86" t="str"/>
-      <x:c r="C40" s="92" t="str"/>
-      <x:c r="D40" s="86" t="str"/>
-      <x:c r="E40" s="86" t="str">
+      <x:c r="A40" s="88" t="str"/>
+      <x:c r="B40" s="89" t="str"/>
+      <x:c r="C40" s="95" t="str"/>
+      <x:c r="D40" s="89" t="str"/>
+      <x:c r="E40" s="89" t="str">
         <x:v>Open</x:v>
       </x:c>
-      <x:c r="F40" s="86" t="str"/>
-      <x:c r="G40" s="87" t="str"/>
+      <x:c r="F40" s="89" t="str"/>
+      <x:c r="G40" s="90" t="str"/>
     </x:row>
     <x:row r="41">
-      <x:c r="A41" s="85" t="str"/>
-      <x:c r="B41" s="86" t="str"/>
-      <x:c r="C41" s="92" t="str"/>
-      <x:c r="D41" s="86" t="str"/>
-      <x:c r="E41" s="86" t="str">
+      <x:c r="A41" s="88" t="str"/>
+      <x:c r="B41" s="89" t="str"/>
+      <x:c r="C41" s="95" t="str"/>
+      <x:c r="D41" s="89" t="str"/>
+      <x:c r="E41" s="89" t="str">
         <x:v>Open</x:v>
       </x:c>
-      <x:c r="F41" s="86" t="str"/>
-      <x:c r="G41" s="87" t="str"/>
+      <x:c r="F41" s="89" t="str"/>
+      <x:c r="G41" s="90" t="str"/>
     </x:row>
     <x:row r="42">
-      <x:c r="A42" s="88" t="str"/>
-      <x:c r="B42" s="89" t="str"/>
-      <x:c r="C42" s="93" t="str"/>
-      <x:c r="D42" s="89" t="str"/>
-      <x:c r="E42" s="89" t="str">
+      <x:c r="A42" s="91" t="str"/>
+      <x:c r="B42" s="92" t="str"/>
+      <x:c r="C42" s="96" t="str"/>
+      <x:c r="D42" s="92" t="str"/>
+      <x:c r="E42" s="92" t="str">
         <x:v>Open</x:v>
       </x:c>
-      <x:c r="F42" s="89" t="str"/>
-      <x:c r="G42" s="90" t="str"/>
+      <x:c r="F42" s="92" t="str"/>
+      <x:c r="G42" s="93" t="str"/>
     </x:row>
     <x:row r="44" ht="32" customHeight="1">
-      <x:c r="A44" s="104" t="str">
-        <x:v>Approval requires five Approve votes. Any Revise or Reject vote produces REVISION REQUIRED; document the change and reconvene before the next gate.</x:v>
-      </x:c>
-      <x:c r="B44" s="104"/>
-      <x:c r="C44" s="104"/>
-      <x:c r="D44" s="104"/>
-      <x:c r="E44" s="104"/>
-      <x:c r="F44" s="104"/>
-      <x:c r="G44" s="104"/>
+      <x:c r="A44" s="107" t="str">
+        <x:v>Approval requires one Approve vote from each of the four or five distinct members listed on the roster. A dual-role member votes once. Any Revise or Reject vote requires revision and a new meeting.</x:v>
+      </x:c>
+      <x:c r="B44" s="107"/>
+      <x:c r="C44" s="107"/>
+      <x:c r="D44" s="107"/>
+      <x:c r="E44" s="107"/>
+      <x:c r="F44" s="107"/>
+      <x:c r="G44" s="107"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -5575,9 +5841,9 @@
     <x:mergeCell ref="A44:G44"/>
   </x:mergeCells>
   <x:conditionalFormatting sqref="B30:C30">
-    <x:cfRule type="containsText" dxfId="46" priority="1" operator="containsText" text="APPROVED"/>
-    <x:cfRule type="containsText" dxfId="47" priority="2" operator="containsText" text="REVISION"/>
-    <x:cfRule type="containsText" dxfId="48" priority="3" operator="containsText" text="INCOMPLETE"/>
+    <x:cfRule type="containsText" dxfId="53" priority="1" operator="containsText" text="APPROVED"/>
+    <x:cfRule type="containsText" dxfId="54" priority="2" operator="containsText" text="REVISION"/>
+    <x:cfRule type="containsText" dxfId="55" priority="3" operator="containsText" text="INCOMPLETE"/>
   </x:conditionalFormatting>
   <x:dataValidations count="3">
     <x:dataValidation type="list" sqref="G10:G15">
@@ -5665,292 +5931,292 @@
       </x:c>
     </x:row>
     <x:row r="5">
-      <x:c r="A5" s="115" t="str"/>
-      <x:c r="B5" s="83" t="str"/>
-      <x:c r="C5" s="83" t="str"/>
-      <x:c r="D5" s="83" t="str"/>
-      <x:c r="E5" s="83" t="str"/>
-      <x:c r="F5" s="83" t="str"/>
-      <x:c r="G5" s="83" t="str"/>
-      <x:c r="H5" s="83" t="str"/>
-      <x:c r="I5" s="84" t="str"/>
+      <x:c r="A5" s="124" t="str"/>
+      <x:c r="B5" s="86" t="str"/>
+      <x:c r="C5" s="86" t="str"/>
+      <x:c r="D5" s="86" t="str"/>
+      <x:c r="E5" s="86" t="str"/>
+      <x:c r="F5" s="86" t="str"/>
+      <x:c r="G5" s="86" t="str"/>
+      <x:c r="H5" s="86" t="str"/>
+      <x:c r="I5" s="87" t="str"/>
     </x:row>
     <x:row r="6">
-      <x:c r="A6" s="116" t="str"/>
-      <x:c r="B6" s="86" t="str"/>
-      <x:c r="C6" s="86" t="str"/>
-      <x:c r="D6" s="86" t="str"/>
-      <x:c r="E6" s="86" t="str"/>
-      <x:c r="F6" s="86" t="str"/>
-      <x:c r="G6" s="86" t="str"/>
-      <x:c r="H6" s="86" t="str"/>
-      <x:c r="I6" s="87" t="str"/>
+      <x:c r="A6" s="125" t="str"/>
+      <x:c r="B6" s="89" t="str"/>
+      <x:c r="C6" s="89" t="str"/>
+      <x:c r="D6" s="89" t="str"/>
+      <x:c r="E6" s="89" t="str"/>
+      <x:c r="F6" s="89" t="str"/>
+      <x:c r="G6" s="89" t="str"/>
+      <x:c r="H6" s="89" t="str"/>
+      <x:c r="I6" s="90" t="str"/>
     </x:row>
     <x:row r="7">
-      <x:c r="A7" s="116" t="str"/>
-      <x:c r="B7" s="86" t="str"/>
-      <x:c r="C7" s="86" t="str"/>
-      <x:c r="D7" s="86" t="str"/>
-      <x:c r="E7" s="86" t="str"/>
-      <x:c r="F7" s="86" t="str"/>
-      <x:c r="G7" s="86" t="str"/>
-      <x:c r="H7" s="86" t="str"/>
-      <x:c r="I7" s="87" t="str"/>
+      <x:c r="A7" s="125" t="str"/>
+      <x:c r="B7" s="89" t="str"/>
+      <x:c r="C7" s="89" t="str"/>
+      <x:c r="D7" s="89" t="str"/>
+      <x:c r="E7" s="89" t="str"/>
+      <x:c r="F7" s="89" t="str"/>
+      <x:c r="G7" s="89" t="str"/>
+      <x:c r="H7" s="89" t="str"/>
+      <x:c r="I7" s="90" t="str"/>
     </x:row>
     <x:row r="8">
-      <x:c r="A8" s="116" t="str"/>
-      <x:c r="B8" s="86" t="str"/>
-      <x:c r="C8" s="86" t="str"/>
-      <x:c r="D8" s="86" t="str"/>
-      <x:c r="E8" s="86" t="str"/>
-      <x:c r="F8" s="86" t="str"/>
-      <x:c r="G8" s="86" t="str"/>
-      <x:c r="H8" s="86" t="str"/>
-      <x:c r="I8" s="87" t="str"/>
+      <x:c r="A8" s="125" t="str"/>
+      <x:c r="B8" s="89" t="str"/>
+      <x:c r="C8" s="89" t="str"/>
+      <x:c r="D8" s="89" t="str"/>
+      <x:c r="E8" s="89" t="str"/>
+      <x:c r="F8" s="89" t="str"/>
+      <x:c r="G8" s="89" t="str"/>
+      <x:c r="H8" s="89" t="str"/>
+      <x:c r="I8" s="90" t="str"/>
     </x:row>
     <x:row r="9">
-      <x:c r="A9" s="116" t="str"/>
-      <x:c r="B9" s="86" t="str"/>
-      <x:c r="C9" s="86" t="str"/>
-      <x:c r="D9" s="86" t="str"/>
-      <x:c r="E9" s="86" t="str"/>
-      <x:c r="F9" s="86" t="str"/>
-      <x:c r="G9" s="86" t="str"/>
-      <x:c r="H9" s="86" t="str"/>
-      <x:c r="I9" s="87" t="str"/>
+      <x:c r="A9" s="125" t="str"/>
+      <x:c r="B9" s="89" t="str"/>
+      <x:c r="C9" s="89" t="str"/>
+      <x:c r="D9" s="89" t="str"/>
+      <x:c r="E9" s="89" t="str"/>
+      <x:c r="F9" s="89" t="str"/>
+      <x:c r="G9" s="89" t="str"/>
+      <x:c r="H9" s="89" t="str"/>
+      <x:c r="I9" s="90" t="str"/>
     </x:row>
     <x:row r="10">
-      <x:c r="A10" s="116" t="str"/>
-      <x:c r="B10" s="86" t="str"/>
-      <x:c r="C10" s="86" t="str"/>
-      <x:c r="D10" s="86" t="str"/>
-      <x:c r="E10" s="86" t="str"/>
-      <x:c r="F10" s="86" t="str"/>
-      <x:c r="G10" s="86" t="str"/>
-      <x:c r="H10" s="86" t="str"/>
-      <x:c r="I10" s="87" t="str"/>
+      <x:c r="A10" s="125" t="str"/>
+      <x:c r="B10" s="89" t="str"/>
+      <x:c r="C10" s="89" t="str"/>
+      <x:c r="D10" s="89" t="str"/>
+      <x:c r="E10" s="89" t="str"/>
+      <x:c r="F10" s="89" t="str"/>
+      <x:c r="G10" s="89" t="str"/>
+      <x:c r="H10" s="89" t="str"/>
+      <x:c r="I10" s="90" t="str"/>
     </x:row>
     <x:row r="11">
-      <x:c r="A11" s="116" t="str"/>
-      <x:c r="B11" s="86" t="str"/>
-      <x:c r="C11" s="86" t="str"/>
-      <x:c r="D11" s="86" t="str"/>
-      <x:c r="E11" s="86" t="str"/>
-      <x:c r="F11" s="86" t="str"/>
-      <x:c r="G11" s="86" t="str"/>
-      <x:c r="H11" s="86" t="str"/>
-      <x:c r="I11" s="87" t="str"/>
+      <x:c r="A11" s="125" t="str"/>
+      <x:c r="B11" s="89" t="str"/>
+      <x:c r="C11" s="89" t="str"/>
+      <x:c r="D11" s="89" t="str"/>
+      <x:c r="E11" s="89" t="str"/>
+      <x:c r="F11" s="89" t="str"/>
+      <x:c r="G11" s="89" t="str"/>
+      <x:c r="H11" s="89" t="str"/>
+      <x:c r="I11" s="90" t="str"/>
     </x:row>
     <x:row r="12">
-      <x:c r="A12" s="116" t="str"/>
-      <x:c r="B12" s="86" t="str"/>
-      <x:c r="C12" s="86" t="str"/>
-      <x:c r="D12" s="86" t="str"/>
-      <x:c r="E12" s="86" t="str"/>
-      <x:c r="F12" s="86" t="str"/>
-      <x:c r="G12" s="86" t="str"/>
-      <x:c r="H12" s="86" t="str"/>
-      <x:c r="I12" s="87" t="str"/>
+      <x:c r="A12" s="125" t="str"/>
+      <x:c r="B12" s="89" t="str"/>
+      <x:c r="C12" s="89" t="str"/>
+      <x:c r="D12" s="89" t="str"/>
+      <x:c r="E12" s="89" t="str"/>
+      <x:c r="F12" s="89" t="str"/>
+      <x:c r="G12" s="89" t="str"/>
+      <x:c r="H12" s="89" t="str"/>
+      <x:c r="I12" s="90" t="str"/>
     </x:row>
     <x:row r="13">
-      <x:c r="A13" s="116" t="str"/>
-      <x:c r="B13" s="86" t="str"/>
-      <x:c r="C13" s="86" t="str"/>
-      <x:c r="D13" s="86" t="str"/>
-      <x:c r="E13" s="86" t="str"/>
-      <x:c r="F13" s="86" t="str"/>
-      <x:c r="G13" s="86" t="str"/>
-      <x:c r="H13" s="86" t="str"/>
-      <x:c r="I13" s="87" t="str"/>
+      <x:c r="A13" s="125" t="str"/>
+      <x:c r="B13" s="89" t="str"/>
+      <x:c r="C13" s="89" t="str"/>
+      <x:c r="D13" s="89" t="str"/>
+      <x:c r="E13" s="89" t="str"/>
+      <x:c r="F13" s="89" t="str"/>
+      <x:c r="G13" s="89" t="str"/>
+      <x:c r="H13" s="89" t="str"/>
+      <x:c r="I13" s="90" t="str"/>
     </x:row>
     <x:row r="14">
-      <x:c r="A14" s="116" t="str"/>
-      <x:c r="B14" s="86" t="str"/>
-      <x:c r="C14" s="86" t="str"/>
-      <x:c r="D14" s="86" t="str"/>
-      <x:c r="E14" s="86" t="str"/>
-      <x:c r="F14" s="86" t="str"/>
-      <x:c r="G14" s="86" t="str"/>
-      <x:c r="H14" s="86" t="str"/>
-      <x:c r="I14" s="87" t="str"/>
+      <x:c r="A14" s="125" t="str"/>
+      <x:c r="B14" s="89" t="str"/>
+      <x:c r="C14" s="89" t="str"/>
+      <x:c r="D14" s="89" t="str"/>
+      <x:c r="E14" s="89" t="str"/>
+      <x:c r="F14" s="89" t="str"/>
+      <x:c r="G14" s="89" t="str"/>
+      <x:c r="H14" s="89" t="str"/>
+      <x:c r="I14" s="90" t="str"/>
     </x:row>
     <x:row r="15">
-      <x:c r="A15" s="116" t="str"/>
-      <x:c r="B15" s="86" t="str"/>
-      <x:c r="C15" s="86" t="str"/>
-      <x:c r="D15" s="86" t="str"/>
-      <x:c r="E15" s="86" t="str"/>
-      <x:c r="F15" s="86" t="str"/>
-      <x:c r="G15" s="86" t="str"/>
-      <x:c r="H15" s="86" t="str"/>
-      <x:c r="I15" s="87" t="str"/>
+      <x:c r="A15" s="125" t="str"/>
+      <x:c r="B15" s="89" t="str"/>
+      <x:c r="C15" s="89" t="str"/>
+      <x:c r="D15" s="89" t="str"/>
+      <x:c r="E15" s="89" t="str"/>
+      <x:c r="F15" s="89" t="str"/>
+      <x:c r="G15" s="89" t="str"/>
+      <x:c r="H15" s="89" t="str"/>
+      <x:c r="I15" s="90" t="str"/>
     </x:row>
     <x:row r="16">
-      <x:c r="A16" s="116" t="str"/>
-      <x:c r="B16" s="86" t="str"/>
-      <x:c r="C16" s="86" t="str"/>
-      <x:c r="D16" s="86" t="str"/>
-      <x:c r="E16" s="86" t="str"/>
-      <x:c r="F16" s="86" t="str"/>
-      <x:c r="G16" s="86" t="str"/>
-      <x:c r="H16" s="86" t="str"/>
-      <x:c r="I16" s="87" t="str"/>
+      <x:c r="A16" s="125" t="str"/>
+      <x:c r="B16" s="89" t="str"/>
+      <x:c r="C16" s="89" t="str"/>
+      <x:c r="D16" s="89" t="str"/>
+      <x:c r="E16" s="89" t="str"/>
+      <x:c r="F16" s="89" t="str"/>
+      <x:c r="G16" s="89" t="str"/>
+      <x:c r="H16" s="89" t="str"/>
+      <x:c r="I16" s="90" t="str"/>
     </x:row>
     <x:row r="17">
-      <x:c r="A17" s="116" t="str"/>
-      <x:c r="B17" s="86" t="str"/>
-      <x:c r="C17" s="86" t="str"/>
-      <x:c r="D17" s="86" t="str"/>
-      <x:c r="E17" s="86" t="str"/>
-      <x:c r="F17" s="86" t="str"/>
-      <x:c r="G17" s="86" t="str"/>
-      <x:c r="H17" s="86" t="str"/>
-      <x:c r="I17" s="87" t="str"/>
+      <x:c r="A17" s="125" t="str"/>
+      <x:c r="B17" s="89" t="str"/>
+      <x:c r="C17" s="89" t="str"/>
+      <x:c r="D17" s="89" t="str"/>
+      <x:c r="E17" s="89" t="str"/>
+      <x:c r="F17" s="89" t="str"/>
+      <x:c r="G17" s="89" t="str"/>
+      <x:c r="H17" s="89" t="str"/>
+      <x:c r="I17" s="90" t="str"/>
     </x:row>
     <x:row r="18">
-      <x:c r="A18" s="116" t="str"/>
-      <x:c r="B18" s="86" t="str"/>
-      <x:c r="C18" s="86" t="str"/>
-      <x:c r="D18" s="86" t="str"/>
-      <x:c r="E18" s="86" t="str"/>
-      <x:c r="F18" s="86" t="str"/>
-      <x:c r="G18" s="86" t="str"/>
-      <x:c r="H18" s="86" t="str"/>
-      <x:c r="I18" s="87" t="str"/>
+      <x:c r="A18" s="125" t="str"/>
+      <x:c r="B18" s="89" t="str"/>
+      <x:c r="C18" s="89" t="str"/>
+      <x:c r="D18" s="89" t="str"/>
+      <x:c r="E18" s="89" t="str"/>
+      <x:c r="F18" s="89" t="str"/>
+      <x:c r="G18" s="89" t="str"/>
+      <x:c r="H18" s="89" t="str"/>
+      <x:c r="I18" s="90" t="str"/>
     </x:row>
     <x:row r="19">
-      <x:c r="A19" s="116" t="str"/>
-      <x:c r="B19" s="86" t="str"/>
-      <x:c r="C19" s="86" t="str"/>
-      <x:c r="D19" s="86" t="str"/>
-      <x:c r="E19" s="86" t="str"/>
-      <x:c r="F19" s="86" t="str"/>
-      <x:c r="G19" s="86" t="str"/>
-      <x:c r="H19" s="86" t="str"/>
-      <x:c r="I19" s="87" t="str"/>
+      <x:c r="A19" s="125" t="str"/>
+      <x:c r="B19" s="89" t="str"/>
+      <x:c r="C19" s="89" t="str"/>
+      <x:c r="D19" s="89" t="str"/>
+      <x:c r="E19" s="89" t="str"/>
+      <x:c r="F19" s="89" t="str"/>
+      <x:c r="G19" s="89" t="str"/>
+      <x:c r="H19" s="89" t="str"/>
+      <x:c r="I19" s="90" t="str"/>
     </x:row>
     <x:row r="20">
-      <x:c r="A20" s="116" t="str"/>
-      <x:c r="B20" s="86" t="str"/>
-      <x:c r="C20" s="86" t="str"/>
-      <x:c r="D20" s="86" t="str"/>
-      <x:c r="E20" s="86" t="str"/>
-      <x:c r="F20" s="86" t="str"/>
-      <x:c r="G20" s="86" t="str"/>
-      <x:c r="H20" s="86" t="str"/>
-      <x:c r="I20" s="87" t="str"/>
+      <x:c r="A20" s="125" t="str"/>
+      <x:c r="B20" s="89" t="str"/>
+      <x:c r="C20" s="89" t="str"/>
+      <x:c r="D20" s="89" t="str"/>
+      <x:c r="E20" s="89" t="str"/>
+      <x:c r="F20" s="89" t="str"/>
+      <x:c r="G20" s="89" t="str"/>
+      <x:c r="H20" s="89" t="str"/>
+      <x:c r="I20" s="90" t="str"/>
     </x:row>
     <x:row r="21">
-      <x:c r="A21" s="116" t="str"/>
-      <x:c r="B21" s="86" t="str"/>
-      <x:c r="C21" s="86" t="str"/>
-      <x:c r="D21" s="86" t="str"/>
-      <x:c r="E21" s="86" t="str"/>
-      <x:c r="F21" s="86" t="str"/>
-      <x:c r="G21" s="86" t="str"/>
-      <x:c r="H21" s="86" t="str"/>
-      <x:c r="I21" s="87" t="str"/>
+      <x:c r="A21" s="125" t="str"/>
+      <x:c r="B21" s="89" t="str"/>
+      <x:c r="C21" s="89" t="str"/>
+      <x:c r="D21" s="89" t="str"/>
+      <x:c r="E21" s="89" t="str"/>
+      <x:c r="F21" s="89" t="str"/>
+      <x:c r="G21" s="89" t="str"/>
+      <x:c r="H21" s="89" t="str"/>
+      <x:c r="I21" s="90" t="str"/>
     </x:row>
     <x:row r="22">
-      <x:c r="A22" s="116" t="str"/>
-      <x:c r="B22" s="86" t="str"/>
-      <x:c r="C22" s="86" t="str"/>
-      <x:c r="D22" s="86" t="str"/>
-      <x:c r="E22" s="86" t="str"/>
-      <x:c r="F22" s="86" t="str"/>
-      <x:c r="G22" s="86" t="str"/>
-      <x:c r="H22" s="86" t="str"/>
-      <x:c r="I22" s="87" t="str"/>
+      <x:c r="A22" s="125" t="str"/>
+      <x:c r="B22" s="89" t="str"/>
+      <x:c r="C22" s="89" t="str"/>
+      <x:c r="D22" s="89" t="str"/>
+      <x:c r="E22" s="89" t="str"/>
+      <x:c r="F22" s="89" t="str"/>
+      <x:c r="G22" s="89" t="str"/>
+      <x:c r="H22" s="89" t="str"/>
+      <x:c r="I22" s="90" t="str"/>
     </x:row>
     <x:row r="23">
-      <x:c r="A23" s="116" t="str"/>
-      <x:c r="B23" s="86" t="str"/>
-      <x:c r="C23" s="86" t="str"/>
-      <x:c r="D23" s="86" t="str"/>
-      <x:c r="E23" s="86" t="str"/>
-      <x:c r="F23" s="86" t="str"/>
-      <x:c r="G23" s="86" t="str"/>
-      <x:c r="H23" s="86" t="str"/>
-      <x:c r="I23" s="87" t="str"/>
+      <x:c r="A23" s="125" t="str"/>
+      <x:c r="B23" s="89" t="str"/>
+      <x:c r="C23" s="89" t="str"/>
+      <x:c r="D23" s="89" t="str"/>
+      <x:c r="E23" s="89" t="str"/>
+      <x:c r="F23" s="89" t="str"/>
+      <x:c r="G23" s="89" t="str"/>
+      <x:c r="H23" s="89" t="str"/>
+      <x:c r="I23" s="90" t="str"/>
     </x:row>
     <x:row r="24">
-      <x:c r="A24" s="116" t="str"/>
-      <x:c r="B24" s="86" t="str"/>
-      <x:c r="C24" s="86" t="str"/>
-      <x:c r="D24" s="86" t="str"/>
-      <x:c r="E24" s="86" t="str"/>
-      <x:c r="F24" s="86" t="str"/>
-      <x:c r="G24" s="86" t="str"/>
-      <x:c r="H24" s="86" t="str"/>
-      <x:c r="I24" s="87" t="str"/>
+      <x:c r="A24" s="125" t="str"/>
+      <x:c r="B24" s="89" t="str"/>
+      <x:c r="C24" s="89" t="str"/>
+      <x:c r="D24" s="89" t="str"/>
+      <x:c r="E24" s="89" t="str"/>
+      <x:c r="F24" s="89" t="str"/>
+      <x:c r="G24" s="89" t="str"/>
+      <x:c r="H24" s="89" t="str"/>
+      <x:c r="I24" s="90" t="str"/>
     </x:row>
     <x:row r="25">
-      <x:c r="A25" s="116" t="str"/>
-      <x:c r="B25" s="86" t="str"/>
-      <x:c r="C25" s="86" t="str"/>
-      <x:c r="D25" s="86" t="str"/>
-      <x:c r="E25" s="86" t="str"/>
-      <x:c r="F25" s="86" t="str"/>
-      <x:c r="G25" s="86" t="str"/>
-      <x:c r="H25" s="86" t="str"/>
-      <x:c r="I25" s="87" t="str"/>
+      <x:c r="A25" s="125" t="str"/>
+      <x:c r="B25" s="89" t="str"/>
+      <x:c r="C25" s="89" t="str"/>
+      <x:c r="D25" s="89" t="str"/>
+      <x:c r="E25" s="89" t="str"/>
+      <x:c r="F25" s="89" t="str"/>
+      <x:c r="G25" s="89" t="str"/>
+      <x:c r="H25" s="89" t="str"/>
+      <x:c r="I25" s="90" t="str"/>
     </x:row>
     <x:row r="26">
-      <x:c r="A26" s="116" t="str"/>
-      <x:c r="B26" s="86" t="str"/>
-      <x:c r="C26" s="86" t="str"/>
-      <x:c r="D26" s="86" t="str"/>
-      <x:c r="E26" s="86" t="str"/>
-      <x:c r="F26" s="86" t="str"/>
-      <x:c r="G26" s="86" t="str"/>
-      <x:c r="H26" s="86" t="str"/>
-      <x:c r="I26" s="87" t="str"/>
+      <x:c r="A26" s="125" t="str"/>
+      <x:c r="B26" s="89" t="str"/>
+      <x:c r="C26" s="89" t="str"/>
+      <x:c r="D26" s="89" t="str"/>
+      <x:c r="E26" s="89" t="str"/>
+      <x:c r="F26" s="89" t="str"/>
+      <x:c r="G26" s="89" t="str"/>
+      <x:c r="H26" s="89" t="str"/>
+      <x:c r="I26" s="90" t="str"/>
     </x:row>
     <x:row r="27">
-      <x:c r="A27" s="116" t="str"/>
-      <x:c r="B27" s="86" t="str"/>
-      <x:c r="C27" s="86" t="str"/>
-      <x:c r="D27" s="86" t="str"/>
-      <x:c r="E27" s="86" t="str"/>
-      <x:c r="F27" s="86" t="str"/>
-      <x:c r="G27" s="86" t="str"/>
-      <x:c r="H27" s="86" t="str"/>
-      <x:c r="I27" s="87" t="str"/>
+      <x:c r="A27" s="125" t="str"/>
+      <x:c r="B27" s="89" t="str"/>
+      <x:c r="C27" s="89" t="str"/>
+      <x:c r="D27" s="89" t="str"/>
+      <x:c r="E27" s="89" t="str"/>
+      <x:c r="F27" s="89" t="str"/>
+      <x:c r="G27" s="89" t="str"/>
+      <x:c r="H27" s="89" t="str"/>
+      <x:c r="I27" s="90" t="str"/>
     </x:row>
     <x:row r="28">
-      <x:c r="A28" s="116" t="str"/>
-      <x:c r="B28" s="86" t="str"/>
-      <x:c r="C28" s="86" t="str"/>
-      <x:c r="D28" s="86" t="str"/>
-      <x:c r="E28" s="86" t="str"/>
-      <x:c r="F28" s="86" t="str"/>
-      <x:c r="G28" s="86" t="str"/>
-      <x:c r="H28" s="86" t="str"/>
-      <x:c r="I28" s="87" t="str"/>
+      <x:c r="A28" s="125" t="str"/>
+      <x:c r="B28" s="89" t="str"/>
+      <x:c r="C28" s="89" t="str"/>
+      <x:c r="D28" s="89" t="str"/>
+      <x:c r="E28" s="89" t="str"/>
+      <x:c r="F28" s="89" t="str"/>
+      <x:c r="G28" s="89" t="str"/>
+      <x:c r="H28" s="89" t="str"/>
+      <x:c r="I28" s="90" t="str"/>
     </x:row>
     <x:row r="29">
-      <x:c r="A29" s="111" t="str"/>
-      <x:c r="B29" s="89" t="str"/>
-      <x:c r="C29" s="89" t="str"/>
-      <x:c r="D29" s="89" t="str"/>
-      <x:c r="E29" s="89" t="str"/>
-      <x:c r="F29" s="89" t="str"/>
-      <x:c r="G29" s="89" t="str"/>
-      <x:c r="H29" s="89" t="str"/>
-      <x:c r="I29" s="90" t="str"/>
+      <x:c r="A29" s="114" t="str"/>
+      <x:c r="B29" s="92" t="str"/>
+      <x:c r="C29" s="92" t="str"/>
+      <x:c r="D29" s="92" t="str"/>
+      <x:c r="E29" s="92" t="str"/>
+      <x:c r="F29" s="92" t="str"/>
+      <x:c r="G29" s="92" t="str"/>
+      <x:c r="H29" s="92" t="str"/>
+      <x:c r="I29" s="93" t="str"/>
     </x:row>
     <x:row r="31" ht="32" customHeight="1">
-      <x:c r="A31" s="104" t="str">
+      <x:c r="A31" s="107" t="str">
         <x:v>Do not paste confidential client information or proprietary FactSet data into an AI tool. Every AI-assisted factual claim or number must be traceable to a human-verified source.</x:v>
       </x:c>
-      <x:c r="B31" s="104"/>
-      <x:c r="C31" s="104"/>
-      <x:c r="D31" s="104"/>
-      <x:c r="E31" s="104"/>
-      <x:c r="F31" s="104"/>
-      <x:c r="G31" s="104"/>
-      <x:c r="H31" s="104"/>
-      <x:c r="I31" s="104"/>
+      <x:c r="B31" s="107"/>
+      <x:c r="C31" s="107"/>
+      <x:c r="D31" s="107"/>
+      <x:c r="E31" s="107"/>
+      <x:c r="F31" s="107"/>
+      <x:c r="G31" s="107"/>
+      <x:c r="H31" s="107"/>
+      <x:c r="I31" s="107"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>

--- a/files/BUS331_Investment_Committee_Decision_Record_Student.xlsx
+++ b/files/BUS331_Investment_Committee_Decision_Record_Student.xlsx
@@ -1798,10 +1798,10 @@
       </x:c>
       <x:c r="B5" s="53" t="str"/>
       <x:c r="C5" s="54" t="str">
-        <x:v>Own client discovery, the 12-month market view, IPS objectives and constraints, and the handoff from client needs to investment criteria.</x:v>
+        <x:v>Own client scenario analysis, the 12-month market view, IPS objectives and constraints, and the handoff from client needs to investment criteria.</x:v>
       </x:c>
       <x:c r="D5" s="54" t="str">
-        <x:v>Lead the client interview, document goals and RRTTLLU constraints, establish the macro context, and name unresolved information gaps.</x:v>
+        <x:v>Lead analysis of the assigned client scenarios, document goals and RRTTLLU constraints, establish the macro context, and label reasoned assumptions and information gaps.</x:v>
       </x:c>
       <x:c r="E5" s="54" t="str">
         <x:v>Test whether proposed allocations and securities fit the approved client mandate and the committee's market view.</x:v>
@@ -2162,7 +2162,7 @@
     </x:row>
     <x:row r="5" ht="30" customHeight="1">
       <x:c r="A5" s="37" t="str">
-        <x:v>Summarize AI output; do not paste transcripts. Unknown client information stays unknown. Do not enter real personal information or proprietary FactSet data into an AI tool.</x:v>
+        <x:v>Separate supplied case facts from labeled, reasoned assumptions. Mark unsupported exact values for confirmation. Summarize AI challenges; do not enter real personal information or proprietary FactSet data into an AI tool.</x:v>
       </x:c>
       <x:c r="B5" s="37"/>
       <x:c r="C5" s="37"/>
